--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -10468,11 +10468,23 @@
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>UM+1174926</t>
+        </is>
+      </c>
       <c r="Q88" s="4" t="inlineStr"/>
-      <c r="R88" s="4" t="inlineStr"/>
+      <c r="R88" s="4" t="inlineStr">
+        <is>
+          <t>29-maktab</t>
+        </is>
+      </c>
       <c r="S88" s="5" t="inlineStr"/>
-      <c r="T88" s="5" t="inlineStr"/>
+      <c r="T88" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U88" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -35705,11 +35717,23 @@
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>UM+1174926</t>
+        </is>
+      </c>
       <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>29-maktab</t>
+        </is>
+      </c>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U19" s="16" t="inlineStr">
         <is>
           <t>CHALA</t>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -10470,7 +10470,7 @@
       <c r="O88" s="4" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>UM+1174926</t>
+          <t>UM 1174926</t>
         </is>
       </c>
       <c r="Q88" s="4" t="inlineStr"/>
@@ -12747,18 +12747,18 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Azamat+qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat+qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>AE+4905104</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P109" s="9" t="inlineStr">
         <is>
-          <t>UM+03730102</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q109" s="11" t="inlineStr"/>
@@ -24428,18 +24428,18 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Azamat+qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat+qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE+4905104</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM+03730102</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr"/>
@@ -35919,7 +35919,7 @@
       <c r="O19" s="11" t="inlineStr"/>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM+1174926</t>
+          <t>UM 1174926</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr"/>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X181"/>
+  <dimension ref="A1:X182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -15069,79 +15069,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+      <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr"/>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T130" s="5" t="inlineStr">
@@ -15154,15 +15134,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V130" s="4" t="inlineStr"/>
-      <c r="W130" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X130" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V130" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W130" s="15" t="inlineStr"/>
+      <c r="X130" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -15172,12 +15152,12 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -15187,7 +15167,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -15197,37 +15177,37 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
@@ -15237,23 +15217,27 @@
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q131" s="11" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q131" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T131" s="12" t="inlineStr">
@@ -15284,12 +15268,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Soyipova Dinora</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -15299,43 +15283,47 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Sanjar qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
@@ -15343,41 +15331,41 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O132" s="4" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>UM03297405</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q132" s="4" t="inlineStr"/>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>22-maktab</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U132" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W132" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U132" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V132" s="4" t="inlineStr"/>
+      <c r="W132" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X132" s="7" t="inlineStr">
@@ -15397,51 +15385,53 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Suyarova Dinora</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr"/>
+          <t>Soyipova Dinora</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="F133" s="18" t="n">
-        <v>46280</v>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Sodiq qizi</t>
+          <t>Sanjar qizi</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+          <t>Soyipova Dinora Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
@@ -15449,20 +15439,16 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O133" s="11" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+      <c r="O133" s="11" t="inlineStr"/>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>UM 03755218</t>
+          <t>UM03297405</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr"/>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>22-maktab</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
@@ -15470,22 +15456,24 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T133" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T133" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U133" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
-      <c r="W133" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W133" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15500,90 +15488,86 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
+          <t>Suyarova Dinora</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>46280</v>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Sodiq qizi</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>01.08.2008</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
+          <t>UM 03755218</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T134" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T134" s="5" t="n">
+        <v>2026</v>
       </c>
       <c r="U134" s="7" t="inlineStr">
         <is>
@@ -15592,12 +15576,12 @@
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
         </is>
       </c>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15612,22 +15596,18 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -15637,72 +15617,68 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>UM 03296212</t>
-        </is>
-      </c>
-      <c r="Q135" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q135" s="11" t="inlineStr"/>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T135" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
@@ -15710,10 +15686,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V135" s="11" t="inlineStr"/>
+      <c r="V135" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15728,12 +15708,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Temirboyeva Iroda</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -15743,43 +15723,47 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr"/>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>01.12.2007</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
@@ -15789,18 +15773,22 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr"/>
+          <t>UM 03296212</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
+        </is>
+      </c>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
@@ -15810,18 +15798,18 @@
       </c>
       <c r="T136" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U136" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U136" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V136" s="4" t="inlineStr"/>
-      <c r="W136" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W136" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15836,12 +15824,12 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -15851,47 +15839,43 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr"/>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
@@ -15901,22 +15885,18 @@
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q137" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q137" s="11" t="inlineStr"/>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
@@ -15929,15 +15909,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U137" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr"/>
-      <c r="W137" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W137" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15957,7 +15937,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15967,74 +15947,82 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N138" s="5" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T138" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U138" s="7" t="inlineStr">
@@ -16043,9 +16031,9 @@
         </is>
       </c>
       <c r="V138" s="4" t="inlineStr"/>
-      <c r="W138" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W138" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -16060,12 +16048,12 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -16075,7 +16063,7 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
@@ -16085,68 +16073,64 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
-        </is>
-      </c>
-      <c r="N139" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr"/>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q139" s="11" t="inlineStr"/>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T139" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -16172,12 +16156,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Toshmurodova Sarvara</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -16187,7 +16171,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -16197,37 +16181,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
@@ -16237,22 +16221,18 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr"/>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
@@ -16262,7 +16242,7 @@
       </c>
       <c r="T140" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
@@ -16273,7 +16253,7 @@
       <c r="V140" s="4" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X140" s="7" t="inlineStr">
@@ -16288,12 +16268,12 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Toshpo'latova Asila</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -16303,7 +16283,7 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -16313,54 +16293,62 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>17.09.2008</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O141" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q141" s="11" t="inlineStr"/>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q141" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
@@ -16373,15 +16361,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U141" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U141" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16396,83 +16384,79 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Oybek qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr">
-        <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03751635</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr"/>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
@@ -16485,15 +16469,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U142" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U142" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16508,62 +16492,58 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Turayeva Dilsuz</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr"/>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Oybek qizi</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>12.05.2009</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
@@ -16573,22 +16553,22 @@
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03751635</t>
         </is>
       </c>
       <c r="Q143" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
         </is>
       </c>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
@@ -16598,7 +16578,7 @@
       </c>
       <c r="T143" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -16624,12 +16604,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -16639,7 +16619,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -16649,37 +16629,37 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
@@ -16689,39 +16669,43 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>PT 0339231</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-sonli politexnikum</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U144" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U144" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V144" s="4" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X144" s="7" t="inlineStr">
@@ -16736,18 +16720,22 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr"/>
+          <t>Turg'unova Jasmina</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -16757,67 +16745,63 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q145" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339231</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr"/>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-sonli politexnikum</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T145" s="12" t="inlineStr">
@@ -16825,15 +16809,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U145" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X145" s="7" t="inlineStr">
@@ -16848,87 +16832,83 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
@@ -16938,7 +16918,7 @@
       </c>
       <c r="T146" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U146" s="7" t="inlineStr">
@@ -16949,7 +16929,7 @@
       <c r="V146" s="4" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X146" s="7" t="inlineStr">
@@ -16969,78 +16949,82 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr"/>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q147" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -17050,7 +17034,7 @@
       </c>
       <c r="T147" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -17061,7 +17045,7 @@
       <c r="V147" s="11" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X147" s="7" t="inlineStr">
@@ -17081,13 +17065,13 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -17102,22 +17086,22 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
@@ -17137,17 +17121,17 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
@@ -17188,56 +17172,58 @@
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F149" s="18" t="n">
-        <v>46272</v>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Dalerovna</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
@@ -17247,22 +17233,22 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM-O 00064269</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S149" s="12" t="inlineStr">
@@ -17280,11 +17266,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V149" s="11" t="inlineStr">
-        <is>
-          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
-        </is>
-      </c>
+      <c r="V149" s="11" t="inlineStr"/>
       <c r="W149" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -17307,70 +17289,76 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tuychiyeva Farzona</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F150" s="5" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Dalerovna</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr"/>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM 03728161</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr"/>
+          <t>UM-O 00064269</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+        </is>
+      </c>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -17380,12 +17368,24 @@
       </c>
       <c r="T150" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U150" s="5" t="inlineStr"/>
-      <c r="V150" s="4" t="inlineStr"/>
-      <c r="W150" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U150" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr">
+        <is>
+          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
+        </is>
+      </c>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X150" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Ulugbekova Zara</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -17413,47 +17413,39 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr"/>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr"/>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.09.2008</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
@@ -17463,22 +17455,18 @@
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728161</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr"/>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17488,20 +17476,12 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U151" s="12" t="inlineStr"/>
       <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W151" s="15" t="inlineStr"/>
       <c r="X151" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17514,98 +17494,108 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="n">
-        <v>46275</v>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O152" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>Umarova Iroda Muzaffar qizi</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr"/>
+          <t>UM 03754201</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+        </is>
+      </c>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U152" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U152" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X152" s="7" t="inlineStr">
@@ -17620,112 +17610,98 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Umirova Sevinch</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr"/>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="n">
+        <v>46275</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>09.06.2005</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr"/>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr"/>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T153" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U153" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V153" s="11" t="inlineStr">
         <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
         </is>
       </c>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17745,7 +17721,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -17755,85 +17731,97 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T154" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U154" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U154" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V154" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17848,56 +17836,62 @@
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr"/>
+          <t>Usmanova Iroda</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F155" s="18" t="n">
-        <v>46272</v>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:00:00</t>
+        </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Xamdam qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
@@ -17905,20 +17899,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O155" s="11" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
+      <c r="O155" s="11" t="inlineStr"/>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>K 1994177</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q155" s="11" t="inlineStr"/>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
@@ -17928,22 +17918,18 @@
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V155" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U155" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V155" s="11" t="inlineStr"/>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17958,97 +17944,87 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>26.01.1992</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
-        </is>
-      </c>
+          <t>K 1994177</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U156" s="7" t="inlineStr">
@@ -18056,7 +18032,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V156" s="4" t="inlineStr"/>
+      <c r="V156" s="4" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W156" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -18074,18 +18054,22 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr"/>
+          <t>Usmonova Sabrina</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -18095,62 +18079,62 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
+          <t>UM 03754097</t>
         </is>
       </c>
       <c r="Q157" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
         </is>
       </c>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
@@ -18160,7 +18144,7 @@
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -18186,71 +18170,83 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr"/>
-      <c r="F158" s="5" t="inlineStr"/>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr"/>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
+        </is>
+      </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr"/>
+          <t>UM 03273678</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+        </is>
+      </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -18260,16 +18256,20 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U158" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U158" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V158" s="4" t="inlineStr"/>
-      <c r="W158" s="15" t="inlineStr"/>
+      <c r="W158" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X158" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Xamdamova Madina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
@@ -18295,96 +18295,77 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F159" s="18" t="n">
-        <v>46197</v>
-      </c>
+      <c r="E159" s="12" t="inlineStr"/>
+      <c r="F159" s="12" t="inlineStr"/>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Abdiqodir qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>07.12.1990</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O159" s="11" t="inlineStr">
-        <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr"/>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>K 5487959</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q159" s="11" t="inlineStr"/>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V159" s="11" t="inlineStr">
-        <is>
-          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
-to'g'risi: 62701015680026</t>
-        </is>
-      </c>
-      <c r="W159" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U159" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V159" s="11" t="inlineStr"/>
+      <c r="W159" s="15" t="inlineStr"/>
       <c r="X159" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18402,51 +18383,55 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr"/>
+          <t>Xamdamova Madina</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F160" s="6" t="n">
-        <v>46247</v>
+        <v>46197</v>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Abdiqodir qizi</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
@@ -18454,33 +18439,46 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O160" s="4" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>UM 0862565</t>
+          <t>K 5487959</t>
         </is>
       </c>
       <c r="Q160" s="4" t="inlineStr"/>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
-        </is>
-      </c>
-      <c r="S160" s="5" t="inlineStr"/>
+          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U160" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="inlineStr"/>
-      <c r="W160" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U160" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V160" s="4" t="inlineStr">
+        <is>
+          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
+to'g'risi: 62701015680026</t>
+        </is>
+      </c>
+      <c r="W160" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X160" s="7" t="inlineStr">
@@ -18495,108 +18493,90 @@
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xannonova Shohsanam</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="F161" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="n">
+        <v>46247</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>02.06.2004</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O161" s="11" t="inlineStr">
-        <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O161" s="11" t="inlineStr"/>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
-        </is>
-      </c>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0862565</t>
+        </is>
+      </c>
+      <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S161" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="S161" s="12" t="inlineStr"/>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U161" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V161" s="11" t="inlineStr"/>
-      <c r="W161" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W161" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18616,7 +18596,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -18626,7 +18606,7 @@
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -18636,37 +18616,37 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
@@ -18676,23 +18656,27 @@
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S162" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T162" s="5" t="inlineStr">
@@ -18706,9 +18690,9 @@
         </is>
       </c>
       <c r="V162" s="4" t="inlineStr"/>
-      <c r="W162" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W162" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X162" s="7" t="inlineStr">
@@ -18723,12 +18707,12 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
+          <t>Xayrullayeva Umida</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18738,91 +18722,89 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
+          <t>PT 0025701</t>
         </is>
       </c>
       <c r="Q163" s="11" t="inlineStr"/>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T163" s="12" t="n">
-        <v>2019</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T163" s="12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V163" s="11" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W163" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V163" s="11" t="inlineStr"/>
+      <c r="W163" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X163" s="7" t="inlineStr">
@@ -18837,83 +18819,83 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0086260</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
@@ -18921,10 +18903,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T164" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T164" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
@@ -18933,7 +18913,7 @@
       </c>
       <c r="V164" s="4" t="inlineStr">
         <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W164" s="8" t="inlineStr">
@@ -18958,17 +18938,13 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -18978,62 +18954,62 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q165" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
@@ -19051,7 +19027,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V165" s="11" t="inlineStr"/>
+      <c r="V165" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W165" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -19069,12 +19049,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -19084,7 +19064,7 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -19094,37 +19074,37 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
@@ -19134,28 +19114,32 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr"/>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+        </is>
+      </c>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T166" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U166" s="7" t="inlineStr">
@@ -19163,14 +19147,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W166" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V166" s="4" t="inlineStr"/>
+      <c r="W166" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X166" s="7" t="inlineStr">
@@ -19185,12 +19165,12 @@
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
@@ -19200,81 +19180,79 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N167" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P167" s="9" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q167" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>K 3418837</t>
+        </is>
+      </c>
+      <c r="Q167" s="11" t="inlineStr"/>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T167" s="12" t="n">
-        <v>2026</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T167" s="12" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
@@ -19283,12 +19261,12 @@
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W167" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W167" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X167" s="7" t="inlineStr">
@@ -19303,12 +19281,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -19318,47 +19296,47 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N168" s="5" t="inlineStr">
@@ -19368,18 +19346,22 @@
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R168" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S168" s="5" t="inlineStr">
@@ -19387,20 +19369,22 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T168" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="T168" s="5" t="n">
+        <v>2026</v>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V168" s="4" t="inlineStr"/>
+      <c r="V168" s="4" t="inlineStr">
+        <is>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W168" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X168" s="7" t="inlineStr">
@@ -19415,12 +19399,12 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
@@ -19430,60 +19414,68 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="F169" s="12" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="I169" s="10" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N169" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="Q169" s="11" t="inlineStr"/>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
@@ -19496,9 +19488,17 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U169" s="12" t="inlineStr"/>
+      <c r="U169" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V169" s="11" t="inlineStr"/>
-      <c r="W169" s="15" t="inlineStr"/>
+      <c r="W169" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X169" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xujamuratova Durdona</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -19526,72 +19526,60 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr"/>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03717652</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S170" s="5" t="inlineStr">
@@ -19601,20 +19589,12 @@
       </c>
       <c r="T170" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U170" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U170" s="5" t="inlineStr"/>
       <c r="V170" s="4" t="inlineStr"/>
-      <c r="W170" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W170" s="15" t="inlineStr"/>
       <c r="X170" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19632,7 +19612,7 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Sabina</t>
+          <t>Xurramova Lobar</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
@@ -19642,56 +19622,72 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr"/>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Yuldosh qizi</t>
+          <t>Ural qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
-        </is>
-      </c>
-      <c r="I171" s="10" t="inlineStr"/>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
-        </is>
-      </c>
-      <c r="N171" s="12" t="inlineStr"/>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N171" s="12" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>UM 1315230</t>
-        </is>
-      </c>
-      <c r="Q171" s="11" t="inlineStr"/>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19701,12 +19697,20 @@
       </c>
       <c r="T171" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U171" s="12" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U171" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V171" s="11" t="inlineStr"/>
-      <c r="W171" s="15" t="inlineStr"/>
+      <c r="W171" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X171" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19719,12 +19723,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -19734,89 +19738,71 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F172" s="6" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr"/>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N172" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr"/>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q172" s="4" t="inlineStr"/>
       <c r="R172" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S172" s="5" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U172" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U172" s="5" t="inlineStr"/>
       <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W172" s="15" t="inlineStr"/>
       <c r="X172" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19834,7 +19820,7 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
@@ -19844,13 +19830,11 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F173" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="n">
+        <v>46204</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -19859,32 +19843,32 @@
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N173" s="12" t="inlineStr">
@@ -19894,32 +19878,28 @@
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q173" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q173" s="11" t="inlineStr"/>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S173" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T173" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -19945,12 +19925,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -19960,7 +19940,7 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -19970,58 +19950,62 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R174" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S174" s="5" t="inlineStr">
@@ -20031,7 +20015,7 @@
       </c>
       <c r="T174" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U174" s="7" t="inlineStr">
@@ -20039,11 +20023,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V174" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V174" s="4" t="inlineStr"/>
       <c r="W174" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -20061,12 +20041,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -20076,7 +20056,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -20086,37 +20066,37 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N175" s="12" t="inlineStr">
@@ -20126,22 +20106,18 @@
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="P175" s="9" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q175" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q175" s="11" t="inlineStr"/>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S175" s="12" t="inlineStr">
@@ -20151,7 +20127,7 @@
       </c>
       <c r="T175" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -20161,12 +20137,12 @@
       </c>
       <c r="V175" s="11" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
         </is>
       </c>
       <c r="W175" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X175" s="7" t="inlineStr">
@@ -20181,18 +20157,22 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -20202,62 +20182,62 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q176" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R176" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S176" s="5" t="inlineStr">
@@ -20275,10 +20255,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V176" s="4" t="inlineStr"/>
+      <c r="V176" s="4" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W176" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X176" s="7" t="inlineStr">
@@ -20293,22 +20277,18 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr"/>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -20318,37 +20298,37 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N177" s="12" t="inlineStr">
@@ -20358,22 +20338,22 @@
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P177" s="9" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q177" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R177" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S177" s="12" t="inlineStr">
@@ -20383,7 +20363,7 @@
       </c>
       <c r="T177" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
@@ -20394,7 +20374,7 @@
       <c r="V177" s="11" t="inlineStr"/>
       <c r="W177" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X177" s="7" t="inlineStr">
@@ -20409,12 +20389,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -20424,7 +20404,7 @@
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -20434,68 +20414,72 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N178" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
-        </is>
-      </c>
-      <c r="Q178" s="4" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R178" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S178" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T178" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr">
@@ -20503,14 +20487,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V178" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W178" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V178" s="4" t="inlineStr"/>
+      <c r="W178" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X178" s="7" t="inlineStr">
@@ -20525,12 +20505,12 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
@@ -20540,7 +20520,7 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -20550,67 +20530,63 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N179" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P179" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q179" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q179" s="11" t="inlineStr"/>
       <c r="R179" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S179" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T179" s="12" t="inlineStr">
@@ -20623,10 +20599,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V179" s="11" t="inlineStr"/>
-      <c r="W179" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V179" s="11" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W179" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X179" s="7" t="inlineStr">
@@ -20641,12 +20621,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -20656,7 +20636,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -20666,37 +20646,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N180" s="5" t="inlineStr">
@@ -20706,22 +20686,22 @@
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q180" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R180" s="4" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S180" s="5" t="inlineStr">
@@ -20742,7 +20722,7 @@
       <c r="V180" s="4" t="inlineStr"/>
       <c r="W180" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X180" s="7" t="inlineStr">
@@ -20757,18 +20737,22 @@
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D181" s="11" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -20778,62 +20762,62 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L181" s="12" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M181" s="12" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q181" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R181" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S181" s="12" t="inlineStr">
@@ -20843,7 +20827,7 @@
       </c>
       <c r="T181" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
@@ -20854,17 +20838,129 @@
       <c r="V181" s="11" t="inlineStr"/>
       <c r="W181" s="8" t="inlineStr">
         <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X181" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M182" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R182" s="4" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S182" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T182" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U182" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V182" s="4" t="inlineStr"/>
+      <c r="W182" s="8" t="inlineStr">
+        <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X181" s="7" t="inlineStr">
+      <c r="X182" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X181"/>
+  <autoFilter ref="A1:X182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22630,7 +22726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25164,7 +25260,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25172,79 +25268,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25257,15 +25333,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W23" s="15" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25280,13 +25356,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>Shukriyeva Nariye</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -25296,68 +25376,72 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
@@ -25365,14 +25449,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
+      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -25392,92 +25472,84 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25485,10 +25557,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25508,7 +25584,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -25518,74 +25594,82 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25594,9 +25678,9 @@
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25616,7 +25700,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25626,7 +25710,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -25636,69 +25720,69 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="inlineStr"/>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr"/>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>Tosheva Aziza Sherzod qizi</t>
+        </is>
+      </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
@@ -25724,13 +25808,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25740,37 +25828,37 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -25778,24 +25866,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
-        </is>
-      </c>
+      <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -25808,15 +25888,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -25836,17 +25916,13 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -25856,62 +25932,62 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -25952,7 +26028,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Umarova Iroda</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -25962,7 +26038,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -25972,37 +26048,37 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -26012,22 +26088,22 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26045,11 +26121,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26072,7 +26144,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26082,85 +26154,97 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q31" s="11" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V31" s="11" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -26180,7 +26264,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26190,93 +26274,85 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Xurramova Shodiya Arol qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26296,113 +26372,229 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
+          <t>Xurramova Shodiya</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Arol qizi</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>AC1967100</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>62704025590042</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>12.06.2019</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>27.04.2002</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S33" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Xusan qizi</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>09.04.2018</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>22.07.1993</t>
         </is>
       </c>
-      <c r="N33" s="12" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="P33" s="9" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="S33" s="12" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T33" s="12" t="inlineStr">
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="U33" s="7" t="inlineStr">
+      <c r="U34" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V33" s="11" t="inlineStr"/>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X33" s="7" t="inlineStr">
+      <c r="X34" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -5786,7 +5786,11 @@
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr"/>
-      <c r="R46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
@@ -23837,7 +23841,11 @@
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X182"/>
+  <dimension ref="A1:X183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13928,109 +13928,97 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr"/>
+          <t>Samatova Oydin</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O120" s="4" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr"/>
       <c r="R120" s="4" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S120" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T120" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U120" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="inlineStr"/>
-      <c r="W120" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X120" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U120" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V120" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W120" s="15" t="inlineStr"/>
+      <c r="X120" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -14045,82 +14033,78 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Samiyeva Sevinchbonu</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr"/>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P121" s="9" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q121" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R121" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S121" s="12" t="inlineStr">
@@ -14139,9 +14123,9 @@
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr"/>
-      <c r="W121" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X121" s="7" t="inlineStr">
@@ -14161,53 +14145,57 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr"/>
+          <t>Sanaqulova Muxtarama</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
@@ -14217,33 +14205,37 @@
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S122" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T122" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U122" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U122" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V122" s="4" t="inlineStr"/>
@@ -14264,62 +14256,58 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr"/>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N123" s="12" t="inlineStr">
@@ -14329,32 +14317,28 @@
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P123" s="9" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q123" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>K 5509185</t>
+        </is>
+      </c>
+      <c r="Q123" s="11" t="inlineStr"/>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S123" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T123" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -14362,14 +14346,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V123" s="11" t="inlineStr">
-        <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W123" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V123" s="11" t="inlineStr"/>
+      <c r="W123" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X123" s="7" t="inlineStr">
@@ -14384,12 +14364,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -14397,41 +14377,49 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N124" s="5" t="inlineStr">
@@ -14441,37 +14429,49 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>K 4587984</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S124" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U124" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X124" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sayfieva Sarvinoz</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
@@ -14497,101 +14497,81 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+      <c r="E125" s="12" t="inlineStr"/>
+      <c r="F125" s="12" t="inlineStr"/>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P125" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q125" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q125" s="11" t="inlineStr"/>
       <c r="R125" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S125" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T125" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V125" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W125" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U125" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V125" s="11" t="inlineStr"/>
+      <c r="W125" s="15" t="inlineStr"/>
       <c r="X125" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -14604,83 +14584,87 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr"/>
+          <t>Sayfillayeva Shodiyona</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Axmad qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>AD7984192</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>61007085590081</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>23.07.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Sayfiyeva Zarina Axmad qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>UM 03751932</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S126" s="5" t="inlineStr">
@@ -14698,10 +14682,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V126" s="4" t="inlineStr"/>
-      <c r="W126" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V126" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W126" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X126" s="7" t="inlineStr">
@@ -14721,78 +14709,78 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z</t>
+          <t>Sayfiyeva Zarina</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr"/>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Qahramon qizi</t>
+          <t>Axmad qizi</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>AE6071273</t>
+          <t>AD7984192</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>62708095680047</t>
+          <t>61007085590081</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>27.01.2026</t>
+          <t>23.07.2024</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>27.08.2009</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>Sayidova Dilafro'z Qahramon qizi</t>
+          <t>Sayfiyeva Zarina Axmad qizi</t>
         </is>
       </c>
       <c r="P127" s="9" t="inlineStr">
         <is>
-          <t>UM 03729168</t>
+          <t>UM 03751932</t>
         </is>
       </c>
       <c r="Q127" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832608/3447191/76c097af-86b5-43c8-a92d-2811565e56f3?preview=true</t>
         </is>
       </c>
       <c r="R127" s="11" t="inlineStr">
         <is>
-          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S127" s="12" t="inlineStr">
@@ -14833,82 +14821,78 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Sayidova Dilafro'z</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Qahramon qizi</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>AE2370999</t>
+          <t>AE6071273</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>60307085730074</t>
+          <t>62708095680047</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>03.07.2008</t>
+          <t>27.08.2009</t>
         </is>
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Sayidova Dilafro'z Qahramon qizi</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>UM 03758004</t>
+          <t>UM 03729168</t>
         </is>
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3743118/3827061/8d968761-cded-44aa-a481-f5732e7b775c?preview=true</t>
         </is>
       </c>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>38-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S128" s="5" t="inlineStr">
@@ -14944,12 +14928,12 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora</t>
+          <t>Shamsiyeva Fotima</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
@@ -14959,7 +14943,7 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
@@ -14969,62 +14953,62 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>AE5776687</t>
+          <t>AE2370999</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>62307095590022</t>
+          <t>60307085730074</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>23.07.2009</t>
+          <t>03.07.2008</t>
         </is>
       </c>
       <c r="N129" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>Sharipova Diyora Jasur qizi</t>
+          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P129" s="9" t="inlineStr">
         <is>
-          <t>UM 03751494</t>
+          <t>UM 03758004</t>
         </is>
       </c>
       <c r="Q129" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845467/3883533/77671008-6a79-4442-bbd3-dc2cfb091ca8?preview=true</t>
         </is>
       </c>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S129" s="12" t="inlineStr">
@@ -15060,12 +15044,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Sharipova Diyora</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -15073,59 +15057,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr"/>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE5776687</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62307095590022</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>23.07.2009</t>
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>Sharipova Diyora Jasur qizi</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr"/>
+          <t>UM 03751494</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3502177/4121891/1e7dac98-a929-407e-b29d-2cbeafd050e7?preview=true</t>
+        </is>
+      </c>
       <c r="R130" s="4" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S130" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T130" s="5" t="inlineStr">
@@ -15138,15 +15142,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V130" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W130" s="15" t="inlineStr"/>
-      <c r="X130" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V130" s="4" t="inlineStr"/>
+      <c r="W130" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X130" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15165,7 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -15169,79 +15173,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E131" s="12" t="inlineStr"/>
+      <c r="F131" s="12" t="inlineStr"/>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N131" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O131" s="11" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
       <c r="P131" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q131" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q131" s="11" t="inlineStr"/>
       <c r="R131" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S131" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T131" s="12" t="inlineStr">
@@ -15254,15 +15238,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V131" s="11" t="inlineStr"/>
-      <c r="W131" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X131" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V131" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W131" s="15" t="inlineStr"/>
+      <c r="X131" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -15272,12 +15256,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -15287,7 +15271,7 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -15297,37 +15281,37 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Farxod qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farxod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>AE1059205</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>60610085590150</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>06.10.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
@@ -15337,23 +15321,27 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Shukurova Zilola Farhod qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>PT 0339050</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr">
@@ -15384,12 +15372,12 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Soyipova Dinora</t>
+          <t>Shukurova Zilola</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -15399,43 +15387,47 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Sanjar qizi</t>
+          <t>Farxod qizi</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Soyipova Dinora Sanjar qizi</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr"/>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farxod qizi</t>
+        </is>
+      </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>AD9484395</t>
+          <t>AE1059205</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>62208085590065</t>
+          <t>60610085590150</t>
         </is>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>22.08.2008</t>
+          <t>06.10.2008</t>
         </is>
       </c>
       <c r="N133" s="12" t="inlineStr">
@@ -15443,41 +15435,41 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O133" s="11" t="inlineStr"/>
+      <c r="O133" s="11" t="inlineStr">
+        <is>
+          <t>Shukurova Zilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="P133" s="9" t="inlineStr">
         <is>
-          <t>UM03297405</t>
+          <t>PT 0339050</t>
         </is>
       </c>
       <c r="Q133" s="11" t="inlineStr"/>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>22-maktab</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S133" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T133" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U133" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
-        </is>
-      </c>
-      <c r="V133" s="11" t="inlineStr">
-        <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W133" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U133" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V133" s="11" t="inlineStr"/>
+      <c r="W133" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X133" s="7" t="inlineStr">
@@ -15497,51 +15489,53 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Suyarova Dinora</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr"/>
+          <t>Soyipova Dinora</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="n">
-        <v>46280</v>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Sodiq qizi</t>
+          <t>Sanjar qizi</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+          <t>Soyipova Dinora Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>AD9863476</t>
+          <t>AD9484395</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>60108085590037</t>
+          <t>62208085590065</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>18.12.2024</t>
+          <t>20.11.2024</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>01.08.2008</t>
+          <t>22.08.2008</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
@@ -15549,20 +15543,16 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O134" s="4" t="inlineStr">
-        <is>
-          <t>Suyarova Dinora Sodiq qizi</t>
-        </is>
-      </c>
+      <c r="O134" s="4" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>UM 03755218</t>
+          <t>UM03297405</t>
         </is>
       </c>
       <c r="Q134" s="4" t="inlineStr"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>22-maktab</t>
         </is>
       </c>
       <c r="S134" s="5" t="inlineStr">
@@ -15570,22 +15560,24 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T134" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U134" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="T134" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U134" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
-        </is>
-      </c>
-      <c r="W134" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 125) dan shartnoma №288 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W134" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X134" s="7" t="inlineStr">
@@ -15600,90 +15592,86 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
+          <t>Suyarova Dinora</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="n">
+        <v>46280</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Sodiq qizi</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD9863476</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>60108085590037</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>18.12.2024</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>01.08.2008</t>
         </is>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Suyarova Dinora Sodiq qizi</t>
         </is>
       </c>
       <c r="P135" s="9" t="inlineStr">
         <is>
-          <t>K 5491697</t>
+          <t>UM 03755218</t>
         </is>
       </c>
       <c r="Q135" s="11" t="inlineStr"/>
       <c r="R135" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>56-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S135" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T135" s="12" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T135" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
@@ -15692,12 +15680,12 @@
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+          <t>KARANTIN: ❌ Bir xil PINFL (60108085590037) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Pasport (AD9863476) 2 ta talabada: Rustamova Charos [26-03], Suyarova Dinora [26-04]; ❌ Bir xil Shahodatnoma (UM 03755218) 2 ta talabada: Rus | Operator: begona xujjat ma'lumotlari kerak emas || HAL QILINDI 20.09.2026: takror PINFL sababi — 309/311 fayllari nusxa edi; asl egalarining qatorlari tozalandi.</t>
         </is>
       </c>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X135" s="7" t="inlineStr">
@@ -15712,22 +15700,18 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -15737,72 +15721,68 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>AD6024952</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>60112075590084</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>05.02.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>01.12.2007</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>UM 03296212</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr"/>
       <c r="R136" s="4" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S136" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T136" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U136" s="7" t="inlineStr">
@@ -15810,10 +15790,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V136" s="4" t="inlineStr"/>
+      <c r="V136" s="4" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X136" s="7" t="inlineStr">
@@ -15828,12 +15812,12 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Temirova Rushana</t>
+          <t>Temirboyeva Iroda</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -15843,43 +15827,47 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Sarvarovna</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Temirova Rushana Sarvarovna</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr"/>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
+        </is>
+      </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>AD9123776</t>
+          <t>AD6024952</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>60709085590113</t>
+          <t>60112075590084</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>23.10.2024</t>
+          <t>05.02.2024</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>07.09.2008</t>
+          <t>01.12.2007</t>
         </is>
       </c>
       <c r="N137" s="12" t="inlineStr">
@@ -15889,18 +15877,22 @@
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Temirboyeva Iroda Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr">
         <is>
-          <t>UM 03755349</t>
-        </is>
-      </c>
-      <c r="Q137" s="11" t="inlineStr"/>
+          <t>UM 03296212</t>
+        </is>
+      </c>
+      <c r="Q137" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973552/2554812/7f935a7a-8206-4976-970f-b2b0bfec833a?preview=true</t>
+        </is>
+      </c>
       <c r="R137" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S137" s="12" t="inlineStr">
@@ -15910,18 +15902,18 @@
       </c>
       <c r="T137" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U137" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U137" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr"/>
-      <c r="W137" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W137" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X137" s="7" t="inlineStr">
@@ -15936,12 +15928,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Temirova Rushana</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15951,47 +15943,43 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-10 00:00:00</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sarvarovna</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
-        </is>
-      </c>
+          <t>Temirova Rushana Sarvarovna</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr"/>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD9123776</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>60709085590113</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>23.10.2024</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>07.09.2008</t>
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr">
@@ -16001,22 +15989,18 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03755349</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati, Shahrisabz tumani 61-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S138" s="5" t="inlineStr">
@@ -16029,15 +16013,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U138" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U138" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V138" s="4" t="inlineStr"/>
-      <c r="W138" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W138" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X138" s="7" t="inlineStr">
@@ -16057,7 +16041,7 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -16067,74 +16051,82 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N139" s="12" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q139" s="11" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q139" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R139" s="11" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S139" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T139" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -16143,9 +16135,9 @@
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr"/>
-      <c r="W139" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W139" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X139" s="7" t="inlineStr">
@@ -16160,12 +16152,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -16175,7 +16167,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -16185,68 +16177,64 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Ilxom qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>AD0914473</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>62803055590089</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>14.12.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>28.03.2005</t>
-        </is>
-      </c>
-      <c r="N140" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Toshmurodova Sarvara Ilxom qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>UM 1319051</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q140" s="4" t="inlineStr"/>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S140" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T140" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
@@ -16272,12 +16260,12 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila</t>
+          <t>Toshmurodova Sarvara</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -16287,7 +16275,7 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -16297,37 +16285,37 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ilxom qizi</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>AE3444231</t>
+          <t>AD0914473</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>61709085590015</t>
+          <t>62803055590089</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>18.07.2025</t>
+          <t>14.12.2021</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>17.09.2008</t>
+          <t>28.03.2005</t>
         </is>
       </c>
       <c r="N141" s="12" t="inlineStr">
@@ -16337,22 +16325,18 @@
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>Toshpo'latova Asila Akmal qizi</t>
+          <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
       <c r="P141" s="9" t="inlineStr">
         <is>
-          <t>UM 03754061</t>
-        </is>
-      </c>
-      <c r="Q141" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1319051</t>
+        </is>
+      </c>
+      <c r="Q141" s="11" t="inlineStr"/>
       <c r="R141" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
       <c r="S141" s="12" t="inlineStr">
@@ -16362,7 +16346,7 @@
       </c>
       <c r="T141" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -16373,7 +16357,7 @@
       <c r="V141" s="11" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X141" s="7" t="inlineStr">
@@ -16388,12 +16372,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Toshpo'latova Asila</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -16403,7 +16387,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -16413,54 +16397,62 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Toshpo'latova Asila Akmal qizi</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE3444231</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>61709085590015</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>18.07.2025</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>17.09.2008</t>
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>Toshpo'latova Asila Akmal qizi</t>
+        </is>
+      </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr"/>
+          <t>UM 03754061</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751197/3334326/3e3c9f4c-9b94-4ee1-9e1c-98c316a7d2dc?preview=true</t>
+        </is>
+      </c>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S142" s="5" t="inlineStr">
@@ -16473,15 +16465,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U142" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U142" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X142" s="7" t="inlineStr">
@@ -16496,83 +16488,79 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Oybek qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>AE5053541</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>61205095590053</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>12.05.2009</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N143" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O143" s="11" t="inlineStr">
-        <is>
-          <t>Turayeva Dilsuz Oybek qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
       <c r="P143" s="9" t="inlineStr">
         <is>
-          <t>UM 03751635</t>
-        </is>
-      </c>
-      <c r="Q143" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q143" s="11" t="inlineStr"/>
       <c r="R143" s="11" t="inlineStr">
         <is>
-          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S143" s="12" t="inlineStr">
@@ -16585,15 +16573,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U143" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X143" s="7" t="inlineStr">
@@ -16608,62 +16596,58 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Turayeva Dilsuz</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Oybek qizi</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE5053541</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>61205095590053</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>12.05.2009</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
@@ -16673,22 +16657,22 @@
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Turayeva Dilsuz Oybek qizi</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03751635</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4361470/3974374/48b26608-a18d-46a4-ac19-cba528a20b3b?preview=true</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>2-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S144" s="5" t="inlineStr">
@@ -16698,7 +16682,7 @@
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U144" s="7" t="inlineStr">
@@ -16724,12 +16708,12 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina</t>
+          <t>Turayeva Gulasal</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
@@ -16739,7 +16723,7 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -16749,37 +16733,37 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>AE6171425</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>62802085590087</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N145" s="12" t="inlineStr">
@@ -16789,39 +16773,43 @@
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>Turg'unova Jasmina Turg'un qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P145" s="9" t="inlineStr">
         <is>
-          <t>PT 0339231</t>
-        </is>
-      </c>
-      <c r="Q145" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-sonli politexnikum</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S145" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T145" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U145" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U145" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X145" s="7" t="inlineStr">
@@ -16836,18 +16824,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr"/>
+          <t>Turg'unova Jasmina</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -16857,67 +16849,63 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE6171425</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>62802085590087</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Turg'unova Jasmina Turg'un qizi</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339231</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr"/>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-sonli politexnikum</t>
         </is>
       </c>
       <c r="S146" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T146" s="5" t="inlineStr">
@@ -16925,15 +16913,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U146" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U146" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V146" s="4" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X146" s="7" t="inlineStr">
@@ -16948,87 +16936,83 @@
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr"/>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Anvarovna</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>AD6026687</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>61407075590019</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>06.02.2024</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>14.07.2007</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Aziza Anvarovna</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P147" s="9" t="inlineStr">
         <is>
-          <t>UM 02172465</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q147" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R147" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S147" s="12" t="inlineStr">
@@ -17038,7 +17022,7 @@
       </c>
       <c r="T147" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -17049,7 +17033,7 @@
       <c r="V147" s="11" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X147" s="7" t="inlineStr">
@@ -17069,78 +17053,82 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>Tursunova Aziza</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Qosim qizi</t>
+          <t>Anvarovna</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>AE5949204</t>
+          <t>AD6026687</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>62710085680012</t>
+          <t>61407075590019</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>06.02.2024</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>27.10.2008</t>
+          <t>14.07.2007</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
+          <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>UM 03730083</t>
+          <t>UM 02172465</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1665797/1529886/6a8bd5b3-4f70-483d-dc25-08dc8cc4bb61?preview=true</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S148" s="5" t="inlineStr">
@@ -17150,7 +17138,7 @@
       </c>
       <c r="T148" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U148" s="7" t="inlineStr">
@@ -17161,7 +17149,7 @@
       <c r="V148" s="4" t="inlineStr"/>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X148" s="7" t="inlineStr">
@@ -17181,13 +17169,13 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra</t>
+          <t>Tursunova Fotima</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr"/>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -17202,22 +17190,22 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>AE5949016</t>
+          <t>AE5949204</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>62710085680029</t>
+          <t>62710085680012</t>
         </is>
       </c>
       <c r="L149" s="12" t="inlineStr">
@@ -17237,17 +17225,17 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="P149" s="9" t="inlineStr">
         <is>
-          <t>UM 03730084</t>
+          <t>UM 03730083</t>
         </is>
       </c>
       <c r="Q149" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927356/3458091/7a5c850f-479b-4395-8dfd-9cb850430169?preview=true</t>
         </is>
       </c>
       <c r="R149" s="11" t="inlineStr">
@@ -17288,56 +17276,58 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona</t>
+          <t>Tursunova Zuhra</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F150" s="6" t="n">
-        <v>46272</v>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Dalerovna</t>
+          <t>Qosim qizi</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE5949016</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>62710085680029</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>27.10.2008</t>
         </is>
       </c>
       <c r="N150" s="5" t="inlineStr">
@@ -17347,22 +17337,22 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>UM-O 00064269</t>
+          <t>UM 03730084</t>
         </is>
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927355/3457908/4a18ffb4-013a-4ab0-ac14-264fcc939f2f?preview=true</t>
         </is>
       </c>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S150" s="5" t="inlineStr">
@@ -17380,11 +17370,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V150" s="4" t="inlineStr">
-        <is>
-          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
-        </is>
-      </c>
+      <c r="V150" s="4" t="inlineStr"/>
       <c r="W150" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -17407,70 +17393,76 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tuychiyeva Farzona</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr"/>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="n">
+        <v>46272</v>
+      </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Dalerovna</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr"/>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>05.08.2009</t>
         </is>
       </c>
       <c r="N151" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Tuychiyeva Farzona Dalerovna</t>
         </is>
       </c>
       <c r="P151" s="9" t="inlineStr">
         <is>
-          <t>UM 03728161</t>
-        </is>
-      </c>
-      <c r="Q151" s="11" t="inlineStr"/>
+          <t>UM-O 00064269</t>
+        </is>
+      </c>
+      <c r="Q151" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+        </is>
+      </c>
       <c r="R151" s="11" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S151" s="12" t="inlineStr">
@@ -17480,12 +17472,24 @@
       </c>
       <c r="T151" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U151" s="12" t="inlineStr"/>
-      <c r="V151" s="11" t="inlineStr"/>
-      <c r="W151" s="15" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U151" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V151" s="11" t="inlineStr">
+        <is>
+          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
+        </is>
+      </c>
+      <c r="W151" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X151" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17498,12 +17502,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Ulugbekova Zara</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -17513,47 +17517,39 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr"/>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
-        </is>
-      </c>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.09.2008</t>
         </is>
       </c>
       <c r="N152" s="5" t="inlineStr">
@@ -17563,22 +17559,18 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728161</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr"/>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S152" s="5" t="inlineStr">
@@ -17588,20 +17580,12 @@
       </c>
       <c r="T152" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U152" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U152" s="5" t="inlineStr"/>
       <c r="V152" s="4" t="inlineStr"/>
-      <c r="W152" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W152" s="15" t="inlineStr"/>
       <c r="X152" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -17614,98 +17598,108 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="F153" s="18" t="n">
-        <v>46275</v>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Avlayor qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Umirova Sevinch Avlayor qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>AD1671106</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>60906055720101</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>18.08.2022</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>09.06.2005</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O153" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr">
+        <is>
+          <t>Umarova Iroda Muzaffar qizi</t>
+        </is>
+      </c>
       <c r="P153" s="9" t="inlineStr">
         <is>
-          <t>UM 01891594</t>
-        </is>
-      </c>
-      <c r="Q153" s="11" t="inlineStr"/>
+          <t>UM 03754201</t>
+        </is>
+      </c>
+      <c r="Q153" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+        </is>
+      </c>
       <c r="R153" s="11" t="inlineStr">
         <is>
-          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S153" s="12" t="inlineStr">
         <is>
-          <t>ID-karta</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T153" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U153" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V153" s="11" t="inlineStr">
-        <is>
-          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U153" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V153" s="11" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X153" s="7" t="inlineStr">
@@ -17720,112 +17714,98 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Umirova Sevinch</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>46275</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Avlayor qizi</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AD1671106</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60906055720101</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>18.08.2022</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>09.06.2005</t>
         </is>
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 01891594</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr"/>
       <c r="R154" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>42-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S154" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>ID-karta</t>
         </is>
       </c>
       <c r="T154" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U154" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U154" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V154" s="4" t="inlineStr">
         <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+          <t>Pasportning orqa tomoni yo'q (JSHSHIR ko'rinmagan)</t>
         </is>
       </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X154" s="7" t="inlineStr">
@@ -17845,7 +17825,7 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
@@ -17855,85 +17835,97 @@
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O155" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P155" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q155" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R155" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S155" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T155" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U155" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V155" s="11" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U155" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V155" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X155" s="7" t="inlineStr">
@@ -17948,56 +17940,62 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>Usmanova Iroda</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F156" s="6" t="n">
-        <v>46272</v>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:00:00</t>
+        </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Xamdam qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N156" s="5" t="inlineStr">
@@ -18005,20 +18003,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O156" s="4" t="inlineStr">
-        <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
-        </is>
-      </c>
+      <c r="O156" s="4" t="inlineStr"/>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>K 1994177</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr">
         <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S156" s="5" t="inlineStr">
@@ -18028,22 +18022,18 @@
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U156" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U156" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V156" s="4" t="inlineStr"/>
       <c r="W156" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X156" s="7" t="inlineStr">
@@ -18058,97 +18048,87 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="F157" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="n">
+        <v>46272</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>AE4384190</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>61810085590061</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>26.01.1992</t>
         </is>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Sabrina Baxtiyor qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="P157" s="9" t="inlineStr">
         <is>
-          <t>UM 03754097</t>
-        </is>
-      </c>
-      <c r="Q157" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
-        </is>
-      </c>
+          <t>K 1994177</t>
+        </is>
+      </c>
+      <c r="Q157" s="11" t="inlineStr"/>
       <c r="R157" s="11" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T157" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -18156,7 +18136,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V157" s="11" t="inlineStr"/>
+      <c r="V157" s="11" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
       <c r="W157" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -18174,18 +18158,22 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr"/>
+          <t>Usmonova Sabrina</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -18195,62 +18183,62 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Nu'mon qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>AD9589389</t>
+          <t>AE4384190</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>62112075680077</t>
+          <t>61810085590061</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>21.12.2007</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Yulduz Nu'mon qizi</t>
+          <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>UM 03273678</t>
+          <t>UM 03754097</t>
         </is>
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751235/3336638/25861597-706d-4722-a5f4-6d0442b1dea6?preview=true</t>
         </is>
       </c>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S158" s="5" t="inlineStr">
@@ -18260,7 +18248,7 @@
       </c>
       <c r="T158" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U158" s="7" t="inlineStr">
@@ -18286,71 +18274,83 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr"/>
-      <c r="F159" s="12" t="inlineStr"/>
+          <t>Usmonova Yulduz</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr"/>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Nu'mon qizi</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9589389</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>62112075680077</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>21.12.2007</t>
         </is>
       </c>
       <c r="N159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O159" s="11" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr">
+        <is>
+          <t>Usmonova Yulduz Nu'mon qizi</t>
+        </is>
+      </c>
       <c r="P159" s="9" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
-        </is>
-      </c>
-      <c r="Q159" s="11" t="inlineStr"/>
+          <t>UM 03273678</t>
+        </is>
+      </c>
+      <c r="Q159" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2510609/2335994/5d45b8e4-a117-4e26-ab03-12eb3391bac3?preview=true</t>
+        </is>
+      </c>
       <c r="R159" s="11" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S159" s="12" t="inlineStr">
@@ -18360,16 +18360,20 @@
       </c>
       <c r="T159" s="12" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U159" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U159" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr"/>
-      <c r="W159" s="15" t="inlineStr"/>
+      <c r="W159" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X159" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18382,12 +18386,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Xamdamova Madina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -18395,96 +18399,77 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="n">
-        <v>46197</v>
-      </c>
+      <c r="E160" s="5" t="inlineStr"/>
+      <c r="F160" s="5" t="inlineStr"/>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Abdiqodir qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>07.12.1990</t>
         </is>
       </c>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O160" s="4" t="inlineStr">
-        <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>K 5487959</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q160" s="4" t="inlineStr"/>
       <c r="R160" s="4" t="inlineStr">
         <is>
-          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S160" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U160" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="inlineStr">
-        <is>
-          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
-to'g'risi: 62701015680026</t>
-        </is>
-      </c>
-      <c r="W160" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U160" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V160" s="4" t="inlineStr"/>
+      <c r="W160" s="15" t="inlineStr"/>
       <c r="X160" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -18502,51 +18487,55 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr"/>
+          <t>Xamdamova Madina</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F161" s="18" t="n">
-        <v>46247</v>
+        <v>46197</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Abdiqodir qizi</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>27.01.2001</t>
         </is>
       </c>
       <c r="N161" s="12" t="inlineStr">
@@ -18554,33 +18543,46 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O161" s="11" t="inlineStr"/>
+      <c r="O161" s="11" t="inlineStr">
+        <is>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
       <c r="P161" s="9" t="inlineStr">
         <is>
-          <t>UM 0862565</t>
+          <t>K 5487959</t>
         </is>
       </c>
       <c r="Q161" s="11" t="inlineStr"/>
       <c r="R161" s="11" t="inlineStr">
         <is>
-          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
-        </is>
-      </c>
-      <c r="S161" s="12" t="inlineStr"/>
+          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S161" s="12" t="inlineStr">
+        <is>
+          <t>Diplom</t>
+        </is>
+      </c>
       <c r="T161" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U161" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V161" s="11" t="inlineStr"/>
-      <c r="W161" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U161" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V161" s="11" t="inlineStr">
+        <is>
+          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
+to'g'risi: 62701015680026</t>
+        </is>
+      </c>
+      <c r="W161" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X161" s="7" t="inlineStr">
@@ -18595,108 +18597,90 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xannonova Shohsanam</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>46247</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Zarif qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>AE4240266</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>61906085590032</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>02.06.2004</t>
         </is>
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O162" s="4" t="inlineStr">
-        <is>
-          <t>Xaydarova Iroda Zarif qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O162" s="4" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>UM 03754068</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0862565</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr"/>
       <c r="R162" s="4" t="inlineStr">
         <is>
-          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S162" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr"/>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U162" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U162" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V162" s="4" t="inlineStr"/>
-      <c r="W162" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W162" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X162" s="7" t="inlineStr">
@@ -18716,7 +18700,7 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
+          <t>Xaydarova Iroda</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
@@ -18726,7 +18710,7 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -18736,37 +18720,37 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Zarif qizi</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AE4240266</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>61906085590032</t>
         </is>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N163" s="12" t="inlineStr">
@@ -18776,23 +18760,27 @@
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
+          <t>Xaydarova Iroda Zarif qizi</t>
         </is>
       </c>
       <c r="P163" s="9" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
-        </is>
-      </c>
-      <c r="Q163" s="11" t="inlineStr"/>
+          <t>UM 03754068</t>
+        </is>
+      </c>
+      <c r="Q163" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3751211/3334984/ed85efd3-f963-438f-9075-a2496493f195?preview=true</t>
+        </is>
+      </c>
       <c r="R163" s="11" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S163" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T163" s="12" t="inlineStr">
@@ -18806,9 +18794,9 @@
         </is>
       </c>
       <c r="V163" s="11" t="inlineStr"/>
-      <c r="W163" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W163" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X163" s="7" t="inlineStr">
@@ -18823,12 +18811,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
+          <t>Xayrullayeva Umida</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -18838,91 +18826,89 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xayrullayeva Umida Safar qizi</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
+          <t>PT 0025701</t>
         </is>
       </c>
       <c r="Q164" s="4" t="inlineStr"/>
       <c r="R164" s="4" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S164" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T164" s="5" t="n">
-        <v>2019</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U164" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V164" s="4" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W164" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V164" s="4" t="inlineStr"/>
+      <c r="W164" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X164" s="7" t="inlineStr">
@@ -18937,83 +18923,83 @@
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N165" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="P165" s="9" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q165" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0086260</t>
+        </is>
+      </c>
+      <c r="Q165" s="11" t="inlineStr"/>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S165" s="12" t="inlineStr">
@@ -19021,10 +19007,8 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T165" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="T165" s="12" t="n">
+        <v>2019</v>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
@@ -19033,7 +19017,7 @@
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W165" s="8" t="inlineStr">
@@ -19058,17 +19042,13 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -19078,62 +19058,62 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q166" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R166" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S166" s="5" t="inlineStr">
@@ -19151,7 +19131,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V166" s="4" t="inlineStr"/>
+      <c r="V166" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W166" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -19169,12 +19153,12 @@
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
@@ -19184,7 +19168,7 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -19194,37 +19178,37 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N167" s="12" t="inlineStr">
@@ -19234,28 +19218,32 @@
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P167" s="9" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q167" s="11" t="inlineStr"/>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="Q167" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+        </is>
+      </c>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S167" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T167" s="12" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
@@ -19263,14 +19251,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V167" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W167" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V167" s="11" t="inlineStr"/>
+      <c r="W167" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X167" s="7" t="inlineStr">
@@ -19285,12 +19269,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -19300,81 +19284,79 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>K 3418837</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr"/>
       <c r="R168" s="4" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S168" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T168" s="5" t="n">
-        <v>2026</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T168" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="U168" s="7" t="inlineStr">
         <is>
@@ -19383,12 +19365,12 @@
       </c>
       <c r="V168" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W168" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W168" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X168" s="7" t="inlineStr">
@@ -19403,12 +19385,12 @@
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
@@ -19418,47 +19400,47 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N169" s="12" t="inlineStr">
@@ -19468,18 +19450,22 @@
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q169" s="11" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q169" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S169" s="12" t="inlineStr">
@@ -19487,20 +19473,22 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T169" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="T169" s="12" t="n">
+        <v>2026</v>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V169" s="11" t="inlineStr"/>
+      <c r="V169" s="11" t="inlineStr">
+        <is>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W169" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X169" s="7" t="inlineStr">
@@ -19515,12 +19503,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
+          <t>Xolmurodova Sabina</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -19530,60 +19518,68 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="Q170" s="4" t="inlineStr"/>
       <c r="R170" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S170" s="5" t="inlineStr">
@@ -19596,9 +19592,17 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U170" s="5" t="inlineStr"/>
+      <c r="U170" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V170" s="4" t="inlineStr"/>
-      <c r="W170" s="15" t="inlineStr"/>
+      <c r="W170" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X170" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19611,12 +19615,12 @@
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
+          <t>Xujamuratova Durdona</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
@@ -19626,72 +19630,60 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr"/>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
-      <c r="I171" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr"/>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N171" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P171" s="9" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
-        </is>
-      </c>
-      <c r="Q171" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03717652</t>
+        </is>
+      </c>
+      <c r="Q171" s="11" t="inlineStr"/>
       <c r="R171" s="11" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S171" s="12" t="inlineStr">
@@ -19701,20 +19693,12 @@
       </c>
       <c r="T171" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U171" s="12" t="inlineStr"/>
       <c r="V171" s="11" t="inlineStr"/>
-      <c r="W171" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W171" s="15" t="inlineStr"/>
       <c r="X171" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19732,7 +19716,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Sabina</t>
+          <t>Xurramova Lobar</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -19742,56 +19726,72 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="inlineStr"/>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Yuldosh qizi</t>
+          <t>Ural qizi</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr"/>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
-        </is>
-      </c>
-      <c r="N172" s="5" t="inlineStr"/>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>UM 1315230</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="inlineStr"/>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
       <c r="R172" s="4" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S172" s="5" t="inlineStr">
@@ -19801,12 +19801,20 @@
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U172" s="5" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U172" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="15" t="inlineStr"/>
+      <c r="W172" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X172" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19819,12 +19827,12 @@
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
@@ -19834,89 +19842,71 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F173" s="18" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr"/>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I173" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr"/>
       <c r="J173" s="12" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N173" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N173" s="12" t="inlineStr"/>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q173" s="11" t="inlineStr"/>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S173" s="12" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T173" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U173" s="12" t="inlineStr"/>
       <c r="V173" s="11" t="inlineStr"/>
-      <c r="W173" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W173" s="15" t="inlineStr"/>
       <c r="X173" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -19934,7 +19924,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -19944,13 +19934,11 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>46204</v>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
@@ -19959,32 +19947,32 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
@@ -19994,32 +19982,28 @@
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr"/>
       <c r="R174" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S174" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T174" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U174" s="7" t="inlineStr">
@@ -20045,12 +20029,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -20060,7 +20044,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -20070,58 +20054,62 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N175" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P175" s="9" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q175" s="11" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q175" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S175" s="12" t="inlineStr">
@@ -20131,7 +20119,7 @@
       </c>
       <c r="T175" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -20139,11 +20127,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V175" s="11" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V175" s="11" t="inlineStr"/>
       <c r="W175" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -20161,12 +20145,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -20176,7 +20160,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -20186,37 +20170,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
@@ -20226,22 +20210,18 @@
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="inlineStr"/>
       <c r="R176" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S176" s="5" t="inlineStr">
@@ -20251,7 +20231,7 @@
       </c>
       <c r="T176" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U176" s="7" t="inlineStr">
@@ -20261,12 +20241,12 @@
       </c>
       <c r="V176" s="4" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
         </is>
       </c>
       <c r="W176" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X176" s="7" t="inlineStr">
@@ -20281,18 +20261,22 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -20302,62 +20286,62 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N177" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P177" s="9" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q177" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R177" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S177" s="12" t="inlineStr">
@@ -20375,10 +20359,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V177" s="11" t="inlineStr"/>
+      <c r="V177" s="11" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W177" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X177" s="7" t="inlineStr">
@@ -20393,22 +20381,18 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -20418,37 +20402,37 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>22.07.1993</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N178" s="5" t="inlineStr">
@@ -20458,22 +20442,22 @@
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q178" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R178" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S178" s="5" t="inlineStr">
@@ -20483,7 +20467,7 @@
       </c>
       <c r="T178" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr">
@@ -20494,7 +20478,7 @@
       <c r="V178" s="4" t="inlineStr"/>
       <c r="W178" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X178" s="7" t="inlineStr">
@@ -20509,12 +20493,12 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
@@ -20524,7 +20508,7 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -20534,68 +20518,72 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
         <is>
-          <t>13.09.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N179" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P179" s="9" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
-        </is>
-      </c>
-      <c r="Q179" s="11" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q179" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R179" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S179" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T179" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
@@ -20603,14 +20591,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V179" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W179" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+      <c r="V179" s="11" t="inlineStr"/>
+      <c r="W179" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X179" s="7" t="inlineStr">
@@ -20625,12 +20609,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
+          <t>Yuldosheva Ruhshona</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -20640,7 +20624,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -20650,67 +20634,63 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N180" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>PT 0339260</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="inlineStr"/>
       <c r="R180" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S180" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T180" s="5" t="inlineStr">
@@ -20723,10 +20703,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V180" s="4" t="inlineStr"/>
-      <c r="W180" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V180" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W180" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X180" s="7" t="inlineStr">
@@ -20741,12 +20725,12 @@
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D181" s="11" t="inlineStr">
@@ -20756,7 +20740,7 @@
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -20766,37 +20750,37 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L181" s="12" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M181" s="12" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N181" s="12" t="inlineStr">
@@ -20806,22 +20790,22 @@
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="Q181" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
         </is>
       </c>
       <c r="R181" s="11" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S181" s="12" t="inlineStr">
@@ -20842,7 +20826,7 @@
       <c r="V181" s="11" t="inlineStr"/>
       <c r="W181" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X181" s="7" t="inlineStr">
@@ -20857,18 +20841,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
@@ -20878,62 +20866,62 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>12.06.2007</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N182" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q182" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R182" s="4" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S182" s="5" t="inlineStr">
@@ -20943,7 +20931,7 @@
       </c>
       <c r="T182" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U182" s="7" t="inlineStr">
@@ -20954,17 +20942,129 @@
       <c r="V182" s="4" t="inlineStr"/>
       <c r="W182" s="8" t="inlineStr">
         <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X182" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr"/>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H183" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J183" s="12" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K183" s="9" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L183" s="12" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M183" s="12" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N183" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O183" s="11" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P183" s="9" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q183" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R183" s="11" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S183" s="12" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T183" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U183" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V183" s="11" t="inlineStr"/>
+      <c r="W183" s="8" t="inlineStr">
+        <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X182" s="7" t="inlineStr">
+      <c r="X183" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X182"/>
+  <autoFilter ref="A1:X183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22730,7 +22830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25148,7 +25248,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Samatova Oydin</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -25158,82 +25258,66 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -25243,17 +25327,13 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W22" s="15" t="inlineStr"/>
+      <c r="X22" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25348,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25276,59 +25356,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25343,13 +25443,17 @@
       </c>
       <c r="V23" s="11" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W23" s="15" t="inlineStr"/>
-      <c r="X23" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25468,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -25372,79 +25476,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -25457,15 +25541,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W24" s="15" t="inlineStr"/>
+      <c r="X24" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25480,13 +25564,17 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr"/>
+          <t>Shukriyeva Nariye</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -25496,68 +25584,72 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25565,14 +25657,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
+      <c r="V25" s="11" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25592,92 +25680,84 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25685,10 +25765,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25708,7 +25792,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'raboyeva Sabrina</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25718,74 +25802,82 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr"/>
+          <t>27.09.2008</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>K 3736287</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -25794,9 +25886,9 @@
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -25816,7 +25908,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -25826,7 +25918,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25836,69 +25928,69 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr"/>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Tosheva Aziza Sherzod qizi</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
+          <t>K 3736287</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U28" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
@@ -25924,13 +26016,17 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr"/>
+          <t>To'xtayeva Durdona</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -25940,37 +26036,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>19.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -25978,24 +26074,16 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
-        <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
-        </is>
-      </c>
+      <c r="O29" s="11" t="inlineStr"/>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728346</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -26008,15 +26096,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+      <c r="U29" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -26036,17 +26124,13 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -26056,62 +26140,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03730110</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26152,7 +26236,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Umarova Iroda</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26162,7 +26246,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -26172,37 +26256,37 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -26212,22 +26296,22 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -26245,11 +26329,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+      <c r="V31" s="11" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26272,7 +26352,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26282,85 +26362,97 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Uroqova Jasmina Jasur qizi</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>K 4590366</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr"/>
+          <t>UM 03752857</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
+        </is>
+      </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U32" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26380,7 +26472,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -26390,93 +26482,85 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>Xurramova Shodiya Arol qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr"/>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
+          <t>K 4590366</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V33" s="11" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U33" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -26496,113 +26580,229 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>Xurramova Shodiya</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Arol qizi</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>AC1967100</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>62704025590042</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2019</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>27.04.2002</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>UM 0438281</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U34" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X34" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
           <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Xusan qizi</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>09.04.2018</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M35" s="12" t="inlineStr">
         <is>
           <t>22.07.1993</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P35" s="9" t="inlineStr">
         <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="Q35" s="11" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="R35" s="11" t="inlineStr">
         <is>
           <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="S35" s="12" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr">
+      <c r="T35" s="12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="U34" s="7" t="inlineStr">
+      <c r="U35" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="8" t="inlineStr">
+      <c r="V35" s="11" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr">
         <is>
           <t>Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X34" s="7" t="inlineStr">
+      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -22830,7 +22830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora</t>
+          <t>Islomova Nilufar</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -23896,37 +23896,49 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Shodmon qizi</t>
+          <t>Abdulxafiz qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Irgasheva Dinora Shodmon qizi</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AC 2430931</t>
+          <t>AD9664280</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60106035590029</t>
+          <t>61911085590104</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>15.11.2019</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>01.06.2003</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -23934,21 +23946,29 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Islomova Nilufar Abdulxafiz qizi</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 0441030</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr"/>
+          <t>UM 03752502</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3580119/3231058/665e452b-f84e-49a9-8c0a-114015a02ee9?preview=true</t>
+        </is>
+      </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>14-maktab</t>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
@@ -23961,15 +23981,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W10" s="15" t="inlineStr"/>
-      <c r="X10" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -23984,7 +24004,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Islomova Nilufar</t>
+          <t>Jalolova Rayxona</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -23994,72 +24014,72 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Abdulxafiz qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AD9664280</t>
+          <t>AE3492384</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>61911085590104</t>
+          <t>62207085680059</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>22.07.2008</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Islomova Nilufar Abdulxafiz qizi</t>
+          <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>UM 03752502</t>
+          <t>UM 03729365</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3580119/3231058/665e452b-f84e-49a9-8c0a-114015a02ee9?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4054768/3621740/e249f0ee-bae2-4fd1-b709-560d5089a083?preview=true</t>
         </is>
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -24078,9 +24098,9 @@
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="W11" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -24100,7 +24120,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona</t>
+          <t>Javliyeva Nargiza</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -24110,47 +24130,47 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Ortiq qizi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE3492384</t>
+          <t>AE5222372</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62207085680059</t>
+          <t>62401095680012</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>23.07.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>22.07.2008</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -24160,22 +24180,22 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Jalolova Rayxona Akmal qizi</t>
+          <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03729365</t>
+          <t>UM 03729316</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4054768/3621740/e249f0ee-bae2-4fd1-b709-560d5089a083?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4089340/3633473/dd6bd3e0-37a5-444d-8a53-a22ed29c5347?preview=true</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>47-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -24194,9 +24214,9 @@
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X12" s="7" t="inlineStr">
@@ -24216,7 +24236,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza</t>
+          <t>Maxmashoxova Feruza</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -24226,7 +24246,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -24236,62 +24256,62 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Ortiq qizi</t>
+          <t>Bekmurod qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>AE5222372</t>
+          <t>AE5088010</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>62401095680012</t>
+          <t>60201085630050</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>18.11.2025</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Javliyeva Nargiza Ortiq qizi</t>
+          <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>UM 03729316</t>
+          <t>UM 03742126</t>
         </is>
       </c>
       <c r="Q13" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4089340/3633473/dd6bd3e0-37a5-444d-8a53-a22ed29c5347?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801846/3533937/132e5ac9-15d4-4739-bdb7-4e20c5ce7245?preview=true</t>
         </is>
       </c>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
@@ -24312,7 +24332,7 @@
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X13" s="7" t="inlineStr">
@@ -24332,7 +24352,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza</t>
+          <t>Meyliqulova Hilola</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -24342,7 +24362,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -24352,72 +24372,68 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Bekmurod qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AE5088010</t>
+          <t>AB7137876</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60201085630050</t>
+          <t>61202005680055</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>07.07.2017</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>12.02.2000</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Maxmashoxova Feruza Bekmurod qizi</t>
+          <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>UM 03742126</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801846/3533937/132e5ac9-15d4-4739-bdb7-4e20c5ce7245?preview=true</t>
-        </is>
-      </c>
+          <t>K 5470992</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
@@ -24425,10 +24441,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Qo'lda tasdiqlandi: Meyliqulova Hilola Farhod qizi</t>
+        </is>
+      </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X14" s="7" t="inlineStr">
@@ -24448,7 +24468,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola</t>
+          <t>Nu'monova Saidabonu</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -24458,7 +24478,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -24468,68 +24488,72 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AB7137876</t>
+          <t>AE1067914</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>61202005680055</t>
+          <t>62410085590084</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>07.07.2017</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>12.02.2000</t>
+          <t>24.10.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Meyliqulova Hilola Farhod qizi</t>
+          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>K 5470992</t>
-        </is>
-      </c>
-      <c r="Q15" s="11" t="inlineStr"/>
+          <t>UM 03752610</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3982307/4146791/0ce0ca2c-2594-48a0-b1c4-8773beb807f7?preview=true</t>
+        </is>
+      </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
@@ -24537,14 +24561,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V15" s="11" t="inlineStr">
-        <is>
-          <t>Qo'lda tasdiqlandi: Meyliqulova Hilola Farhod qizi</t>
-        </is>
-      </c>
+      <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: TUTUQ BELGISI</t>
         </is>
       </c>
       <c r="X15" s="7" t="inlineStr">
@@ -24564,7 +24584,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu</t>
+          <t>Ochildiyeva Dinora</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -24574,7 +24594,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -24584,37 +24604,37 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Otabek qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AE1067914</t>
+          <t>AE4084333</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62410085590084</t>
+          <t>62012085590055</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>24.10.2008</t>
+          <t>20.12.2008</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -24624,22 +24644,22 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Nu'monova Saidabonu Ulug'bek qizi</t>
+          <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 03752610</t>
+          <t>UM 03754418</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3982307/4146791/0ce0ca2c-2594-48a0-b1c4-8773beb807f7?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3714426/3303458/d7200d74-420a-43ca-a745-51967def2eee?preview=true</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -24657,10 +24677,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: TUTUQ BELGISI</t>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'OCHILDIYEVA DINORA' | bazada: 'Ochildiyeva Dinara'; imlo farqi — Shahodatnoma PDF: 'Ochildiyeva Dinora Otabek qizi' | bazada: 'Ochildiyeva Dinara'</t>
+        </is>
+      </c>
+      <c r="W16" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X16" s="7" t="inlineStr">
@@ -24680,7 +24704,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora</t>
+          <t>Qulmatova Shabbona</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -24688,74 +24712,62 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+      <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Otabek qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
-        </is>
-      </c>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AE4084333</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>62012085590055</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>20.12.2008</t>
+          <t>10.08.2008</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Ochildiyeva Dinora Otabek qizi</t>
+          <t>Yo'q</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>UM 03754418</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3714426/3303458/d7200d74-420a-43ca-a745-51967def2eee?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730102</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -24773,19 +24785,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'OCHILDIYEVA DINORA' | bazada: 'Ochildiyeva Dinara'; imlo farqi — Shahodatnoma PDF: 'Ochildiyeva Dinora Otabek qizi' | bazada: 'Ochildiyeva Dinara'</t>
-        </is>
-      </c>
-      <c r="W17" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V17" s="11" t="inlineStr"/>
+      <c r="W17" s="15" t="inlineStr"/>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24804,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Quysinova Rohshona</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -24808,62 +24812,74 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Azamat qizi</t>
+          <t>To'lqin qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Yo'q</t>
+          <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03730102</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+          <t>UM 02138929</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>Ixtisoslashtirilgan maktabni</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -24873,7 +24889,7 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -24881,11 +24897,19 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="15" t="inlineStr"/>
-      <c r="X18" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
+        </is>
+      </c>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24900,17 +24924,13 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Ro'zimurodova Larisa</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -24920,62 +24940,62 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>To'lqin qizi</t>
+          <t>Ma'matali qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>16.08.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>UM 02138929</t>
+          <t>UM 03742132</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
         </is>
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>Ixtisoslashtirilgan maktabni</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -24985,7 +25005,7 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -24995,12 +25015,12 @@
       </c>
       <c r="V19" s="11" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
-        </is>
-      </c>
-      <c r="W19" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
+        </is>
+      </c>
+      <c r="W19" s="13" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -25020,13 +25040,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>Samadova Nigora</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -25036,62 +25060,58 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ma'matali qizi</t>
+          <t>Abdisamiyevna</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>07.10.1989</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03742132</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
-        </is>
-      </c>
+          <t>O'R-SH 0658073</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -25101,7 +25121,7 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -25109,14 +25129,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
-        </is>
-      </c>
-      <c r="W20" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: FARQ</t>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -25136,7 +25152,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Samadova Nigora</t>
+          <t>Samatova Oydin</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -25146,78 +25162,66 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr"/>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Abdisamiyevna</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
-        </is>
-      </c>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>O'R-SH 0658073</t>
+          <t>OR-SH 0346677</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -25225,15 +25229,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W21" s="15" t="inlineStr"/>
+      <c r="X21" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25248,7 +25252,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Samatova Oydin</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -25258,66 +25262,82 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sulaymon qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OR-SH 0346677</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -25327,13 +25347,17 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W22" s="15" t="inlineStr"/>
-      <c r="X22" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25372,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -25356,79 +25380,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -25443,17 +25447,13 @@
       </c>
       <c r="V23" s="11" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W23" s="15" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -25476,59 +25476,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -25541,15 +25561,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W24" s="15" t="inlineStr"/>
-      <c r="X24" s="16" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25564,17 +25584,13 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -25584,72 +25600,68 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -25657,10 +25669,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -25680,84 +25696,92 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>To'raboyeva Sabrina</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>27.09.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -25765,14 +25789,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -25792,7 +25812,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -25802,82 +25822,74 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 3736287</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -25886,9 +25898,9 @@
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -25908,7 +25920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'xtayeva Durdona</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -25918,7 +25930,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -25928,69 +25940,69 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
-        </is>
-      </c>
+          <t>19.06.2008</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
+          <t>UM 03728346</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U28" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
@@ -26016,17 +26028,13 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -26036,37 +26044,37 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -26074,16 +26082,24 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
+        </is>
+      </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr"/>
+          <t>UM 03730110</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+        </is>
+      </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
@@ -26096,15 +26112,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -26124,13 +26140,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -26140,62 +26160,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -26236,7 +26256,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -26246,7 +26266,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -26256,37 +26276,37 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -26296,22 +26316,22 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03752857</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
@@ -26329,7 +26349,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr"/>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -26352,7 +26376,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -26362,97 +26386,85 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>K 4590366</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U32" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -26472,7 +26484,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -26482,85 +26494,93 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>K 4590366</t>
+          <t>UM 0438281</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U33" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V33" s="11" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -26580,7 +26600,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -26590,7 +26610,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -26600,58 +26620,62 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -26661,7 +26685,7 @@
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U34" s="7" t="inlineStr">
@@ -26669,140 +26693,20 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X34" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>26-02</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>Xusan qizi</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>AB9239333</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>42207935680042</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>09.04.2018</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="inlineStr">
-        <is>
-          <t>22.07.1993</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O35" s="11" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>UM 03524597</t>
-        </is>
-      </c>
-      <c r="Q35" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
-        </is>
-      </c>
-      <c r="R35" s="11" t="inlineStr">
-        <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S35" s="12" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V35" s="11" t="inlineStr"/>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38093,7 +37997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38927,7 +38831,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam</t>
+          <t>Irgasheva Dinora</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -38935,49 +38839,37 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Ozodjon qizi</t>
+          <t>Shodmon qizi</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>AD9937321</t>
+          <t>AC 2430931</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60603085590037</t>
+          <t>60106035590029</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>24.12.2024</t>
+          <t>15.11.2019</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>06.03.2008</t>
+          <t>01.06.2003</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -38985,29 +38877,21 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Jalilova Shabnam Ozodjon qizi</t>
-        </is>
-      </c>
+      <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>UM 03752997</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0441030</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>14-maktab</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
@@ -39020,15 +38904,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W8" s="15" t="inlineStr"/>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -39043,7 +38927,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida</t>
+          <t>Jalilova Shabnam</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -39053,7 +38937,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -39063,37 +38947,37 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Shovkat qizi</t>
+          <t>Ozodjon qizi</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>AE6299685</t>
+          <t>AD9937321</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>60907085590063</t>
+          <t>60603085590037</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>09.07.2008</t>
+          <t>06.03.2008</t>
         </is>
       </c>
       <c r="N9" s="12" t="inlineStr">
@@ -39103,17 +38987,17 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Jumayeva Husnida Shovkat qizi</t>
+          <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>UM 03752998</t>
+          <t>UM 03752997</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385717/4069314/c3a33a4f-c2ab-4b51-8cc8-b8c19ac9ca12?preview=true</t>
         </is>
       </c>
       <c r="R9" s="11" t="inlineStr">
@@ -39137,9 +39021,9 @@
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X9" s="7" t="inlineStr">
@@ -39159,7 +39043,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya</t>
+          <t>Jumayeva Husnida</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -39169,72 +39053,72 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Rustamovna</t>
+          <t>Shovkat qizi</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>AE4674508</t>
+          <t>AE6299685</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61502085680047</t>
+          <t>60907085590063</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>15.02.2008</t>
+          <t>09.07.2008</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Karimova Nozliya Rustamovna</t>
+          <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>UM 03729342</t>
+          <t>UM 03752998</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4385718/4069764/009c2d04-09c9-4841-9d43-da9ac99e0514?preview=true</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
@@ -39253,9 +39137,9 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
+      <c r="W10" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
       </c>
       <c r="X10" s="7" t="inlineStr">
@@ -39275,7 +39159,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara</t>
+          <t>Karimova Nozliya</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -39285,47 +39169,47 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Safarali qizi</t>
+          <t>Rustamovna</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Mahmadmurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>AE2103843</t>
+          <t>AE4674508</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>60705005680087</t>
+          <t>61502085680047</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>07.05.2000</t>
+          <t>15.02.2008</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
@@ -39335,28 +39219,32 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Mahmamurodova Sevara Safarali qizi</t>
+          <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>K 5493345</t>
-        </is>
-      </c>
-      <c r="Q11" s="11" t="inlineStr"/>
+          <t>UM 03729342</t>
+        </is>
+      </c>
+      <c r="Q11" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101953/3661545/e114013f-14d6-4b30-a74f-3002af797fb8?preview=true</t>
+        </is>
+      </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>Kitob agrobiznes kasb-hunar kolleji</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -39364,14 +39252,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
-        </is>
-      </c>
-      <c r="W11" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: BOSHQA ODAM</t>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -39391,7 +39275,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar</t>
+          <t>Mahmadmurodova Sevara</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -39401,75 +39285,95 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Qayum qizi</t>
+          <t>Safarali qizi</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Mahmatqulova Nilufar Qayum qizi</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Mahmadmurodova Sevara Safarali qizi</t>
+        </is>
+      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>AE6047826</t>
+          <t>AE2103843</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60806085590115</t>
+          <t>60705005680087</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>08.06.2008</t>
+          <t>07.05.2000</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Mahmamurodova Sevara Safarali qizi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>UM 03754788</t>
+          <t>K 5493345</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="15" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' | KARANTIN: ❌ BOSHQA ODAM — ID-karta MRZ: 'MAHMADMURODOVA SEVARA' | bazada: 'Mahmamurodova Sevara' (fayl: Maxmudmurodova Sevara 390.docx)</t>
+        </is>
+      </c>
+      <c r="W12" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: BOSHQA ODAM</t>
+        </is>
+      </c>
       <c r="X12" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -39487,7 +39391,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna</t>
+          <t>Mahmatqulova Nilufar</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -39497,72 +39401,60 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>To'ra qizi</t>
+          <t>Qayum qizi</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
-        </is>
-      </c>
+          <t>Mahmatqulova Nilufar Qayum qizi</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>AE4270256</t>
+          <t>AE6047826</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>61707085680068</t>
+          <t>60806085590115</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>17.07.2008</t>
+          <t>08.06.2008</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Mahmudova Maftuna To'ra qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>UM 03730531</t>
-        </is>
-      </c>
-      <c r="Q13" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03754788</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>43-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
@@ -39572,20 +39464,12 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W13" s="15" t="inlineStr"/>
       <c r="X13" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -39603,7 +39487,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda</t>
+          <t>Mahmudova Maftuna</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -39613,7 +39497,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -39623,27 +39507,27 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nosir qizi</t>
+          <t>To'ra qizi</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>AE4263249</t>
+          <t>AE4270256</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60710085680047</t>
+          <t>61707085680068</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -39653,7 +39537,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>07.10.2008</t>
+          <t>17.07.2008</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -39663,22 +39547,22 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Mannonova Shahrizoda Nosir qizi</t>
+          <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>UM 03728995</t>
+          <t>UM 03730531</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4114844/3626812/61c2907f-efef-4fbc-82c2-3b7af55a8b93?preview=true</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -39719,78 +39603,82 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr"/>
+          <t>Mannonova Shahrizoda</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Hasan qizi</t>
+          <t>Nosir qizi</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>AE5221552</t>
+          <t>AE4263249</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>60106075720246</t>
+          <t>60710085680047</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>01.06.2007</t>
+          <t>07.10.2008</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Maxmarajabova Zerda Hasan qizi</t>
+          <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>UM 03718284</t>
+          <t>UM 03728995</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872455/3622330/75fbcdcb-2539-4ead-8c37-5043f369070d?preview=true</t>
         </is>
       </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
@@ -39831,82 +39719,78 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Maxmarajabova Zerda</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Hasan qizi</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AE2259069</t>
+          <t>AE5221552</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63001085590111</t>
+          <t>60106075720246</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>09.04.2025</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>30.01.2008</t>
+          <t>01.06.2007</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Muminova Sevinch Uchqun qizi</t>
+          <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>UM 03752895</t>
+          <t>UM 03718284</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4397186/4088504/fbeb9dfa-b793-4602-9fb9-5ad6bf15f7ac?preview=true</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>35-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -39947,51 +39831,57 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr"/>
+          <t>Muminova Sevinch</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>46255</v>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>AB8521319</t>
+          <t>AE2259069</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>62906005590060</t>
+          <t>63001085590111</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>02.01.2018</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>29.06.2000</t>
+          <t>30.01.2008</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
@@ -40001,28 +39891,32 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
+          <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>K 5487472</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="inlineStr"/>
+          <t>UM 03752895</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4378215/3988713/2d167389-30e1-4cdc-b2f7-87aeecafae73?preview=true</t>
+        </is>
+      </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
+          <t>20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -40030,11 +39924,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
-        </is>
-      </c>
+      <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -40057,57 +39947,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Mustafayeva Nargiza</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>46255</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Zaxriddin qizi</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE2428256</t>
+          <t>AB8521319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60506085590066</t>
+          <t>62906005590060</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>02.01.2018</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>05.06.2008</t>
+          <t>29.06.2000</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -40117,32 +40001,28 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Muxtorova Xadicha Zaxriddin qizi</t>
+          <t>Mustafayeva Nargiza Ulug‘bek qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03751925</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
-        </is>
-      </c>
+          <t>K 5487472</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -40150,7 +40030,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 206 tasdiqlandi (docx ichidagi raqam). Fayl nomidagi '205' xato — 205 Salayeva Dilrozga tegishli.</t>
+        </is>
+      </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -40173,7 +40057,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor</t>
+          <t>Muxtorova Xadicha</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -40183,93 +40067,93 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Zaxriddin qizi</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>AB5359926</t>
+          <t>AE2428256</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>40211995680023</t>
+          <t>60506085590066</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>12.12.2016</t>
+          <t>22.04.2025</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>02.11.1999</t>
+          <t>05.06.2008</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Narziyeva Intizor Iskandar qizi</t>
+          <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>K 5047841</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr"/>
+          <t>UM 03751925</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3832607/3445630/3d6b7fad-5d24-4750-a08d-cd3dbdebae33?preview=true</t>
+        </is>
+      </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>To'liq</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -40289,7 +40173,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Niyozova Sevara</t>
+          <t>Narziyeva Intizor</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -40299,60 +40183,68 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Turoqulovna</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Niyozova Sevara Turoqulovna</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AD9706738</t>
+          <t>AB5359926</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>412068 9256 0120</t>
+          <t>40211995680023</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>12.12.2016</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>12.06.1989</t>
+          <t>02.11.1999</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Narziyeva Intizor Iskandar qizi</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>K 0998119</t>
+          <t>K 5047841</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -40362,22 +40254,22 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U20" s="17" t="inlineStr">
-        <is>
-          <t>FAYL_YOQ</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>To'liq</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
-        </is>
-      </c>
-      <c r="W20" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+          <t>Familiya biometrik pasport AB5359926 va kasb-hunar kolleji diplomi K 5047841 bo'yicha 'Narziyeva' deb tasdiqlandi (#212)</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -40397,103 +40289,95 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr"/>
+          <t>Niyozova Sevara</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Mashrab qizi</t>
+          <t>Turoqulovna</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
+          <t>Niyozova Sevara Turoqulovna</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>AD9494409</t>
+          <t>AD9706738</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>60504085680019</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>26.09.2025</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>12.06.1989</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>Nurillayeva Sevinch Mashrab qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>UM 03729348</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
-        </is>
-      </c>
+          <t>K 0998119</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U21" s="17" t="inlineStr">
+        <is>
+          <t>FAYL_YOQ</t>
         </is>
       </c>
       <c r="V21" s="11" t="inlineStr">
         <is>
-          <t>Nurillayeva Sevinch Mashrab qizi (#246) ma'lumotlari tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>1-kurs kontrakt biriktirish (bank qatori 134) dan shartnoma №304 biriktirildi</t>
+        </is>
+      </c>
+      <c r="W21" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -40513,78 +40397,78 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Nurillayeva Sevinch</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Zokir qizi</t>
+          <t>Mashrab qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD0776916</t>
+          <t>AD9494409</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62012045590040</t>
+          <t>60504085680019</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Ortiqova Dilnoza Zokir qizi</t>
+          <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 1313018</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03729348</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3719931/3709607/bb57b93a-9984-4d2d-a8e6-2d723d68011f?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -40594,7 +40478,7 @@
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -40602,10 +40486,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>Nurillayeva Sevinch Mashrab qizi (#246) ma'lumotlari tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -40625,7 +40513,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo</t>
+          <t>Ortiqova Dilnoza</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -40635,7 +40523,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -40645,37 +40533,37 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Talantjon qizi</t>
+          <t>Zokir qizi</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>AE2118072</t>
+          <t>AD0776916</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>62201085590064</t>
+          <t>62012045590040</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -40685,22 +40573,18 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+          <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>UM 03753960</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1313018</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
@@ -40710,7 +40594,7 @@
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -40721,7 +40605,7 @@
       <c r="V23" s="11" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -40741,13 +40625,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>Qarshiyeva Shahlo</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -40757,54 +40645,62 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Farhod qizi</t>
+          <t>Talantjon qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Quchqarova Zebiniso Farhod qizi</t>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE1143288</t>
+          <t>AE2118072</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62911085630012</t>
+          <t>62201085590064</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Shahlo Talantjon qizi</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03742130</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03753960</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3427009/3170947/1ca0fd7a-fc37-4346-8a03-bd93c2f367b7?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -40817,19 +40713,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U24" s="16" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
-        </is>
-      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -40849,78 +40741,70 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu</t>
+          <t>Quchqarova Zebiniso</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Uyg'un qizi</t>
+          <t>Farhod qizi</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
+          <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>AE4246251</t>
+          <t>AE1143288</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>62702085680028</t>
+          <t>62911085630012</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>18.09.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>27.02.2008</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O25" s="11" t="inlineStr">
-        <is>
-          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
-        </is>
-      </c>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr"/>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>UM 03729118</t>
-        </is>
-      </c>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03742130</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
@@ -40938,10 +40822,14 @@
           <t>CHALA</t>
         </is>
       </c>
-      <c r="V25" s="11" t="inlineStr"/>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>Otasining ismi ID-karta AE1143288 bo'yicha 'Farhod qizi' deb tuzatildi (#187). Shahodatnoma kutilmoqda.</t>
+        </is>
+      </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -40961,82 +40849,78 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Samiyeva Sevinchbonu</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-08 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Xudoyqulovna</t>
+          <t>Uyg'un qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD8686485</t>
+          <t>AE4246251</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62201085590019</t>
+          <t>62702085680028</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>19.09.2024</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>27.02.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
+          <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 03751785</t>
+          <t>UM 03729118</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3921813/3528167/a25b83d1-50fe-4e6b-b16e-c40e1585873a?preview=true</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -41055,9 +40939,9 @@
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="15" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -41077,53 +40961,57 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr"/>
+          <t>Sanaqulova Muxtarama</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>G'ofur qizi</t>
+          <t>Xudoyqulovna</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>AC1805235</t>
+          <t>AD8686485</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>60409015590065</t>
+          <t>62201085590019</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>08.04.2019</t>
+          <t>19.09.2024</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>04.09.2001</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -41133,33 +41021,37 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Sanaqulova Nozliya G'ofur qizi</t>
+          <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
       <c r="P27" s="9" t="inlineStr">
         <is>
-          <t>K 5509185</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="inlineStr"/>
+          <t>UM 03751785</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4368419/3969790/17c6835f-3af9-4593-91bc-271a04412172?preview=true</t>
+        </is>
+      </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>Miroq sport pedagogika kolleji</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U27" s="16" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr"/>
@@ -41185,49 +41077,53 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>Sanaqulova Nozliya</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Zafar qizi</t>
+          <t>G'ofur qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AB6304158</t>
+          <t>AC1805235</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>415079 8559 0074</t>
+          <t>60409015590065</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>28.03.2017</t>
+          <t>08.04.2019</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>15.07.1998</t>
+          <t>04.09.2001</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -41237,18 +41133,18 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>K 4587984</t>
+          <t>K 5509185</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
+          <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -41258,16 +41154,20 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U28" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="15" t="inlineStr"/>
+      <c r="W28" s="15" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
       <c r="X28" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -41285,7 +41185,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona</t>
+          <t>Sayfieva Sarvinoz</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -41293,101 +41193,81 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
+      <c r="E29" s="12" t="inlineStr"/>
+      <c r="F29" s="12" t="inlineStr"/>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Sayfilla qizi</t>
+          <t>Zafar qizi</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Sayfiyeva Sarvinoz Zafar qizi</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>AE4385111</t>
+          <t>AB6304158</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>62203085730015</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>28.03.2017</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>22.03.2008</t>
+          <t>15.07.1998</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>UM 03757340</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
-        </is>
-      </c>
+          <t>K 4587984</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz qurulish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V29" s="11" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
-        </is>
-      </c>
-      <c r="W29" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
-        </is>
-      </c>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="U29" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr"/>
+      <c r="W29" s="15" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -41405,7 +41285,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal</t>
+          <t>Sayfillayeva Shodiyona</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -41415,72 +41295,72 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Jura qizi</t>
+          <t>Sayfilla qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AD2624840</t>
+          <t>AE4385111</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>62408065590018</t>
+          <t>62203085730015</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>18.02.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>24.08.2006</t>
+          <t>22.03.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Turayeva Gulasal Jura qizi</t>
+          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 01922678</t>
+          <t>UM 03757340</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3858565/3533800/f70f4bd4-3f76-4fc0-9ece-c3af7f562982?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -41490,7 +41370,7 @@
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U30" s="7" t="inlineStr">
@@ -41498,10 +41378,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'SAYFILLAYEVA SHODIYONA' | bazada: 'Sayfullayeva Shodiyona'; imlo farqi — Shahodatnoma PDF: 'Sayfillayeva Shodiyona Sayfilla qizi' | bazada: 'Sayfullayeva Shodiyona'</t>
+        </is>
+      </c>
+      <c r="W30" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
@@ -41521,82 +41405,92 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr"/>
+          <t>Turayeva Gulasal</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>46272</v>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Xamdam qizi</t>
+          <t>Jura qizi</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>AB5702170</t>
+          <t>AD2624840</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>42601925680010</t>
+          <t>62408065590018</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>19.01.2017</t>
+          <t>18.02.2023</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>26.01.1992</t>
+          <t>24.08.2006</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Usmonova Gulnoza Xamdam qizi</t>
+          <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>K 1994177</t>
-        </is>
-      </c>
-      <c r="Q31" s="11" t="inlineStr"/>
+          <t>UM 01922678</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/638245/461782/a3aa29cb-5370-4c81-224d-08db6f993680?preview=true</t>
+        </is>
+      </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -41604,11 +41498,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="11" t="inlineStr">
-        <is>
-          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
-        </is>
-      </c>
+      <c r="V31" s="11" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -41631,85 +41521,99 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
+          <t>Usmonova Gulnoza</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Xamdam qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AB5702170</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>42601925680010</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>19.01.2017</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>26.01.1992</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Usmonova Gulnoza Xamdam qizi</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>K 1994177</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U32" s="16" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="15" t="inlineStr"/>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Shartnoma raqami 283 (fayl nomi bo'yicha). Docx ichida xato '271' yozilgan — 271 Samiyeva Sevinchbonuga tegishli (uning o'z docx fayli bilan tasdiqlangan).</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X32" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -41727,7 +41631,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Uzoqova Fazilat</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -41735,49 +41639,41 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="12" t="inlineStr"/>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>07.12.1990</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
@@ -41785,20 +41681,16 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
-        </is>
-      </c>
+      <c r="O33" s="11" t="inlineStr"/>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
@@ -41808,20 +41700,16 @@
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U33" s="16" t="inlineStr">
+        <is>
+          <t>Chala</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr"/>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
+      <c r="W33" s="15" t="inlineStr"/>
       <c r="X33" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -41839,13 +41727,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
+          <t>Xolmurodova Sabina</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -41855,62 +41747,58 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02172469</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -41920,7 +41808,7 @@
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U34" s="7" t="inlineStr">
@@ -41931,7 +41819,7 @@
       <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X34" s="7" t="inlineStr">
@@ -41951,17 +41839,13 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Yahyomurodova Gulsanam</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -41971,37 +41855,37 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N35" s="12" t="inlineStr">
@@ -42011,22 +41895,22 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="P35" s="9" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="Q35" s="11" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
         </is>
       </c>
       <c r="R35" s="11" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S35" s="12" t="inlineStr">
@@ -42056,8 +41940,124 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Samijon qizi</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>AE4688777</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>63007085680074</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>20.10.2025</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>30.07.2008</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U36" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X36" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -15060,7 +15060,7 @@
       <c r="I156" s="3" t="inlineStr"/>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>AB6959079</t>
+          <t>AD 4323840</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -2210,7 +2210,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr">
         <is>
@@ -2378,7 +2382,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="4" t="inlineStr">
         <is>
@@ -4790,11 +4798,27 @@
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>K 6071373</t>
+        </is>
+      </c>
       <c r="Q44" s="4" t="inlineStr"/>
-      <c r="R44" s="4" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr"/>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="U44" s="5" t="inlineStr"/>
       <c r="V44" s="4" t="inlineStr">
         <is>
@@ -5494,7 +5518,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
       <c r="U51" s="11" t="inlineStr"/>
       <c r="V51" s="10" t="inlineStr">
         <is>
@@ -7058,7 +7086,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U69" s="11" t="inlineStr"/>
       <c r="V69" s="10" t="inlineStr">
         <is>
@@ -7394,7 +7426,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="U73" s="11" t="inlineStr"/>
       <c r="V73" s="10" t="inlineStr">
         <is>
@@ -7478,7 +7514,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T74" s="5" t="inlineStr"/>
+      <c r="T74" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U74" s="5" t="inlineStr"/>
       <c r="V74" s="4" t="inlineStr">
         <is>
@@ -7730,7 +7770,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="U77" s="11" t="inlineStr"/>
       <c r="V77" s="10" t="inlineStr">
         <is>
@@ -8874,7 +8918,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T90" s="5" t="inlineStr"/>
+      <c r="T90" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U90" s="5" t="inlineStr"/>
       <c r="V90" s="4" t="inlineStr">
         <is>
@@ -11616,7 +11664,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T119" s="11" t="inlineStr"/>
+      <c r="T119" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U119" s="11" t="inlineStr"/>
       <c r="V119" s="10" t="inlineStr">
         <is>
@@ -16636,11 +16688,27 @@
         </is>
       </c>
       <c r="O172" s="4" t="inlineStr"/>
-      <c r="P172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>D 0094389</t>
+        </is>
+      </c>
       <c r="Q172" s="4" t="inlineStr"/>
-      <c r="R172" s="4" t="inlineStr"/>
-      <c r="S172" s="5" t="inlineStr"/>
-      <c r="T172" s="5" t="inlineStr"/>
+      <c r="R172" s="4" t="inlineStr">
+        <is>
+          <t>Sharisabz tuman Chorshanbe agrosanoat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S172" s="5" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T172" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="U172" s="5" t="inlineStr"/>
       <c r="V172" s="4" t="inlineStr">
         <is>
@@ -24072,7 +24140,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T252" s="5" t="inlineStr"/>
+      <c r="T252" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="U252" s="5" t="inlineStr"/>
       <c r="V252" s="4" t="inlineStr">
         <is>
@@ -24772,7 +24844,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T260" s="5" t="inlineStr"/>
+      <c r="T260" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
       <c r="U260" s="5" t="inlineStr"/>
       <c r="V260" s="4" t="inlineStr">
         <is>
@@ -25024,7 +25100,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T263" s="11" t="inlineStr"/>
+      <c r="T263" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U263" s="11" t="inlineStr"/>
       <c r="V263" s="10" t="inlineStr">
         <is>
@@ -25900,11 +25980,27 @@
       </c>
       <c r="N273" s="11" t="inlineStr"/>
       <c r="O273" s="10" t="inlineStr"/>
-      <c r="P273" s="8" t="inlineStr"/>
+      <c r="P273" s="8" t="inlineStr">
+        <is>
+          <t>K 6070161</t>
+        </is>
+      </c>
       <c r="Q273" s="10" t="inlineStr"/>
-      <c r="R273" s="10" t="inlineStr"/>
-      <c r="S273" s="11" t="inlineStr"/>
-      <c r="T273" s="11" t="inlineStr"/>
+      <c r="R273" s="10" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S273" s="11" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T273" s="11" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
       <c r="U273" s="11" t="inlineStr"/>
       <c r="V273" s="10" t="inlineStr">
         <is>
@@ -27476,7 +27572,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T290" s="5" t="inlineStr"/>
+      <c r="T290" s="5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
       <c r="U290" s="5" t="inlineStr"/>
       <c r="V290" s="4" t="inlineStr">
         <is>
@@ -30058,7 +30158,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T319" s="11" t="inlineStr"/>
+      <c r="T319" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U319" s="11" t="inlineStr"/>
       <c r="V319" s="10" t="inlineStr">
         <is>
@@ -30506,7 +30610,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T324" s="5" t="inlineStr"/>
+      <c r="T324" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="U324" s="5" t="inlineStr"/>
       <c r="V324" s="4" t="inlineStr">
         <is>
@@ -33354,7 +33462,11 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T356" s="5" t="inlineStr"/>
+      <c r="T356" s="5" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="U356" s="5" t="inlineStr"/>
       <c r="V356" s="4" t="inlineStr">
         <is>
@@ -34468,7 +34580,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T368" s="5" t="inlineStr"/>
+      <c r="T368" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="U368" s="5" t="inlineStr"/>
       <c r="V368" s="4" t="inlineStr">
         <is>
@@ -35846,8 +35962,16 @@
       <c r="O383" s="10" t="inlineStr"/>
       <c r="P383" s="8" t="inlineStr"/>
       <c r="Q383" s="10" t="inlineStr"/>
-      <c r="R383" s="10" t="inlineStr"/>
-      <c r="S383" s="11" t="inlineStr"/>
+      <c r="R383" s="10" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="S383" s="11" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
       <c r="T383" s="11" t="inlineStr"/>
       <c r="U383" s="11" t="inlineStr"/>
       <c r="V383" s="10" t="inlineStr">
@@ -38460,7 +38584,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T412" s="5" t="inlineStr"/>
+      <c r="T412" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="U412" s="5" t="inlineStr"/>
       <c r="V412" s="4" t="inlineStr">
         <is>
@@ -39560,7 +39688,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T424" s="5" t="inlineStr"/>
+      <c r="T424" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="U424" s="5" t="inlineStr"/>
       <c r="V424" s="4" t="inlineStr">
         <is>
@@ -44394,7 +44526,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T477" s="11" t="inlineStr"/>
+      <c r="T477" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U477" s="11" t="inlineStr"/>
       <c r="V477" s="10" t="inlineStr">
         <is>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -83,14 +83,14 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="001E40AF"/>
-      <sz val="9.5"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="10"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -144,14 +144,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -2486,9 +2486,9 @@
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X19" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="V23" s="10" t="inlineStr"/>
-      <c r="W23" s="15" t="inlineStr">
+      <c r="W23" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="V25" s="10" t="inlineStr"/>
-      <c r="W25" s="15" t="inlineStr">
+      <c r="W25" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="V35" s="10" t="inlineStr"/>
-      <c r="W35" s="15" t="inlineStr">
+      <c r="W35" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -4819,7 +4819,7 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="U44" s="16" t="inlineStr">
+      <c r="U44" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="V47" s="10" t="inlineStr"/>
-      <c r="W47" s="15" t="inlineStr">
+      <c r="W47" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -5247,7 +5247,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U48" s="16" t="inlineStr">
+      <c r="U48" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -5622,9 +5622,9 @@
         </is>
       </c>
       <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X52" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="inlineStr"/>
-      <c r="W80" s="15" t="inlineStr">
+      <c r="W80" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -9679,7 +9679,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U98" s="16" t="inlineStr">
+      <c r="U98" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -12211,13 +12211,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U124" s="16" t="inlineStr">
+      <c r="U124" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="15" t="inlineStr">
+      <c r="W124" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -14124,7 +14124,7 @@
         </is>
       </c>
       <c r="W145" s="6" t="inlineStr"/>
-      <c r="X145" s="16" t="inlineStr">
+      <c r="X145" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -15959,7 +15959,7 @@
         </is>
       </c>
       <c r="V164" s="4" t="inlineStr"/>
-      <c r="W164" s="15" t="inlineStr">
+      <c r="W164" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -16691,7 +16691,7 @@
         </is>
       </c>
       <c r="V172" s="4" t="inlineStr"/>
-      <c r="W172" s="15" t="inlineStr">
+      <c r="W172" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -19769,7 +19769,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U205" s="16" t="inlineStr">
+      <c r="U205" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -22287,7 +22287,7 @@
         </is>
       </c>
       <c r="V232" s="4" t="inlineStr"/>
-      <c r="W232" s="15" t="inlineStr">
+      <c r="W232" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -24509,7 +24509,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U256" s="16" t="inlineStr">
+      <c r="U256" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="W287" s="6" t="inlineStr"/>
-      <c r="X287" s="16" t="inlineStr">
+      <c r="X287" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -30907,7 +30907,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U327" s="16" t="inlineStr">
+      <c r="U327" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -31099,7 +31099,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U329" s="16" t="inlineStr">
+      <c r="U329" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -31462,7 +31462,7 @@
       </c>
       <c r="V333" s="10" t="inlineStr"/>
       <c r="W333" s="6" t="inlineStr"/>
-      <c r="X333" s="16" t="inlineStr">
+      <c r="X333" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -31997,7 +31997,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
         </is>
       </c>
-      <c r="W339" s="15" t="inlineStr">
+      <c r="W339" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -33026,7 +33026,7 @@
       </c>
       <c r="V351" s="10" t="inlineStr"/>
       <c r="W351" s="6" t="inlineStr"/>
-      <c r="X351" s="16" t="inlineStr">
+      <c r="X351" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -33421,7 +33421,7 @@
           <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60204095590028).</t>
         </is>
       </c>
-      <c r="W355" s="15" t="inlineStr">
+      <c r="W355" s="16" t="inlineStr">
         <is>
           <t>Shahodatnoma: TRANSLIT</t>
         </is>
@@ -35688,7 +35688,7 @@
         </is>
       </c>
       <c r="W380" s="6" t="inlineStr"/>
-      <c r="X380" s="16" t="inlineStr">
+      <c r="X380" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -35953,7 +35953,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U383" s="16" t="inlineStr">
+      <c r="U383" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -36069,7 +36069,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U384" s="16" t="inlineStr">
+      <c r="U384" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -36813,7 +36813,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="U392" s="16" t="inlineStr">
+      <c r="U392" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -39152,7 +39152,7 @@
         </is>
       </c>
       <c r="W418" s="6" t="inlineStr"/>
-      <c r="X418" s="16" t="inlineStr">
+      <c r="X418" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -42477,7 +42477,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U455" s="16" t="inlineStr">
+      <c r="U455" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -43469,7 +43469,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U466" s="16" t="inlineStr">
+      <c r="U466" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="V469" s="10" t="inlineStr"/>
       <c r="W469" s="6" t="inlineStr"/>
-      <c r="X469" s="16" t="inlineStr">
+      <c r="X469" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -45189,7 +45189,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="U484" s="16" t="inlineStr">
+      <c r="U484" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -45673,7 +45673,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="U489" s="16" t="inlineStr">
+      <c r="U489" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -46699,7 +46699,7 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="U500" s="16" t="inlineStr">
+      <c r="U500" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -47156,13 +47156,13 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U505" s="16" t="inlineStr">
+      <c r="U505" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V505" s="10" t="inlineStr"/>
-      <c r="W505" s="15" t="inlineStr">
+      <c r="W505" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -51264,7 +51264,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W548" s="15" t="inlineStr">
+      <c r="W548" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="15" t="inlineStr">
+      <c r="W4" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -53939,7 +53939,7 @@
           <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60204095590028).</t>
         </is>
       </c>
-      <c r="W12" s="15" t="inlineStr">
+      <c r="W12" s="16" t="inlineStr">
         <is>
           <t>Shahodatnoma: TRANSLIT</t>
         </is>
@@ -54157,7 +54157,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U14" s="16" t="inlineStr">
+      <c r="U14" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -55096,13 +55096,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U7" s="16" t="inlineStr">
+      <c r="U7" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V7" s="10" t="inlineStr"/>
-      <c r="W7" s="15" t="inlineStr">
+      <c r="W7" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -55566,7 +55566,7 @@
         </is>
       </c>
       <c r="V11" s="10" t="inlineStr"/>
-      <c r="W11" s="15" t="inlineStr">
+      <c r="W11" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -56131,7 +56131,7 @@
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="16" t="inlineStr">
+      <c r="X16" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -56351,7 +56351,7 @@
       </c>
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="16" t="inlineStr">
+      <c r="X18" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -56466,7 +56466,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
         </is>
       </c>
-      <c r="W19" s="15" t="inlineStr">
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -56799,7 +56799,7 @@
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="16" t="inlineStr">
+      <c r="X22" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -57015,7 +57015,7 @@
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="16" t="inlineStr">
+      <c r="X24" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -57564,7 +57564,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="16" t="inlineStr">
+      <c r="U29" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -58020,7 +58020,7 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="U33" s="16" t="inlineStr">
+      <c r="U33" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -59275,7 +59275,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U9" s="16" t="inlineStr">
+      <c r="U9" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -61278,7 +61278,7 @@
       </c>
       <c r="V27" s="10" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="16" t="inlineStr">
+      <c r="X27" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -61369,7 +61369,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="U28" s="16" t="inlineStr">
+      <c r="U28" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -62674,7 +62674,7 @@
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="15" t="inlineStr">
+      <c r="W4" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -62790,7 +62790,7 @@
         </is>
       </c>
       <c r="V5" s="10" t="inlineStr"/>
-      <c r="W5" s="15" t="inlineStr">
+      <c r="W5" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -64018,7 +64018,7 @@
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="15" t="inlineStr">
+      <c r="W16" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -64346,7 +64346,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U19" s="16" t="inlineStr">
+      <c r="U19" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -65105,13 +65105,13 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U26" s="16" t="inlineStr">
+      <c r="U26" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="15" t="inlineStr">
+      <c r="W26" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -66292,7 +66292,7 @@
         </is>
       </c>
       <c r="V3" s="10" t="inlineStr"/>
-      <c r="W3" s="15" t="inlineStr">
+      <c r="W3" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -66632,7 +66632,7 @@
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="15" t="inlineStr">
+      <c r="W6" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -68086,7 +68086,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="U19" s="16" t="inlineStr">
+      <c r="U19" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -69638,7 +69638,7 @@
           <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
         </is>
       </c>
-      <c r="W33" s="15" t="inlineStr">
+      <c r="W33" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT</t>
         </is>
@@ -70135,7 +70135,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U4" s="16" t="inlineStr">
+      <c r="U4" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -70467,7 +70467,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U7" s="16" t="inlineStr">
+      <c r="U7" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -70574,7 +70574,7 @@
         </is>
       </c>
       <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="16" t="inlineStr">
+      <c r="X8" s="15" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
         </is>
@@ -70801,7 +70801,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="15" t="inlineStr">
+      <c r="W10" s="16" t="inlineStr">
         <is>
           <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
         </is>
@@ -72481,7 +72481,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U25" s="16" t="inlineStr">
+      <c r="U25" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -72597,7 +72597,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U26" s="16" t="inlineStr">
+      <c r="U26" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -72713,7 +72713,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U27" s="16" t="inlineStr">
+      <c r="U27" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>
@@ -72925,7 +72925,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="U29" s="16" t="inlineStr">
+      <c r="U29" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -73367,7 +73367,7 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="U33" s="16" t="inlineStr">
+      <c r="U33" s="15" t="inlineStr">
         <is>
           <t>Chala</t>
         </is>
@@ -74054,7 +74054,7 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="U3" s="16" t="inlineStr">
+      <c r="U3" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
         </is>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -33686,7 +33686,7 @@
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="C359" s="9" t="inlineStr">

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$563</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$35</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X562"/>
+  <dimension ref="A1:X563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -33026,9 +33026,9 @@
       </c>
       <c r="V351" s="10" t="inlineStr"/>
       <c r="W351" s="6" t="inlineStr"/>
-      <c r="X351" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X351" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -51977,63 +51977,71 @@
       </c>
       <c r="B557" s="8" t="inlineStr">
         <is>
-          <t>25-18</t>
+          <t>25-17</t>
         </is>
       </c>
       <c r="C557" s="9" t="inlineStr">
         <is>
-          <t>Zarqulova Komila</t>
-        </is>
-      </c>
-      <c r="D557" s="10" t="inlineStr"/>
-      <c r="E557" s="11" t="inlineStr"/>
+          <t>Zaripova Setora</t>
+        </is>
+      </c>
+      <c r="D557" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E557" s="11" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
       <c r="F557" s="11" t="inlineStr"/>
       <c r="G557" s="11" t="inlineStr">
         <is>
-          <t>Mirzayevna</t>
+          <t>Zuxriddin qizi</t>
         </is>
       </c>
       <c r="H557" s="10" t="inlineStr">
         <is>
-          <t>Zarqulova Komila Mirzayevna</t>
+          <t>Zaripova Setora Zuxriddin qizi</t>
         </is>
       </c>
       <c r="I557" s="9" t="inlineStr"/>
       <c r="J557" s="11" t="inlineStr">
         <is>
-          <t>AD9593473</t>
+          <t>AD8594631</t>
         </is>
       </c>
       <c r="K557" s="8" t="inlineStr">
         <is>
-          <t>63107085590134</t>
+          <t>60609075730014</t>
         </is>
       </c>
       <c r="L557" s="11" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>12.09.2024</t>
         </is>
       </c>
       <c r="M557" s="11" t="inlineStr">
         <is>
-          <t>31.07.2008</t>
+          <t>06.09.2007</t>
         </is>
       </c>
       <c r="N557" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O557" s="10" t="inlineStr"/>
       <c r="P557" s="8" t="inlineStr">
         <is>
-          <t>UM 03300424</t>
+          <t>UM 03299021</t>
         </is>
       </c>
       <c r="Q557" s="10" t="inlineStr"/>
       <c r="R557" s="10" t="inlineStr">
         <is>
-          <t>43-maktab</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S557" s="11" t="inlineStr">
@@ -52041,17 +52049,25 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T557" s="11" t="inlineStr"/>
-      <c r="U557" s="11" t="inlineStr"/>
+      <c r="T557" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U557" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V557" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
         </is>
       </c>
       <c r="W557" s="6" t="inlineStr"/>
-      <c r="X557" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X557" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -52061,110 +52077,78 @@
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>25-18</t>
         </is>
       </c>
       <c r="C558" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
-        </is>
-      </c>
-      <c r="D558" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E558" s="5" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="F558" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Zarqulova Komila</t>
+        </is>
+      </c>
+      <c r="D558" s="4" t="inlineStr"/>
+      <c r="E558" s="5" t="inlineStr"/>
+      <c r="F558" s="5" t="inlineStr"/>
       <c r="G558" s="5" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Mirzayevna</t>
         </is>
       </c>
       <c r="H558" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="I558" s="3" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
+          <t>Zarqulova Komila Mirzayevna</t>
+        </is>
+      </c>
+      <c r="I558" s="3" t="inlineStr"/>
       <c r="J558" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AD9593473</t>
         </is>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63107085590134</t>
         </is>
       </c>
       <c r="L558" s="5" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M558" s="5" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>31.07.2008</t>
         </is>
       </c>
       <c r="N558" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O558" s="4" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O558" s="4" t="inlineStr"/>
       <c r="P558" s="2" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
-        </is>
-      </c>
-      <c r="Q558" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03300424</t>
+        </is>
+      </c>
+      <c r="Q558" s="4" t="inlineStr"/>
       <c r="R558" s="4" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>43-maktab</t>
         </is>
       </c>
       <c r="S558" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T558" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U558" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V558" s="4" t="inlineStr"/>
-      <c r="W558" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T558" s="5" t="inlineStr"/>
+      <c r="U558" s="5" t="inlineStr"/>
+      <c r="V558" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W558" s="6" t="inlineStr"/>
       <c r="X558" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52177,46 +52161,62 @@
       </c>
       <c r="B559" s="8" t="inlineStr">
         <is>
-          <t>24-13</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C559" s="9" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Munisa</t>
-        </is>
-      </c>
-      <c r="D559" s="10" t="inlineStr"/>
-      <c r="E559" s="11" t="inlineStr"/>
-      <c r="F559" s="11" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E559" s="11" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="F559" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G559" s="11" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H559" s="10" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Munisa Sherzod qizi</t>
-        </is>
-      </c>
-      <c r="I559" s="9" t="inlineStr"/>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
+      <c r="I559" s="9" t="inlineStr">
+        <is>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
       <c r="J559" s="11" t="inlineStr">
         <is>
-          <t>AD4793465</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K559" s="8" t="inlineStr">
         <is>
-          <t>60810065680099</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L559" s="11" t="inlineStr">
         <is>
-          <t>06.10.2023</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M559" s="11" t="inlineStr">
         <is>
-          <t>08.10.2006</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N559" s="11" t="inlineStr">
@@ -52224,31 +52224,47 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O559" s="10" t="inlineStr"/>
+      <c r="O559" s="10" t="inlineStr">
+        <is>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
       <c r="P559" s="8" t="inlineStr">
         <is>
-          <t>UM 02313341</t>
-        </is>
-      </c>
-      <c r="Q559" s="10" t="inlineStr"/>
+          <t>UM 03729571</t>
+        </is>
+      </c>
+      <c r="Q559" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+        </is>
+      </c>
       <c r="R559" s="10" t="inlineStr">
         <is>
-          <t>266-sonli umumiy o'rta ta'lim maktabin</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S559" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T559" s="11" t="inlineStr"/>
-      <c r="U559" s="11" t="inlineStr"/>
-      <c r="V559" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 3-kurs</t>
-        </is>
-      </c>
-      <c r="W559" s="6" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T559" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U559" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V559" s="10" t="inlineStr"/>
+      <c r="W559" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X559" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52261,12 +52277,12 @@
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>24-13</t>
         </is>
       </c>
       <c r="C560" s="3" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Ziyadullayeva Munisa</t>
         </is>
       </c>
       <c r="D560" s="4" t="inlineStr"/>
@@ -52274,46 +52290,50 @@
       <c r="F560" s="5" t="inlineStr"/>
       <c r="G560" s="5" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H560" s="4" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Ziyadullayeva Munisa Sherzod qizi</t>
         </is>
       </c>
       <c r="I560" s="3" t="inlineStr"/>
       <c r="J560" s="5" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AD4793465</t>
         </is>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>60810065680099</t>
         </is>
       </c>
       <c r="L560" s="5" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
-        </is>
-      </c>
-      <c r="M560" s="5" t="inlineStr"/>
+          <t>06.10.2023</t>
+        </is>
+      </c>
+      <c r="M560" s="5" t="inlineStr">
+        <is>
+          <t>08.10.2006</t>
+        </is>
+      </c>
       <c r="N560" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O560" s="4" t="inlineStr"/>
       <c r="P560" s="2" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>UM 02313341</t>
         </is>
       </c>
       <c r="Q560" s="4" t="inlineStr"/>
       <c r="R560" s="4" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>266-sonli umumiy o'rta ta'lim maktabin</t>
         </is>
       </c>
       <c r="S560" s="5" t="inlineStr">
@@ -52325,7 +52345,7 @@
       <c r="U560" s="5" t="inlineStr"/>
       <c r="V560" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 3-kurs</t>
         </is>
       </c>
       <c r="W560" s="6" t="inlineStr"/>
@@ -52341,106 +52361,74 @@
       </c>
       <c r="B561" s="8" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C561" s="9" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
+          <t>Ziyadullayeva Zahro</t>
         </is>
       </c>
       <c r="D561" s="10" t="inlineStr"/>
-      <c r="E561" s="11" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="F561" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E561" s="11" t="inlineStr"/>
+      <c r="F561" s="11" t="inlineStr"/>
       <c r="G561" s="11" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Ubaydullo qizi</t>
         </is>
       </c>
       <c r="H561" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
-      <c r="I561" s="9" t="inlineStr">
-        <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I561" s="9" t="inlineStr"/>
       <c r="J561" s="11" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AD8888020</t>
         </is>
       </c>
       <c r="K561" s="8" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>62609075590027</t>
         </is>
       </c>
       <c r="L561" s="11" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
-        </is>
-      </c>
-      <c r="M561" s="11" t="inlineStr">
-        <is>
-          <t>12.06.2007</t>
-        </is>
-      </c>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M561" s="11" t="inlineStr"/>
       <c r="N561" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O561" s="10" t="inlineStr">
-        <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
+      <c r="O561" s="10" t="inlineStr"/>
       <c r="P561" s="8" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
-        </is>
-      </c>
-      <c r="Q561" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q561" s="10" t="inlineStr"/>
       <c r="R561" s="10" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S561" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T561" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U561" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V561" s="10" t="inlineStr"/>
-      <c r="W561" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T561" s="11" t="inlineStr"/>
+      <c r="U561" s="11" t="inlineStr"/>
+      <c r="V561" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W561" s="6" t="inlineStr"/>
       <c r="X561" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52453,86 +52441,198 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C562" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D562" s="4" t="inlineStr"/>
+      <c r="E562" s="5" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F562" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G562" s="5" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H562" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I562" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J562" s="5" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L562" s="5" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M562" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N562" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O562" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P562" s="2" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q562" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R562" s="4" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S562" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T562" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U562" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V562" s="4" t="inlineStr"/>
+      <c r="W562" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X562" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="22" customHeight="1">
+      <c r="A563" s="8" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="8" t="inlineStr">
+        <is>
           <t>25-17</t>
         </is>
       </c>
-      <c r="C562" s="3" t="inlineStr">
+      <c r="C563" s="9" t="inlineStr">
         <is>
           <t>Ziyodulloyeva Muxlisa</t>
         </is>
       </c>
-      <c r="D562" s="4" t="inlineStr"/>
-      <c r="E562" s="5" t="inlineStr"/>
-      <c r="F562" s="5" t="inlineStr"/>
-      <c r="G562" s="5" t="inlineStr">
+      <c r="D563" s="10" t="inlineStr"/>
+      <c r="E563" s="11" t="inlineStr"/>
+      <c r="F563" s="11" t="inlineStr"/>
+      <c r="G563" s="11" t="inlineStr">
         <is>
           <t>Shuhrat qizi</t>
         </is>
       </c>
-      <c r="H562" s="4" t="inlineStr">
+      <c r="H563" s="10" t="inlineStr">
         <is>
           <t>Ziyodulloyeva Muxlisa Shuhrat qizi</t>
         </is>
       </c>
-      <c r="I562" s="3" t="inlineStr"/>
-      <c r="J562" s="5" t="inlineStr">
+      <c r="I563" s="9" t="inlineStr"/>
+      <c r="J563" s="11" t="inlineStr">
         <is>
           <t>AD9345748</t>
         </is>
       </c>
-      <c r="K562" s="2" t="inlineStr">
+      <c r="K563" s="8" t="inlineStr">
         <is>
           <t>61504085680074</t>
         </is>
       </c>
-      <c r="L562" s="5" t="inlineStr">
+      <c r="L563" s="11" t="inlineStr">
         <is>
           <t>11.11.2024</t>
         </is>
       </c>
-      <c r="M562" s="5" t="inlineStr">
+      <c r="M563" s="11" t="inlineStr">
         <is>
           <t>15.04.2008</t>
         </is>
       </c>
-      <c r="N562" s="5" t="inlineStr">
+      <c r="N563" s="11" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O562" s="4" t="inlineStr"/>
-      <c r="P562" s="2" t="inlineStr">
+      <c r="O563" s="10" t="inlineStr"/>
+      <c r="P563" s="8" t="inlineStr">
         <is>
           <t>UM 03275067</t>
         </is>
       </c>
-      <c r="Q562" s="4" t="inlineStr"/>
-      <c r="R562" s="4" t="inlineStr">
+      <c r="Q563" s="10" t="inlineStr"/>
+      <c r="R563" s="10" t="inlineStr">
         <is>
           <t>61-maktab</t>
         </is>
       </c>
-      <c r="S562" s="5" t="inlineStr">
+      <c r="S563" s="11" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T562" s="5" t="inlineStr"/>
-      <c r="U562" s="5" t="inlineStr"/>
-      <c r="V562" s="4" t="inlineStr">
+      <c r="T563" s="11" t="inlineStr"/>
+      <c r="U563" s="11" t="inlineStr"/>
+      <c r="V563" s="10" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
-      <c r="W562" s="6" t="inlineStr"/>
-      <c r="X562" s="7" t="inlineStr">
+      <c r="W563" s="6" t="inlineStr"/>
+      <c r="X563" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X562"/>
+  <autoFilter ref="A1:X563"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -52065,9 +52065,9 @@
         </is>
       </c>
       <c r="W557" s="6" t="inlineStr"/>
-      <c r="X557" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X557" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -791,7 +791,11 @@
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr">
         <is>
@@ -875,7 +879,11 @@
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr"/>
-      <c r="E3" s="11" t="inlineStr"/>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
       <c r="F3" s="11" t="inlineStr"/>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -959,7 +967,11 @@
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1043,7 +1055,11 @@
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="11" t="inlineStr"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
       <c r="F5" s="11" t="inlineStr"/>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -1133,7 +1149,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -1200,8 +1216,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T6" s="5" t="n">
-        <v>2026</v>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>+998 88 848-08-27 / +998 97 855-05-81 (Onasi)</t>
+        </is>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
@@ -1239,7 +1257,11 @@
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
       <c r="F7" s="11" t="inlineStr"/>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1329,7 +1351,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1400,7 +1422,7 @@
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>+998 18 980-49-50 / +998 08 830-86-50 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U8" s="7" t="inlineStr">
@@ -1439,7 +1461,11 @@
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="11" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="F9" s="11" t="inlineStr"/>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1531,7 +1557,11 @@
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
@@ -1617,7 +1647,7 @@
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1692,7 +1722,7 @@
       </c>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 871-57-37</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -1727,7 +1757,11 @@
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1817,7 +1851,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1892,7 +1926,7 @@
       </c>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 03 318-70-80 / +998 01 190-68-60 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
@@ -1933,7 +1967,7 @@
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>224</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2008,7 +2042,7 @@
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 905-47-05 / +998 99 419-23-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
@@ -2053,7 +2087,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2128,7 +2162,7 @@
       </c>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 463-62-67</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
@@ -2163,7 +2197,11 @@
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -2247,7 +2285,11 @@
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="F17" s="11" t="inlineStr"/>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -2335,7 +2377,11 @@
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -2419,7 +2465,11 @@
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -2507,7 +2557,11 @@
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -2597,7 +2651,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2672,7 +2726,7 @@
       </c>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 90 243-37-74 / +998 88 588-81-87 (Onasi)</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -2707,7 +2761,11 @@
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
@@ -2797,7 +2855,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2872,7 +2930,7 @@
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 75 910-91-80 / +998 88 566-08-02 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -2907,7 +2965,11 @@
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
@@ -2997,7 +3059,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -3072,7 +3134,7 @@
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 99 221-68-64 / +998 93 666-02-15 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -3107,7 +3169,11 @@
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -3191,7 +3257,11 @@
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -3277,7 +3347,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -3340,7 +3410,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 00 343-13-10</t>
         </is>
       </c>
       <c r="U28" s="7" t="inlineStr">
@@ -3373,7 +3443,7 @@
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>267</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -3442,11 +3512,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -3483,7 +3549,11 @@
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
@@ -3567,7 +3637,11 @@
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -3651,7 +3725,11 @@
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
@@ -3731,7 +3809,11 @@
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="11" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -3815,7 +3897,11 @@
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -3905,7 +3991,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3980,7 +4066,7 @@
       </c>
       <c r="T35" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 95 367-26-02 / +998 90 616-15-60 (Buvasi)</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -4017,7 +4103,7 @@
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>278</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -4090,11 +4176,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="T36" s="5" t="inlineStr"/>
       <c r="U36" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -4127,7 +4209,11 @@
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr"/>
-      <c r="E37" s="11" t="inlineStr"/>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -4217,7 +4303,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -4292,7 +4378,7 @@
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 91 219-06-17 / +998 91 217-34-81 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U38" s="7" t="inlineStr">
@@ -4327,7 +4413,11 @@
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="11" t="inlineStr"/>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -4411,7 +4501,11 @@
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4495,7 +4589,11 @@
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr"/>
-      <c r="E41" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -4579,7 +4677,11 @@
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
@@ -4663,7 +4765,11 @@
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -4753,7 +4859,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>294</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -4816,7 +4922,7 @@
       </c>
       <c r="T44" s="5" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>+998 91 957-18-58</t>
         </is>
       </c>
       <c r="U44" s="15" t="inlineStr">
@@ -4851,7 +4957,11 @@
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr"/>
-      <c r="E45" s="11" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -4945,7 +5055,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -5020,7 +5130,7 @@
       </c>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 70 120-22-08 / +998 70 125-22-08 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U46" s="7" t="inlineStr">
@@ -5061,7 +5171,7 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>383</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -5136,7 +5246,7 @@
       </c>
       <c r="T47" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 312-50-80 / +998 76 078-28-70 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -5177,7 +5287,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
@@ -5244,7 +5354,7 @@
       </c>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 97 799-76-71 / +998 88 403-76-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U48" s="15" t="inlineStr">
@@ -5275,7 +5385,11 @@
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -5365,7 +5479,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -5440,7 +5554,7 @@
       </c>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 602-17-08 / +998 70 219-11-08 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U50" s="7" t="inlineStr">
@@ -5475,7 +5589,11 @@
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr"/>
-      <c r="E51" s="11" t="inlineStr"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -5559,7 +5677,11 @@
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -5643,7 +5765,11 @@
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="11" t="inlineStr"/>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
@@ -5727,7 +5853,11 @@
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr">
         <is>
@@ -5811,7 +5941,11 @@
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr"/>
-      <c r="E55" s="11" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -5895,7 +6029,11 @@
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr">
         <is>
@@ -5979,7 +6117,11 @@
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr"/>
-      <c r="E57" s="11" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
@@ -6063,7 +6205,11 @@
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -6147,7 +6293,11 @@
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr"/>
-      <c r="E59" s="11" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -6233,7 +6383,7 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -6308,7 +6458,7 @@
       </c>
       <c r="T60" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 77 432-17-07 / +998 95 616-35-09 (Onasi)</t>
         </is>
       </c>
       <c r="U60" s="7" t="inlineStr">
@@ -6347,7 +6497,11 @@
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr"/>
-      <c r="E61" s="11" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -6437,7 +6591,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>314</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -6508,7 +6662,7 @@
       </c>
       <c r="T62" s="5" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>+998 70 629-89-00 / +998 97 319-62-60 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U62" s="7" t="inlineStr">
@@ -6543,7 +6697,11 @@
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr"/>
-      <c r="E63" s="11" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -6627,7 +6785,11 @@
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -6711,7 +6873,11 @@
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr"/>
-      <c r="E65" s="11" t="inlineStr"/>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
@@ -6795,7 +6961,11 @@
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -6875,7 +7045,11 @@
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr"/>
-      <c r="E67" s="11" t="inlineStr"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -6959,7 +7133,11 @@
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -7039,7 +7217,11 @@
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr"/>
-      <c r="E69" s="11" t="inlineStr"/>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -7123,7 +7305,11 @@
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -7211,7 +7397,11 @@
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr"/>
-      <c r="E71" s="11" t="inlineStr"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -7295,7 +7485,11 @@
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -7379,7 +7573,11 @@
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr"/>
-      <c r="E73" s="11" t="inlineStr"/>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -7551,7 +7749,11 @@
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr"/>
-      <c r="E75" s="11" t="inlineStr"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -7639,7 +7841,11 @@
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr">
         <is>
@@ -7723,7 +7929,11 @@
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr"/>
-      <c r="E77" s="11" t="inlineStr"/>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -7807,7 +8017,11 @@
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -7895,7 +8109,11 @@
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
@@ -7981,7 +8199,7 @@
       <c r="D80" s="4" t="inlineStr"/>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>282</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -8052,7 +8270,7 @@
       </c>
       <c r="T80" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 88 309-02-28 / +998 88 005-78-08 (Onasi)</t>
         </is>
       </c>
       <c r="U80" s="7" t="inlineStr">
@@ -8087,7 +8305,11 @@
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr"/>
-      <c r="E81" s="11" t="inlineStr"/>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="11" t="inlineStr">
         <is>
@@ -8177,7 +8399,7 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
@@ -8244,8 +8466,10 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T82" s="5" t="n">
-        <v>2014</v>
+      <c r="T82" s="5" t="inlineStr">
+        <is>
+          <t>+998 88 788-60-42 / +998 88 308-60-42 (Otasi / Onasi)</t>
+        </is>
       </c>
       <c r="U82" s="7" t="inlineStr">
         <is>
@@ -8283,7 +8507,11 @@
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr"/>
-      <c r="E83" s="11" t="inlineStr"/>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="F83" s="11" t="inlineStr"/>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -8367,7 +8595,11 @@
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -8451,7 +8683,11 @@
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr"/>
-      <c r="E85" s="11" t="inlineStr"/>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -8535,7 +8771,11 @@
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr">
         <is>
@@ -8787,7 +9027,11 @@
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr"/>
-      <c r="E89" s="11" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -8871,7 +9115,11 @@
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -8955,7 +9203,11 @@
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr"/>
-      <c r="E91" s="11" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
@@ -9043,7 +9295,11 @@
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="inlineStr">
         <is>
@@ -9129,7 +9385,7 @@
       <c r="D93" s="10" t="inlineStr"/>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -9200,7 +9456,7 @@
       </c>
       <c r="T93" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 768-70-08</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
@@ -9239,7 +9495,11 @@
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -9323,7 +9583,11 @@
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr"/>
-      <c r="E95" s="11" t="inlineStr"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -9413,7 +9677,7 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -9484,7 +9748,7 @@
       </c>
       <c r="T96" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>+998 88 097-94-77</t>
         </is>
       </c>
       <c r="U96" s="7" t="inlineStr">
@@ -9609,7 +9873,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -9676,7 +9940,7 @@
       </c>
       <c r="T98" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 042-82-25</t>
         </is>
       </c>
       <c r="U98" s="15" t="inlineStr">
@@ -9711,7 +9975,11 @@
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr"/>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -9791,7 +10059,11 @@
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr">
         <is>
@@ -9875,7 +10147,11 @@
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr"/>
-      <c r="E101" s="11" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="F101" s="11" t="inlineStr"/>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -9955,7 +10231,11 @@
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr">
         <is>
@@ -10045,7 +10325,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -10120,7 +10400,7 @@
       </c>
       <c r="T103" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 619-02-15</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -10157,7 +10437,7 @@
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -10224,7 +10504,7 @@
       </c>
       <c r="T104" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 709-08-76</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
@@ -10259,7 +10539,11 @@
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -10349,7 +10633,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -10424,7 +10708,7 @@
       </c>
       <c r="T106" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 76 310-47-70 / +998 73 210-47-70 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U106" s="7" t="inlineStr">
@@ -10459,7 +10743,11 @@
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr"/>
-      <c r="E107" s="11" t="inlineStr"/>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr">
         <is>
@@ -10545,7 +10833,7 @@
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>392</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
@@ -10612,8 +10900,10 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T108" s="5" t="n">
-        <v>2017</v>
+      <c r="T108" s="5" t="inlineStr">
+        <is>
+          <t>+998 99 186-30-23 / +998 99 186-30-23 (O'zi)</t>
+        </is>
       </c>
       <c r="U108" s="7" t="inlineStr">
         <is>
@@ -10647,7 +10937,11 @@
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr"/>
-      <c r="E109" s="11" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
       <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="11" t="inlineStr">
         <is>
@@ -10731,7 +11025,11 @@
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
       <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr">
         <is>
@@ -10815,7 +11113,11 @@
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr"/>
-      <c r="E111" s="11" t="inlineStr"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="11" t="inlineStr">
         <is>
@@ -10899,7 +11201,11 @@
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
       <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -10985,7 +11291,7 @@
       <c r="D113" s="10" t="inlineStr"/>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -11060,7 +11366,7 @@
       </c>
       <c r="T113" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>+998 70 518-05-60 / +998 99 730-77-09 (Onasi)</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
@@ -11095,7 +11401,11 @@
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr">
         <is>
@@ -11181,7 +11491,7 @@
       <c r="D115" s="10" t="inlineStr"/>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F115" s="18" t="n">
@@ -11250,7 +11560,7 @@
       </c>
       <c r="T115" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>+998 99 153-48-38 / +998 70 034-22-44 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
@@ -11285,7 +11595,11 @@
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr">
         <is>
@@ -11375,7 +11689,7 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -11450,7 +11764,7 @@
       </c>
       <c r="T117" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 005-29-65 / +998 87 486-12-08 (Onasi)</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -11491,7 +11805,7 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -11562,7 +11876,7 @@
       </c>
       <c r="T118" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 76 294-50-80 / +998 87 381-98-20 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U118" s="7" t="inlineStr">
@@ -11603,7 +11917,7 @@
       <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -11666,7 +11980,7 @@
       </c>
       <c r="T119" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 587-79-09</t>
         </is>
       </c>
       <c r="U119" s="17" t="inlineStr">
@@ -11701,7 +12015,11 @@
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr">
         <is>
@@ -11795,7 +12113,7 @@
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F121" s="18" t="n">
@@ -11868,7 +12186,7 @@
       </c>
       <c r="T121" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 88 388-93-26 / +998 99 685-13-21 (O'zi)</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -11905,7 +12223,7 @@
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -11980,7 +12298,7 @@
       </c>
       <c r="T122" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 010-26-21 / +998 97 701-17-83 (Onasi)</t>
         </is>
       </c>
       <c r="U122" s="7" t="inlineStr">
@@ -12021,7 +12339,7 @@
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -12096,7 +12414,7 @@
       </c>
       <c r="T123" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 005-49-08 / +998 93 553-33-51 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -12141,7 +12459,7 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -12208,7 +12526,7 @@
       </c>
       <c r="T124" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 568-15-08 / +998 88 585-70-68 (Otasi)</t>
         </is>
       </c>
       <c r="U124" s="15" t="inlineStr">
@@ -12243,7 +12561,11 @@
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -12307,7 +12629,11 @@
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -12389,7 +12715,7 @@
       <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>288</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
@@ -12464,7 +12790,7 @@
       </c>
       <c r="T127" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 335-05-82 / +998 97 863-50-82 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
@@ -12503,7 +12829,11 @@
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr">
         <is>
@@ -12587,7 +12917,11 @@
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr"/>
-      <c r="E129" s="11" t="inlineStr"/>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
       <c r="F129" s="11" t="inlineStr"/>
       <c r="G129" s="11" t="inlineStr">
         <is>
@@ -12685,7 +13019,7 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -12760,7 +13094,7 @@
       </c>
       <c r="T130" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 91 217-70-09 / +998 91 460-65-62 (Akasi)</t>
         </is>
       </c>
       <c r="U130" s="7" t="inlineStr">
@@ -12795,7 +13129,11 @@
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr"/>
-      <c r="E131" s="11" t="inlineStr"/>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
       <c r="F131" s="11" t="inlineStr"/>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -12879,7 +13217,11 @@
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="F132" s="5" t="inlineStr"/>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -12963,7 +13305,11 @@
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr"/>
-      <c r="E133" s="11" t="inlineStr"/>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="F133" s="11" t="inlineStr"/>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -13053,7 +13399,7 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -13124,7 +13470,7 @@
       </c>
       <c r="T134" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 495-26-08 / +998 97 387-38-03 (Onasi)</t>
         </is>
       </c>
       <c r="U134" s="17" t="inlineStr">
@@ -13159,7 +13505,11 @@
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="F135" s="11" t="inlineStr"/>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -13239,7 +13589,11 @@
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
       <c r="F136" s="5" t="inlineStr"/>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -13319,7 +13673,11 @@
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
       <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="11" t="inlineStr">
         <is>
@@ -13405,7 +13763,7 @@
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F138" s="12" t="n">
@@ -13478,7 +13836,7 @@
       </c>
       <c r="T138" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 95 259-06-25 / +998 99 152-33-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U138" s="7" t="inlineStr">
@@ -13513,7 +13871,11 @@
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr"/>
-      <c r="E139" s="11" t="inlineStr"/>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
@@ -13597,7 +13959,11 @@
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
       <c r="F140" s="5" t="inlineStr"/>
       <c r="G140" s="5" t="inlineStr">
         <is>
@@ -13681,7 +14047,11 @@
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr"/>
-      <c r="E141" s="11" t="inlineStr"/>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
       <c r="F141" s="11" t="inlineStr"/>
       <c r="G141" s="11" t="inlineStr">
         <is>
@@ -13765,7 +14135,11 @@
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
       <c r="F142" s="5" t="inlineStr"/>
       <c r="G142" s="5" t="inlineStr">
         <is>
@@ -13849,7 +14223,11 @@
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr"/>
-      <c r="E143" s="11" t="inlineStr"/>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
       <c r="F143" s="11" t="inlineStr"/>
       <c r="G143" s="11" t="inlineStr">
         <is>
@@ -13939,7 +14317,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>280</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -14010,7 +14388,7 @@
       </c>
       <c r="T144" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 115-10-31 / +998 88 184-05-85 (Onasi)</t>
         </is>
       </c>
       <c r="U144" s="7" t="inlineStr">
@@ -14053,7 +14431,11 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E145" s="11" t="inlineStr"/>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
       <c r="F145" s="11" t="inlineStr"/>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -14145,7 +14527,11 @@
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="F146" s="5" t="inlineStr"/>
       <c r="G146" s="5" t="inlineStr">
         <is>
@@ -14229,7 +14615,11 @@
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr"/>
-      <c r="E147" s="11" t="inlineStr"/>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
       <c r="F147" s="11" t="inlineStr"/>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -14315,7 +14705,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -14388,11 +14778,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T148" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T148" s="5" t="inlineStr"/>
       <c r="U148" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -14425,7 +14811,11 @@
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -14509,7 +14899,11 @@
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
       <c r="F150" s="5" t="inlineStr"/>
       <c r="G150" s="5" t="inlineStr">
         <is>
@@ -14599,7 +14993,7 @@
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
@@ -14670,7 +15064,7 @@
       </c>
       <c r="T151" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 83 403-00-80 / +998 95 264-70-90 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -14709,7 +15103,11 @@
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
       <c r="F152" s="5" t="inlineStr"/>
       <c r="G152" s="5" t="inlineStr">
         <is>
@@ -14799,7 +15197,7 @@
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -14866,7 +15264,7 @@
       </c>
       <c r="T153" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 81 831-16-70 / +998 18 311-67-87 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
@@ -14911,7 +15309,7 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr"/>
@@ -14974,7 +15372,7 @@
       </c>
       <c r="T154" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>+998 87 358-87-97 / +998 88 632-19-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U154" s="5" t="inlineStr"/>
@@ -15001,7 +15399,11 @@
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr"/>
-      <c r="E155" s="11" t="inlineStr"/>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
       <c r="F155" s="11" t="inlineStr"/>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -15091,7 +15493,7 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -15166,7 +15568,7 @@
       </c>
       <c r="T156" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 79 347-60-80 / +998 91 456-46-61 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U156" s="7" t="inlineStr">
@@ -15201,7 +15603,11 @@
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr"/>
-      <c r="E157" s="11" t="inlineStr"/>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
       <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr">
         <is>
@@ -15281,7 +15687,11 @@
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="5" t="inlineStr"/>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
       <c r="F158" s="5" t="inlineStr"/>
       <c r="G158" s="5" t="inlineStr">
         <is>
@@ -15365,7 +15775,11 @@
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr"/>
-      <c r="E159" s="11" t="inlineStr"/>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
       <c r="F159" s="11" t="inlineStr"/>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -15455,7 +15869,7 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -15530,7 +15944,7 @@
       </c>
       <c r="T160" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 618-02-59</t>
         </is>
       </c>
       <c r="U160" s="7" t="inlineStr">
@@ -15565,7 +15979,11 @@
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr"/>
-      <c r="E161" s="11" t="inlineStr"/>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
       <c r="F161" s="11" t="inlineStr"/>
       <c r="G161" s="11" t="inlineStr">
         <is>
@@ -15655,7 +16073,7 @@
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>232</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -15730,7 +16148,7 @@
       </c>
       <c r="T162" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 952-43-44 / +998 90 442-22-47 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U162" s="7" t="inlineStr">
@@ -15771,7 +16189,7 @@
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
@@ -15834,7 +16252,7 @@
       </c>
       <c r="T163" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 00 111-40-90 / +998 97 389-11-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U163" s="17" t="inlineStr">
@@ -15875,7 +16293,7 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -15950,7 +16368,7 @@
       </c>
       <c r="T164" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 811-22-08 / +998 91 815-13-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U164" s="7" t="inlineStr">
@@ -15985,7 +16403,11 @@
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr"/>
-      <c r="E165" s="11" t="inlineStr"/>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
       <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr">
         <is>
@@ -16075,7 +16497,7 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -16150,7 +16572,7 @@
       </c>
       <c r="T166" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 80 880-12-40 / +998 15 613-00-20 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U166" s="7" t="inlineStr">
@@ -16185,7 +16607,11 @@
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr"/>
-      <c r="E167" s="11" t="inlineStr"/>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
       <c r="F167" s="11" t="inlineStr"/>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -16269,7 +16695,11 @@
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="5" t="inlineStr"/>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
       <c r="F168" s="5" t="inlineStr"/>
       <c r="G168" s="5" t="inlineStr">
         <is>
@@ -16349,7 +16779,11 @@
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr"/>
-      <c r="E169" s="11" t="inlineStr"/>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="F169" s="11" t="inlineStr"/>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -16433,7 +16867,11 @@
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="5" t="inlineStr"/>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
       <c r="F170" s="5" t="inlineStr"/>
       <c r="G170" s="5" t="inlineStr">
         <is>
@@ -16517,7 +16955,11 @@
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr"/>
-      <c r="E171" s="11" t="inlineStr"/>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
       <c r="F171" s="11" t="inlineStr"/>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -16607,7 +17049,7 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -16682,7 +17124,7 @@
       </c>
       <c r="T172" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 50 202-81-30 / +998 72 752-81-30 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U172" s="7" t="inlineStr">
@@ -16723,7 +17165,7 @@
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -16794,7 +17236,7 @@
       </c>
       <c r="T173" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 97 852-74-04 / +998 97 852-74-04 (O'zi)</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -16833,7 +17275,11 @@
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="5" t="inlineStr"/>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
       <c r="F174" s="5" t="inlineStr"/>
       <c r="G174" s="5" t="inlineStr">
         <is>
@@ -16921,7 +17367,11 @@
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr"/>
-      <c r="E175" s="11" t="inlineStr"/>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
       <c r="F175" s="11" t="inlineStr"/>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -16987,7 +17437,7 @@
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -17058,7 +17508,7 @@
       </c>
       <c r="T176" s="5" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>+998 59 399-20-50 / +998 52 332-76-60 (Qaynonasi)</t>
         </is>
       </c>
       <c r="U176" s="7" t="inlineStr">
@@ -17256,11 +17706,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T178" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="T178" s="5" t="inlineStr"/>
       <c r="U178" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -17297,7 +17743,11 @@
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr"/>
-      <c r="E179" s="11" t="inlineStr"/>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="F179" s="11" t="inlineStr"/>
       <c r="G179" s="11" t="inlineStr">
         <is>
@@ -17633,7 +18083,11 @@
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr"/>
-      <c r="E183" s="11" t="inlineStr"/>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="F183" s="11" t="inlineStr"/>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -17723,7 +18177,7 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
@@ -17798,7 +18252,7 @@
       </c>
       <c r="T184" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 70 034-95-05 / +998 99 468-84-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U184" s="7" t="inlineStr">
@@ -17898,7 +18352,7 @@
       </c>
       <c r="T185" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 04 403-66-60 / +998 12 247-72-10 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U185" s="17" t="inlineStr">
@@ -18342,7 +18796,7 @@
       </c>
       <c r="T190" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 70 120-65-08 / +998 99 569-81-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U190" s="7" t="inlineStr">
@@ -18538,7 +18992,7 @@
       </c>
       <c r="T192" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 99 673-99-29 / +998 99 673-99-29 (O'zi)</t>
         </is>
       </c>
       <c r="U192" s="7" t="inlineStr">
@@ -18646,7 +19100,7 @@
       </c>
       <c r="T193" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 88 384-85-45</t>
         </is>
       </c>
       <c r="U193" s="11" t="inlineStr"/>
@@ -18836,7 +19290,7 @@
       </c>
       <c r="T195" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 90 815-25-00 / +998 94 817-01-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
@@ -18952,7 +19406,7 @@
       </c>
       <c r="T196" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 33 296-07-08 / +998 88 136-09-26 (Onasi)</t>
         </is>
       </c>
       <c r="U196" s="7" t="inlineStr">
@@ -19208,7 +19662,7 @@
       </c>
       <c r="T199" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 91 810-81-91 / +998 90 099-57-63 (Onasi)</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
@@ -19660,7 +20114,7 @@
       </c>
       <c r="T204" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 732-61-11 / +998 90 617-68-83 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U204" s="7" t="inlineStr">
@@ -19766,7 +20220,7 @@
       <c r="S205" s="11" t="inlineStr"/>
       <c r="T205" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 04 504-24-00 / +998 93 903-47-44 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U205" s="15" t="inlineStr">
@@ -19958,7 +20412,7 @@
       </c>
       <c r="T207" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 217-14-30 / +998 94 134-34-03 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
@@ -20074,7 +20528,7 @@
       </c>
       <c r="T208" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 18 440-30-80 / +998 19 594-21-50 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U208" s="7" t="inlineStr">
@@ -20272,8 +20726,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T210" s="5" t="n">
-        <v>2026</v>
+      <c r="T210" s="5" t="inlineStr">
+        <is>
+          <t>+998 91 464-92-28 / +998 88 601-52-00 (Onasi)</t>
+        </is>
       </c>
       <c r="U210" s="7" t="inlineStr">
         <is>
@@ -20472,7 +20928,7 @@
       </c>
       <c r="T212" s="5" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>+998 88 388-93-26 / +998 99 685-13-21 (O'zi)</t>
         </is>
       </c>
       <c r="U212" s="7" t="inlineStr">
@@ -20672,7 +21128,7 @@
       </c>
       <c r="T214" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 72 130-24-00 / +998 86 188-58-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U214" s="7" t="inlineStr">
@@ -21362,7 +21818,7 @@
       </c>
       <c r="T222" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>+998 16 354-55-60 / +998 95 333-29-60 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U222" s="7" t="inlineStr">
@@ -21714,7 +22170,7 @@
       </c>
       <c r="T226" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 716-01-30 / +998 88 388-79-12 (Onasi)</t>
         </is>
       </c>
       <c r="U226" s="7" t="inlineStr">
@@ -22078,7 +22534,7 @@
       </c>
       <c r="T230" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 217-70-09 / +998 91 460-65-62 (Akasi)</t>
         </is>
       </c>
       <c r="U230" s="7" t="inlineStr">
@@ -22278,7 +22734,7 @@
       </c>
       <c r="T232" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 463-79-08 / +998 10 709-57-90 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U232" s="7" t="inlineStr">
@@ -22388,11 +22844,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T233" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="T233" s="11" t="inlineStr"/>
       <c r="U233" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -22683,7 +23135,7 @@
       </c>
       <c r="E237" s="11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26/27 Sh/A 268</t>
         </is>
       </c>
       <c r="F237" s="11" t="inlineStr">
@@ -22752,8 +23204,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T237" s="11" t="n">
-        <v>2009</v>
+      <c r="T237" s="11" t="inlineStr">
+        <is>
+          <t>+998 88 803-91-93 / +998 88 726-14-12 (Otasi / Onasi)</t>
+        </is>
       </c>
       <c r="U237" s="7" t="inlineStr">
         <is>
@@ -22793,7 +23247,7 @@
       <c r="D238" s="4" t="inlineStr"/>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>26/27 SH/A 216</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
@@ -22862,11 +23316,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T238" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T238" s="5" t="inlineStr"/>
       <c r="U238" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -22905,7 +23355,7 @@
       <c r="D239" s="10" t="inlineStr"/>
       <c r="E239" s="11" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>26/27 SH/A 33</t>
         </is>
       </c>
       <c r="F239" s="18" t="n">
@@ -22974,7 +23424,7 @@
       </c>
       <c r="T239" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 88 399-00-96</t>
         </is>
       </c>
       <c r="U239" s="7" t="inlineStr">
@@ -23013,7 +23463,11 @@
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr"/>
-      <c r="E240" s="5" t="inlineStr"/>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A269</t>
+        </is>
+      </c>
       <c r="F240" s="5" t="inlineStr"/>
       <c r="G240" s="5" t="inlineStr">
         <is>
@@ -23338,7 +23792,7 @@
       </c>
       <c r="T243" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 76 590-02-70 / +998 70 790-86-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
@@ -23459,7 +23913,7 @@
       <c r="D245" s="10" t="inlineStr"/>
       <c r="E245" s="11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>25/26 sh/a 6</t>
         </is>
       </c>
       <c r="F245" s="18" t="n">
@@ -23528,7 +23982,7 @@
       </c>
       <c r="T245" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 70 188-54-32 / +998 95 805-01-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
@@ -23806,7 +24260,7 @@
       </c>
       <c r="T248" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 625-99-07</t>
         </is>
       </c>
       <c r="U248" s="7" t="inlineStr">
@@ -24000,11 +24454,7 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T250" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="T250" s="5" t="inlineStr"/>
       <c r="U250" s="5" t="inlineStr">
         <is>
           <t>To'liq</t>
@@ -24105,7 +24555,11 @@
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr"/>
-      <c r="E252" s="5" t="inlineStr"/>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 33</t>
+        </is>
+      </c>
       <c r="F252" s="5" t="inlineStr"/>
       <c r="G252" s="5" t="inlineStr">
         <is>
@@ -24189,7 +24643,11 @@
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr"/>
-      <c r="E253" s="11" t="inlineStr"/>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 220</t>
+        </is>
+      </c>
       <c r="F253" s="11" t="inlineStr"/>
       <c r="G253" s="11" t="inlineStr">
         <is>
@@ -24273,7 +24731,11 @@
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr"/>
-      <c r="E254" s="5" t="inlineStr"/>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 277</t>
+        </is>
+      </c>
       <c r="F254" s="5" t="inlineStr"/>
       <c r="G254" s="5" t="inlineStr">
         <is>
@@ -24443,7 +24905,7 @@
       <c r="D256" s="4" t="inlineStr"/>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>25/26 SH/A57</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
@@ -24506,7 +24968,7 @@
       <c r="S256" s="5" t="inlineStr"/>
       <c r="T256" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>+998 91 957-18-58</t>
         </is>
       </c>
       <c r="U256" s="15" t="inlineStr">
@@ -25490,7 +25952,7 @@
       </c>
       <c r="T267" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>+998 73 865-61-20 / +998 73 824-60-60 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U267" s="17" t="inlineStr">
@@ -25778,7 +26240,7 @@
       </c>
       <c r="T270" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 800-66-37 / +998 97 001-27-80 (Onasi)</t>
         </is>
       </c>
       <c r="U270" s="7" t="inlineStr">
@@ -25813,7 +26275,11 @@
         </is>
       </c>
       <c r="D271" s="10" t="inlineStr"/>
-      <c r="E271" s="11" t="inlineStr"/>
+      <c r="E271" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 226</t>
+        </is>
+      </c>
       <c r="F271" s="11" t="inlineStr"/>
       <c r="G271" s="11" t="inlineStr">
         <is>
@@ -25981,7 +26447,11 @@
         </is>
       </c>
       <c r="D273" s="10" t="inlineStr"/>
-      <c r="E273" s="11" t="inlineStr"/>
+      <c r="E273" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A252</t>
+        </is>
+      </c>
       <c r="F273" s="11" t="inlineStr"/>
       <c r="G273" s="11" t="inlineStr">
         <is>
@@ -26045,7 +26515,11 @@
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr"/>
-      <c r="E274" s="5" t="inlineStr"/>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="F274" s="5" t="inlineStr"/>
       <c r="G274" s="5" t="inlineStr">
         <is>
@@ -26129,7 +26603,11 @@
         </is>
       </c>
       <c r="D275" s="10" t="inlineStr"/>
-      <c r="E275" s="11" t="inlineStr"/>
+      <c r="E275" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="F275" s="11" t="inlineStr"/>
       <c r="G275" s="11" t="inlineStr">
         <is>
@@ -26284,11 +26762,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T276" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T276" s="5" t="inlineStr"/>
       <c r="U276" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -26321,7 +26795,11 @@
         </is>
       </c>
       <c r="D277" s="10" t="inlineStr"/>
-      <c r="E277" s="11" t="inlineStr"/>
+      <c r="E277" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 286</t>
+        </is>
+      </c>
       <c r="F277" s="11" t="inlineStr"/>
       <c r="G277" s="11" t="inlineStr">
         <is>
@@ -27050,7 +27528,7 @@
       </c>
       <c r="T285" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 99 819-11-07</t>
         </is>
       </c>
       <c r="U285" s="7" t="inlineStr">
@@ -27166,7 +27644,7 @@
       </c>
       <c r="T286" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 607-08-24 / +998 73 990-17-90 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U286" s="7" t="inlineStr">
@@ -27260,11 +27738,7 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T287" s="11" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
+      <c r="T287" s="11" t="inlineStr"/>
       <c r="U287" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -27372,11 +27846,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T288" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T288" s="5" t="inlineStr"/>
       <c r="U288" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -27419,7 +27889,7 @@
       </c>
       <c r="E289" s="11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>26/27 SH/A 288</t>
         </is>
       </c>
       <c r="F289" s="11" t="inlineStr">
@@ -27494,7 +27964,7 @@
       </c>
       <c r="T289" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 70 108-08-29 / +998 99 246-08-29 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U289" s="7" t="inlineStr">
@@ -27789,7 +28259,11 @@
         </is>
       </c>
       <c r="D293" s="10" t="inlineStr"/>
-      <c r="E293" s="11" t="inlineStr"/>
+      <c r="E293" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 259</t>
+        </is>
+      </c>
       <c r="F293" s="11" t="inlineStr"/>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -27873,7 +28347,11 @@
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr"/>
-      <c r="E294" s="5" t="inlineStr"/>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 235</t>
+        </is>
+      </c>
       <c r="F294" s="5" t="inlineStr"/>
       <c r="G294" s="5" t="inlineStr">
         <is>
@@ -28198,7 +28676,7 @@
       </c>
       <c r="T297" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>+998 91 949-16-27 / +998 90 069-89-98 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U297" s="7" t="inlineStr">
@@ -28449,7 +28927,11 @@
         </is>
       </c>
       <c r="D301" s="10" t="inlineStr"/>
-      <c r="E301" s="11" t="inlineStr"/>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 239</t>
+        </is>
+      </c>
       <c r="F301" s="11" t="inlineStr"/>
       <c r="G301" s="11" t="inlineStr">
         <is>
@@ -28533,7 +29015,11 @@
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr"/>
-      <c r="E302" s="5" t="inlineStr"/>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>24/25 SH/A 41</t>
+        </is>
+      </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
           <t>2026-09-08 00:00:00</t>
@@ -28887,7 +29373,7 @@
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>26/27 SH/A 241</t>
         </is>
       </c>
       <c r="F306" s="5" t="inlineStr">
@@ -28958,7 +29444,7 @@
       </c>
       <c r="T306" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>+998 88 829-82-80 / +998 88 303-82-80 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U306" s="7" t="inlineStr">
@@ -29216,7 +29702,7 @@
       </c>
       <c r="T309" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 99 106-08-10 / +998 95 527-81-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U309" s="7" t="inlineStr">
@@ -29414,11 +29900,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T311" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T311" s="11" t="inlineStr"/>
       <c r="U311" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -29457,7 +29939,7 @@
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>25/26 SH/A 286</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
@@ -29532,7 +30014,7 @@
       </c>
       <c r="T312" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 90 453-21-25</t>
         </is>
       </c>
       <c r="U312" s="7" t="inlineStr">
@@ -29819,7 +30301,11 @@
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr"/>
-      <c r="E316" s="5" t="inlineStr"/>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 506</t>
+        </is>
+      </c>
       <c r="F316" s="5" t="inlineStr"/>
       <c r="G316" s="5" t="inlineStr">
         <is>
@@ -29980,7 +30466,7 @@
       </c>
       <c r="T317" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 90 884-12-08 / +998 91 957-27-17 (Akasi)</t>
         </is>
       </c>
       <c r="U317" s="7" t="inlineStr">
@@ -30105,7 +30591,7 @@
       </c>
       <c r="E319" s="11" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>25/26 Sh/A509</t>
         </is>
       </c>
       <c r="F319" s="11" t="inlineStr">
@@ -30172,7 +30658,7 @@
       </c>
       <c r="T319" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 87 392-00-25 / +998 87 392-00-21 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U319" s="17" t="inlineStr">
@@ -30540,7 +31026,7 @@
       </c>
       <c r="T323" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 93 356-50-22 / +998 91 090-16-27 (Onasi)</t>
         </is>
       </c>
       <c r="U323" s="7" t="inlineStr">
@@ -30904,7 +31390,7 @@
       </c>
       <c r="T327" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>+998 88 387-94-04 / +998 88 381-39-79 (Onasi)</t>
         </is>
       </c>
       <c r="U327" s="15" t="inlineStr">
@@ -31096,7 +31582,7 @@
       </c>
       <c r="T329" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 632-37-73 / +998 91 470-84-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U329" s="15" t="inlineStr">
@@ -31135,7 +31621,11 @@
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr"/>
-      <c r="E330" s="5" t="inlineStr"/>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 520</t>
+        </is>
+      </c>
       <c r="F330" s="5" t="inlineStr"/>
       <c r="G330" s="5" t="inlineStr">
         <is>
@@ -31567,7 +32057,11 @@
         </is>
       </c>
       <c r="D335" s="10" t="inlineStr"/>
-      <c r="E335" s="11" t="inlineStr"/>
+      <c r="E335" s="11" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 186</t>
+        </is>
+      </c>
       <c r="F335" s="11" t="inlineStr"/>
       <c r="G335" s="11" t="inlineStr">
         <is>
@@ -31735,7 +32229,11 @@
         </is>
       </c>
       <c r="D337" s="10" t="inlineStr"/>
-      <c r="E337" s="11" t="inlineStr"/>
+      <c r="E337" s="11" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 116</t>
+        </is>
+      </c>
       <c r="F337" s="11" t="inlineStr"/>
       <c r="G337" s="11" t="inlineStr">
         <is>
@@ -31984,7 +32482,7 @@
       </c>
       <c r="T339" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 08 785-10-50 / +998 16 397-68-50 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U339" s="7" t="inlineStr">
@@ -32695,7 +33193,11 @@
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr"/>
-      <c r="E348" s="5" t="inlineStr"/>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 327</t>
+        </is>
+      </c>
       <c r="F348" s="5" t="inlineStr"/>
       <c r="G348" s="5" t="inlineStr">
         <is>
@@ -33124,7 +33626,7 @@
       </c>
       <c r="T352" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>+998 50 158-27-29 / +998 99 730-48-04 (Onasi)</t>
         </is>
       </c>
       <c r="U352" s="7" t="inlineStr">
@@ -33406,11 +33908,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T355" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T355" s="11" t="inlineStr"/>
       <c r="U355" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -33848,7 +34346,7 @@
       </c>
       <c r="T360" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 387-28-25 / +998 91 218-44-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U360" s="17" t="inlineStr">
@@ -34044,7 +34542,7 @@
       </c>
       <c r="T362" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 90 677-80-76</t>
         </is>
       </c>
       <c r="U362" s="7" t="inlineStr">
@@ -34083,7 +34581,11 @@
         </is>
       </c>
       <c r="D363" s="10" t="inlineStr"/>
-      <c r="E363" s="11" t="inlineStr"/>
+      <c r="E363" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 15</t>
+        </is>
+      </c>
       <c r="F363" s="11" t="inlineStr"/>
       <c r="G363" s="11" t="inlineStr">
         <is>
@@ -34238,8 +34740,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T364" s="5" t="n">
-        <v>2026</v>
+      <c r="T364" s="5" t="inlineStr">
+        <is>
+          <t>+998 88 063-26-08 / +998 97 336-01-40 (Otasi / Onasi)</t>
+        </is>
       </c>
       <c r="U364" s="7" t="inlineStr">
         <is>
@@ -34277,7 +34781,11 @@
         </is>
       </c>
       <c r="D365" s="10" t="inlineStr"/>
-      <c r="E365" s="11" t="inlineStr"/>
+      <c r="E365" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 10</t>
+        </is>
+      </c>
       <c r="F365" s="11" t="inlineStr"/>
       <c r="G365" s="11" t="inlineStr">
         <is>
@@ -34774,7 +35282,7 @@
       </c>
       <c r="T370" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 79 656-30-80 / +998 71 390-67-70 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U370" s="7" t="inlineStr">
@@ -34809,7 +35317,11 @@
         </is>
       </c>
       <c r="D371" s="10" t="inlineStr"/>
-      <c r="E371" s="11" t="inlineStr"/>
+      <c r="E371" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A84</t>
+        </is>
+      </c>
       <c r="F371" s="11" t="inlineStr"/>
       <c r="G371" s="11" t="inlineStr">
         <is>
@@ -35040,11 +35552,7 @@
         </is>
       </c>
       <c r="S373" s="11" t="inlineStr"/>
-      <c r="T373" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T373" s="11" t="inlineStr"/>
       <c r="U373" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -35245,7 +35753,11 @@
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr"/>
-      <c r="E376" s="5" t="inlineStr"/>
+      <c r="E376" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 26</t>
+        </is>
+      </c>
       <c r="F376" s="5" t="inlineStr"/>
       <c r="G376" s="5" t="inlineStr">
         <is>
@@ -35413,7 +35925,11 @@
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr"/>
-      <c r="E378" s="5" t="inlineStr"/>
+      <c r="E378" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 28</t>
+        </is>
+      </c>
       <c r="F378" s="5" t="inlineStr"/>
       <c r="G378" s="5" t="inlineStr">
         <is>
@@ -35574,7 +36090,7 @@
       </c>
       <c r="T379" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>+998 16 354-55-60 / +998 95 333-29-60 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U379" s="7" t="inlineStr">
@@ -35615,7 +36131,7 @@
       </c>
       <c r="E380" s="5" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>25/26 Sh/A 107</t>
         </is>
       </c>
       <c r="F380" s="5" t="inlineStr"/>
@@ -35674,7 +36190,7 @@
       </c>
       <c r="T380" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>+998 91 219-20-99</t>
         </is>
       </c>
       <c r="U380" s="7" t="inlineStr">
@@ -35950,7 +36466,7 @@
       </c>
       <c r="T383" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 05 030-53-90 / +998 91 951-05-36 (Akasi)</t>
         </is>
       </c>
       <c r="U383" s="15" t="inlineStr">
@@ -36066,7 +36582,7 @@
       </c>
       <c r="T384" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 558-15-35 / +998 88 633-15-35 (Onasi)</t>
         </is>
       </c>
       <c r="U384" s="15" t="inlineStr">
@@ -36174,7 +36690,7 @@
       </c>
       <c r="T385" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 88 606-15-00 / +998 76 150-09-19 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U385" s="7" t="inlineStr">
@@ -36369,7 +36885,11 @@
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr"/>
-      <c r="E388" s="5" t="inlineStr"/>
+      <c r="E388" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A40</t>
+        </is>
+      </c>
       <c r="F388" s="5" t="inlineStr"/>
       <c r="G388" s="5" t="inlineStr">
         <is>
@@ -36618,7 +37138,7 @@
       </c>
       <c r="T390" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 597-09-64</t>
         </is>
       </c>
       <c r="U390" s="7" t="inlineStr">
@@ -36922,7 +37442,7 @@
       </c>
       <c r="T393" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 31 522-57-70 / +998 77 086-77-25 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U393" s="7" t="inlineStr">
@@ -37206,7 +37726,7 @@
       </c>
       <c r="T396" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 000-14-58 / +998 90 517-61-63 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U396" s="7" t="inlineStr">
@@ -37325,7 +37845,11 @@
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr"/>
-      <c r="E398" s="5" t="inlineStr"/>
+      <c r="E398" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 140</t>
+        </is>
+      </c>
       <c r="F398" s="5" t="inlineStr"/>
       <c r="G398" s="5" t="inlineStr">
         <is>
@@ -37411,7 +37935,7 @@
       <c r="D399" s="10" t="inlineStr"/>
       <c r="E399" s="11" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>25/26 SH/A149</t>
         </is>
       </c>
       <c r="F399" s="11" t="inlineStr">
@@ -37484,11 +38008,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T399" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T399" s="11" t="inlineStr"/>
       <c r="U399" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -37859,7 +38379,7 @@
       </c>
       <c r="E404" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>25/26 Sh/A 142</t>
         </is>
       </c>
       <c r="F404" s="5" t="inlineStr">
@@ -37934,7 +38454,7 @@
       </c>
       <c r="T404" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 94 082-51-16</t>
         </is>
       </c>
       <c r="U404" s="7" t="inlineStr">
@@ -37969,7 +38489,11 @@
         </is>
       </c>
       <c r="D405" s="10" t="inlineStr"/>
-      <c r="E405" s="11" t="inlineStr"/>
+      <c r="E405" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A150</t>
+        </is>
+      </c>
       <c r="F405" s="11" t="inlineStr"/>
       <c r="G405" s="11" t="inlineStr">
         <is>
@@ -38386,7 +38910,7 @@
       </c>
       <c r="T409" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 91 802-16-70 / +998 91 961-40-37 (Onasi)</t>
         </is>
       </c>
       <c r="U409" s="7" t="inlineStr">
@@ -38733,7 +39257,11 @@
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr"/>
-      <c r="E414" s="5" t="inlineStr"/>
+      <c r="E414" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A66</t>
+        </is>
+      </c>
       <c r="F414" s="5" t="inlineStr"/>
       <c r="G414" s="5" t="inlineStr">
         <is>
@@ -39418,7 +39946,7 @@
       </c>
       <c r="T421" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 085-06-27 / +998 88 085-06-27 (Onasi)</t>
         </is>
       </c>
       <c r="U421" s="7" t="inlineStr">
@@ -39537,7 +40065,11 @@
         </is>
       </c>
       <c r="D423" s="10" t="inlineStr"/>
-      <c r="E423" s="11" t="inlineStr"/>
+      <c r="E423" s="11" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 74</t>
+        </is>
+      </c>
       <c r="F423" s="11" t="inlineStr"/>
       <c r="G423" s="11" t="inlineStr">
         <is>
@@ -39698,7 +40230,7 @@
       </c>
       <c r="T424" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 70 478-58-08 / +998 88 753-84-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U424" s="7" t="inlineStr">
@@ -39823,7 +40355,7 @@
       </c>
       <c r="E426" s="5" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>26/27 SH/A 76</t>
         </is>
       </c>
       <c r="F426" s="5" t="inlineStr">
@@ -39884,11 +40416,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T426" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="T426" s="5" t="inlineStr"/>
       <c r="U426" s="17" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -40009,7 +40537,11 @@
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr"/>
-      <c r="E428" s="5" t="inlineStr"/>
+      <c r="E428" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 78</t>
+        </is>
+      </c>
       <c r="F428" s="5" t="inlineStr"/>
       <c r="G428" s="5" t="inlineStr">
         <is>
@@ -40097,7 +40629,11 @@
         </is>
       </c>
       <c r="D429" s="10" t="inlineStr"/>
-      <c r="E429" s="11" t="inlineStr"/>
+      <c r="E429" s="11" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A79</t>
+        </is>
+      </c>
       <c r="F429" s="11" t="inlineStr"/>
       <c r="G429" s="11" t="inlineStr">
         <is>
@@ -40250,8 +40786,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T430" s="5" t="n">
-        <v>2026</v>
+      <c r="T430" s="5" t="inlineStr">
+        <is>
+          <t>+998 90 878-02-80 / +998 95 269-48-78 (Onasi)</t>
+        </is>
       </c>
       <c r="U430" s="7" t="inlineStr">
         <is>
@@ -40360,11 +40898,7 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T431" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="T431" s="11" t="inlineStr"/>
       <c r="U431" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -40401,7 +40935,11 @@
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr"/>
-      <c r="E432" s="5" t="inlineStr"/>
+      <c r="E432" s="5" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 385</t>
+        </is>
+      </c>
       <c r="F432" s="5" t="inlineStr"/>
       <c r="G432" s="5" t="inlineStr">
         <is>
@@ -40677,7 +41215,11 @@
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr"/>
-      <c r="E436" s="5" t="inlineStr"/>
+      <c r="E436" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 159</t>
+        </is>
+      </c>
       <c r="F436" s="5" t="inlineStr"/>
       <c r="G436" s="5" t="inlineStr">
         <is>
@@ -40761,7 +41303,11 @@
         </is>
       </c>
       <c r="D437" s="10" t="inlineStr"/>
-      <c r="E437" s="11" t="inlineStr"/>
+      <c r="E437" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 177</t>
+        </is>
+      </c>
       <c r="F437" s="11" t="inlineStr"/>
       <c r="G437" s="11" t="inlineStr">
         <is>
@@ -40926,7 +41472,7 @@
       </c>
       <c r="T438" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 88 336-77-74 / +998 90 716-31-42 (Onasi)</t>
         </is>
       </c>
       <c r="U438" s="7" t="inlineStr">
@@ -41034,7 +41580,7 @@
       </c>
       <c r="T439" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 95 583-88-58 / +998 91 641-75-32 (Onasi)</t>
         </is>
       </c>
       <c r="U439" s="17" t="inlineStr">
@@ -41321,7 +41867,11 @@
         </is>
       </c>
       <c r="D443" s="10" t="inlineStr"/>
-      <c r="E443" s="11" t="inlineStr"/>
+      <c r="E443" s="11" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A94</t>
+        </is>
+      </c>
       <c r="F443" s="11" t="inlineStr"/>
       <c r="G443" s="11" t="inlineStr">
         <is>
@@ -41566,7 +42116,7 @@
       </c>
       <c r="T445" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 586-06-97 / +998 88 585-14-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U445" s="7" t="inlineStr">
@@ -41601,7 +42151,11 @@
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr"/>
-      <c r="E446" s="5" t="inlineStr"/>
+      <c r="E446" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 98</t>
+        </is>
+      </c>
       <c r="F446" s="5" t="inlineStr"/>
       <c r="G446" s="5" t="inlineStr">
         <is>
@@ -41739,7 +42293,7 @@
       </c>
       <c r="E448" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26/27 sh/a 100</t>
         </is>
       </c>
       <c r="F448" s="5" t="inlineStr">
@@ -41806,7 +42360,7 @@
       </c>
       <c r="T448" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>+998 91 464-92-28 / +998 88 601-52-00 (Onasi)</t>
         </is>
       </c>
       <c r="U448" s="7" t="inlineStr">
@@ -42005,7 +42559,11 @@
         </is>
       </c>
       <c r="D451" s="10" t="inlineStr"/>
-      <c r="E451" s="11" t="inlineStr"/>
+      <c r="E451" s="11" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 103</t>
+        </is>
+      </c>
       <c r="F451" s="11" t="inlineStr"/>
       <c r="G451" s="11" t="inlineStr">
         <is>
@@ -42166,7 +42724,7 @@
       </c>
       <c r="T452" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>+998 94 333-76-08 / +998 94 330-22-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U452" s="7" t="inlineStr">
@@ -42207,7 +42765,7 @@
       </c>
       <c r="E453" s="11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>26/27 SH/A105</t>
         </is>
       </c>
       <c r="F453" s="11" t="inlineStr">
@@ -42282,7 +42840,7 @@
       </c>
       <c r="T453" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 485-36-08 / +998 97 188-07-57 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U453" s="7" t="inlineStr">
@@ -42317,7 +42875,11 @@
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr"/>
-      <c r="E454" s="5" t="inlineStr"/>
+      <c r="E454" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A106</t>
+        </is>
+      </c>
       <c r="F454" s="5" t="inlineStr"/>
       <c r="G454" s="5" t="inlineStr">
         <is>
@@ -42407,7 +42969,7 @@
       </c>
       <c r="E455" s="11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>25/26 SH/A 229</t>
         </is>
       </c>
       <c r="F455" s="11" t="inlineStr">
@@ -42472,11 +43034,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T455" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T455" s="11" t="inlineStr"/>
       <c r="U455" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -42902,7 +43460,7 @@
       </c>
       <c r="T460" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 633-04-14 / +998 91 470-59-57 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U460" s="7" t="inlineStr">
@@ -43016,11 +43574,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T461" s="11" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="T461" s="11" t="inlineStr"/>
       <c r="U461" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -43053,7 +43607,11 @@
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr"/>
-      <c r="E462" s="5" t="inlineStr"/>
+      <c r="E462" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A114</t>
+        </is>
+      </c>
       <c r="F462" s="5" t="inlineStr"/>
       <c r="G462" s="5" t="inlineStr">
         <is>
@@ -43464,11 +44022,7 @@
           <t>Diplom</t>
         </is>
       </c>
-      <c r="T466" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T466" s="5" t="inlineStr"/>
       <c r="U466" s="15" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -43846,7 +44400,7 @@
       </c>
       <c r="T470" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 59 390-70-50 / +998 99 143-79-03 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U470" s="7" t="inlineStr">
@@ -43887,7 +44441,7 @@
       </c>
       <c r="E471" s="11" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>26/27 SH/A123</t>
         </is>
       </c>
       <c r="F471" s="11" t="inlineStr">
@@ -43962,7 +44516,7 @@
       </c>
       <c r="T471" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 91 960-08-14 / +998 91 225-07-67 (Onasi)</t>
         </is>
       </c>
       <c r="U471" s="7" t="inlineStr">
@@ -43999,7 +44553,7 @@
       <c r="D472" s="4" t="inlineStr"/>
       <c r="E472" s="5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>26/27 SH/A174</t>
         </is>
       </c>
       <c r="F472" s="5" t="inlineStr">
@@ -44072,11 +44626,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T472" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T472" s="5" t="inlineStr"/>
       <c r="U472" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -44109,7 +44659,11 @@
         </is>
       </c>
       <c r="D473" s="10" t="inlineStr"/>
-      <c r="E473" s="11" t="inlineStr"/>
+      <c r="E473" s="11" t="inlineStr">
+        <is>
+          <t>26/37 SH/A 125</t>
+        </is>
+      </c>
       <c r="F473" s="11" t="inlineStr"/>
       <c r="G473" s="11" t="inlineStr">
         <is>
@@ -44250,7 +44804,7 @@
       </c>
       <c r="T474" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 809-82-30 / +998 99 565-86-81 (Onasi)</t>
         </is>
       </c>
       <c r="U474" s="7" t="inlineStr">
@@ -44444,7 +44998,7 @@
       </c>
       <c r="T476" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 97 573-22-92</t>
         </is>
       </c>
       <c r="U476" s="7" t="inlineStr">
@@ -44804,7 +45358,7 @@
       </c>
       <c r="T480" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 70 290-27-40 / +998 88 263-38-33 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U480" s="5" t="inlineStr"/>
@@ -44837,7 +45391,7 @@
       </c>
       <c r="E481" s="11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>25/26 SH/A 264</t>
         </is>
       </c>
       <c r="F481" s="11" t="inlineStr">
@@ -44910,11 +45464,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T481" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T481" s="11" t="inlineStr"/>
       <c r="U481" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -45121,7 +45671,7 @@
       <c r="D484" s="4" t="inlineStr"/>
       <c r="E484" s="5" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>25/26 Sh/A 266</t>
         </is>
       </c>
       <c r="F484" s="12" t="n">
@@ -45186,7 +45736,7 @@
       </c>
       <c r="T484" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>+998 87 561-52-96 / +998 77 232-28-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U484" s="15" t="inlineStr">
@@ -45225,7 +45775,11 @@
         </is>
       </c>
       <c r="D485" s="10" t="inlineStr"/>
-      <c r="E485" s="11" t="inlineStr"/>
+      <c r="E485" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 272</t>
+        </is>
+      </c>
       <c r="F485" s="11" t="inlineStr"/>
       <c r="G485" s="11" t="inlineStr">
         <is>
@@ -45399,7 +45953,7 @@
       </c>
       <c r="E487" s="11" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>25/26 SH/A 369</t>
         </is>
       </c>
       <c r="F487" s="11" t="inlineStr">
@@ -45474,7 +46028,7 @@
       </c>
       <c r="T487" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 50 501-01-82 / +998 88 078-06-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U487" s="7" t="inlineStr">
@@ -45670,7 +46224,7 @@
       </c>
       <c r="T489" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>+998 70 072-06-14 / +998 95 774-15-64 (Onasi)</t>
         </is>
       </c>
       <c r="U489" s="15" t="inlineStr">
@@ -46028,7 +46582,7 @@
       </c>
       <c r="T493" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>+998 97 066-26-92</t>
         </is>
       </c>
       <c r="U493" s="7" t="inlineStr">
@@ -46067,7 +46621,11 @@
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr"/>
-      <c r="E494" s="5" t="inlineStr"/>
+      <c r="E494" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 147</t>
+        </is>
+      </c>
       <c r="F494" s="5" t="inlineStr"/>
       <c r="G494" s="5" t="inlineStr">
         <is>
@@ -46151,7 +46709,11 @@
         </is>
       </c>
       <c r="D495" s="10" t="inlineStr"/>
-      <c r="E495" s="11" t="inlineStr"/>
+      <c r="E495" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 263</t>
+        </is>
+      </c>
       <c r="F495" s="11" t="inlineStr"/>
       <c r="G495" s="11" t="inlineStr">
         <is>
@@ -46316,7 +46878,7 @@
       </c>
       <c r="T496" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 87 000-46-08 / +998 77 108-80-48 (Onasi)</t>
         </is>
       </c>
       <c r="U496" s="7" t="inlineStr">
@@ -46437,7 +46999,7 @@
       <c r="D498" s="4" t="inlineStr"/>
       <c r="E498" s="5" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>25/26 Sh/A 260</t>
         </is>
       </c>
       <c r="F498" s="5" t="inlineStr">
@@ -46512,7 +47074,7 @@
       </c>
       <c r="T498" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 87 631-07-21 / +998 87 528-07-82 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U498" s="7" t="inlineStr">
@@ -46635,7 +47197,11 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E500" s="5" t="inlineStr"/>
+      <c r="E500" s="5" t="inlineStr">
+        <is>
+          <t>26/27 SH/A153</t>
+        </is>
+      </c>
       <c r="F500" s="5" t="inlineStr"/>
       <c r="G500" s="5" t="inlineStr">
         <is>
@@ -46811,7 +47377,11 @@
         </is>
       </c>
       <c r="D502" s="4" t="inlineStr"/>
-      <c r="E502" s="5" t="inlineStr"/>
+      <c r="E502" s="5" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 155</t>
+        </is>
+      </c>
       <c r="F502" s="5" t="inlineStr"/>
       <c r="G502" s="5" t="inlineStr">
         <is>
@@ -46970,7 +47540,7 @@
       </c>
       <c r="T503" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 85 872-70-10 / +998 06 872-08-85 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U503" s="7" t="inlineStr">
@@ -47153,7 +47723,7 @@
       <c r="S505" s="11" t="inlineStr"/>
       <c r="T505" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>+998 71 160-30-30</t>
         </is>
       </c>
       <c r="U505" s="15" t="inlineStr">
@@ -47362,7 +47932,7 @@
       </c>
       <c r="E508" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>26/27 SH/A 161</t>
         </is>
       </c>
       <c r="F508" s="5" t="inlineStr">
@@ -47437,7 +48007,7 @@
       </c>
       <c r="T508" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 89 818-38-00 / +998 88 386-17-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U508" s="7" t="inlineStr">
@@ -47712,7 +48282,11 @@
         </is>
       </c>
       <c r="D512" s="4" t="inlineStr"/>
-      <c r="E512" s="5" t="inlineStr"/>
+      <c r="E512" s="5" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A165</t>
+        </is>
+      </c>
       <c r="F512" s="5" t="inlineStr"/>
       <c r="G512" s="5" t="inlineStr">
         <is>
@@ -47886,7 +48460,7 @@
       </c>
       <c r="E514" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>25/26 Sh/A246</t>
         </is>
       </c>
       <c r="F514" s="5" t="inlineStr">
@@ -47957,7 +48531,7 @@
       </c>
       <c r="T514" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 619-91-21</t>
         </is>
       </c>
       <c r="U514" s="7" t="inlineStr">
@@ -48151,8 +48725,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T516" s="5" t="n">
-        <v>2019</v>
+      <c r="T516" s="5" t="inlineStr">
+        <is>
+          <t>+998 88 385-13-78 / +998 88 418-82-78 (Otasi / Onasi)</t>
+        </is>
       </c>
       <c r="U516" s="7" t="inlineStr">
         <is>
@@ -48274,7 +48850,11 @@
         </is>
       </c>
       <c r="D518" s="4" t="inlineStr"/>
-      <c r="E518" s="5" t="inlineStr"/>
+      <c r="E518" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 338</t>
+        </is>
+      </c>
       <c r="F518" s="5" t="inlineStr"/>
       <c r="G518" s="5" t="inlineStr">
         <is>
@@ -48687,7 +49267,7 @@
       </c>
       <c r="T522" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 86 233-80-80 / +998 77 021-67-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U522" s="7" t="inlineStr">
@@ -48807,7 +49387,7 @@
       </c>
       <c r="T523" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 95 147-08-25 / +998 99 742-24-73 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U523" s="7" t="inlineStr">
@@ -48919,7 +49499,7 @@
       </c>
       <c r="T524" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>+998 99 559-09-30 / +998 95 182-01-95 (O'zi)</t>
         </is>
       </c>
       <c r="U524" s="7" t="inlineStr">
@@ -48964,7 +49544,7 @@
       </c>
       <c r="E525" s="11" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>26/27 SH/A178</t>
         </is>
       </c>
       <c r="F525" s="11" t="inlineStr">
@@ -49037,8 +49617,10 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T525" s="11" t="n">
-        <v>2026</v>
+      <c r="T525" s="11" t="inlineStr">
+        <is>
+          <t>+998 87 934-03-01 / +998 88 722-88-84 (Onasi)</t>
+        </is>
       </c>
       <c r="U525" s="7" t="inlineStr">
         <is>
@@ -49153,7 +49735,7 @@
       </c>
       <c r="T526" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 90 881-06-10 / +998 90 863-16-74 (Onasi)</t>
         </is>
       </c>
       <c r="U526" s="7" t="inlineStr">
@@ -49188,7 +49770,11 @@
         </is>
       </c>
       <c r="D527" s="10" t="inlineStr"/>
-      <c r="E527" s="11" t="inlineStr"/>
+      <c r="E527" s="11" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 180</t>
+        </is>
+      </c>
       <c r="F527" s="11" t="inlineStr"/>
       <c r="G527" s="11" t="inlineStr">
         <is>
@@ -49610,7 +50196,7 @@
       </c>
       <c r="E532" s="5" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>25/26 Sh/A367</t>
         </is>
       </c>
       <c r="F532" s="5" t="inlineStr"/>
@@ -49673,7 +50259,7 @@
       </c>
       <c r="T532" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 88 833-85-93 / +998 88 804-06-91 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U532" s="5" t="inlineStr"/>
@@ -49700,7 +50286,11 @@
         </is>
       </c>
       <c r="D533" s="10" t="inlineStr"/>
-      <c r="E533" s="11" t="inlineStr"/>
+      <c r="E533" s="11" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 375</t>
+        </is>
+      </c>
       <c r="F533" s="11" t="inlineStr"/>
       <c r="G533" s="11" t="inlineStr">
         <is>
@@ -49865,7 +50455,7 @@
       </c>
       <c r="T534" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 041-02-27 / +998 88 170-80-81 (Otasi)</t>
         </is>
       </c>
       <c r="U534" s="7" t="inlineStr">
@@ -49965,7 +50555,7 @@
       </c>
       <c r="T535" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>+998 97 960-25-35 / +998 91 216-23-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U535" s="11" t="inlineStr"/>
@@ -50067,7 +50657,7 @@
       </c>
       <c r="T536" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>+998 33 380-11-21 / +998 88 009-61-66 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U536" s="7" t="inlineStr">
@@ -50183,7 +50773,7 @@
       </c>
       <c r="T537" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>+998 06 816-17-70 / +998 96 166-08-83 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U537" s="7" t="inlineStr">
@@ -50224,7 +50814,7 @@
       </c>
       <c r="E538" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25/26 sh/a 333</t>
         </is>
       </c>
       <c r="F538" s="5" t="inlineStr">
@@ -50295,7 +50885,7 @@
       </c>
       <c r="T538" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>+998 70 088-02-80 / +998 88 028-08-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U538" s="7" t="inlineStr">
@@ -50334,7 +50924,11 @@
         </is>
       </c>
       <c r="D539" s="10" t="inlineStr"/>
-      <c r="E539" s="11" t="inlineStr"/>
+      <c r="E539" s="11" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 33</t>
+        </is>
+      </c>
       <c r="F539" s="11" t="inlineStr"/>
       <c r="G539" s="11" t="inlineStr">
         <is>
@@ -50495,7 +51089,7 @@
       </c>
       <c r="T540" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 88 729-14-01 / +998 97 619-84-84 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U540" s="7" t="inlineStr">
@@ -50695,7 +51289,7 @@
       </c>
       <c r="T542" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 77 371-00-28 / +998 95 665-28-82 (Onasi)</t>
         </is>
       </c>
       <c r="U542" s="7" t="inlineStr">
@@ -50814,7 +51408,11 @@
         </is>
       </c>
       <c r="D544" s="4" t="inlineStr"/>
-      <c r="E544" s="5" t="inlineStr"/>
+      <c r="E544" s="5" t="inlineStr">
+        <is>
+          <t>25/26 SH/A358</t>
+        </is>
+      </c>
       <c r="F544" s="5" t="inlineStr"/>
       <c r="G544" s="5" t="inlineStr">
         <is>
@@ -50975,7 +51573,7 @@
       </c>
       <c r="T545" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 88 079-07-24</t>
         </is>
       </c>
       <c r="U545" s="7" t="inlineStr">
@@ -51180,7 +51778,7 @@
       </c>
       <c r="E548" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>25/26 Sh/A361</t>
         </is>
       </c>
       <c r="F548" s="5" t="inlineStr">
@@ -51251,7 +51849,7 @@
       </c>
       <c r="T548" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 04 891-30-00 / +998 90 870-88-27 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U548" s="7" t="inlineStr">
@@ -51454,7 +52052,11 @@
         </is>
       </c>
       <c r="D551" s="10" t="inlineStr"/>
-      <c r="E551" s="11" t="inlineStr"/>
+      <c r="E551" s="11" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 346</t>
+        </is>
+      </c>
       <c r="F551" s="11" t="inlineStr"/>
       <c r="G551" s="11" t="inlineStr">
         <is>
@@ -51538,7 +52140,11 @@
         </is>
       </c>
       <c r="D552" s="4" t="inlineStr"/>
-      <c r="E552" s="5" t="inlineStr"/>
+      <c r="E552" s="5" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A365</t>
+        </is>
+      </c>
       <c r="F552" s="5" t="inlineStr"/>
       <c r="G552" s="5" t="inlineStr">
         <is>
@@ -51876,7 +52482,7 @@
       </c>
       <c r="E556" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>25/26 SH/A 372</t>
         </is>
       </c>
       <c r="F556" s="5" t="inlineStr">
@@ -51951,7 +52557,7 @@
       </c>
       <c r="T556" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 75 613-00-20 / +998 05 181-88-40 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U556" s="7" t="inlineStr">
@@ -52051,7 +52657,7 @@
       </c>
       <c r="T557" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 99 540-78-43 / +998 91 775-05-59 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U557" s="7" t="inlineStr">
@@ -52251,7 +52857,7 @@
       </c>
       <c r="T559" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>+998 33 115-80-83 / +998 97 618-83-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U559" s="7" t="inlineStr">
@@ -52452,7 +53058,7 @@
       <c r="D562" s="4" t="inlineStr"/>
       <c r="E562" s="5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>25/26 SH/A 511</t>
         </is>
       </c>
       <c r="F562" s="5" t="inlineStr">
@@ -52527,7 +53133,7 @@
       </c>
       <c r="T562" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>+998 88 123-65-47</t>
         </is>
       </c>
       <c r="U562" s="7" t="inlineStr">
@@ -52562,7 +53168,11 @@
         </is>
       </c>
       <c r="D563" s="10" t="inlineStr"/>
-      <c r="E563" s="11" t="inlineStr"/>
+      <c r="E563" s="11" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
       <c r="F563" s="11" t="inlineStr"/>
       <c r="G563" s="11" t="inlineStr">
         <is>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X563"/>
+  <dimension ref="A1:AA563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -863,6 +863,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="n">
@@ -951,6 +961,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1039,6 +1059,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="8" t="n">
@@ -1127,6 +1157,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1241,6 +1281,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1329,6 +1379,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1445,6 +1505,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1541,6 +1611,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1629,6 +1709,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1741,6 +1831,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1829,6 +1929,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1949,6 +2059,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -2065,6 +2185,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2181,6 +2311,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -2269,6 +2401,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2361,6 +2503,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -2449,6 +2601,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2541,6 +2703,16 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -2629,6 +2801,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2745,6 +2927,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -2833,6 +3025,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2949,6 +3151,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -3037,6 +3249,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -3153,6 +3375,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -3241,6 +3473,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -3325,6 +3567,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -3425,6 +3677,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -3533,6 +3795,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -3621,6 +3893,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -3709,6 +3991,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -3793,6 +4085,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -3881,6 +4183,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -3969,6 +4281,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -4085,6 +4399,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -4193,6 +4517,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -4281,6 +4615,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -4397,6 +4741,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -4485,6 +4839,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -4573,6 +4937,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -4661,6 +5035,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -4749,6 +5133,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -4837,6 +5231,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -4941,6 +5345,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -5033,6 +5447,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -5149,6 +5573,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -5265,6 +5699,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -5369,6 +5813,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -5457,6 +5911,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -5573,6 +6037,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -5661,6 +6135,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -5749,6 +6233,16 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -5837,6 +6331,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -5925,6 +6429,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -6013,6 +6527,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -6101,6 +6625,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -6189,6 +6723,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -6277,6 +6821,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -6365,6 +6919,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -6481,6 +7045,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -6569,6 +7143,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -6681,6 +7265,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -6769,6 +7363,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -6857,6 +7461,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -6945,6 +7559,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -7029,6 +7653,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -7117,6 +7751,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -7201,6 +7845,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -7289,6 +7943,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -7381,6 +8045,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -7469,6 +8143,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -7557,6 +8241,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -7645,6 +8339,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -7733,6 +8437,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -7825,6 +8531,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -7913,6 +8629,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -8001,6 +8727,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -8093,6 +8829,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -8181,6 +8927,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -8289,6 +9045,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -8377,6 +9143,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -8491,6 +9267,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -8579,6 +9365,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -8667,6 +9463,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -8755,6 +9561,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -8843,6 +9659,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -8927,6 +9753,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -9011,6 +9847,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -9099,6 +9945,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -9187,6 +10043,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -9279,6 +10145,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -9367,6 +10243,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -9479,6 +10365,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -9567,6 +10463,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -9655,6 +10561,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -9767,6 +10683,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -9851,6 +10777,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -9959,6 +10895,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -10043,6 +10989,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -10131,6 +11087,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -10215,6 +11181,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -10303,6 +11279,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -10419,6 +11405,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -10523,6 +11519,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -10611,6 +11617,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -10727,6 +11743,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -10815,6 +11841,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -10921,6 +11957,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -11009,6 +12055,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -11097,6 +12153,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n">
@@ -11185,6 +12251,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -11273,6 +12349,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n">
@@ -11385,6 +12471,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -11473,6 +12569,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n">
@@ -11579,6 +12685,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -11667,6 +12783,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n">
@@ -11783,6 +12909,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -11899,6 +13035,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n">
@@ -11999,6 +13145,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -12091,6 +13247,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n">
@@ -12205,6 +13371,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -12317,6 +13493,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n">
@@ -12437,6 +13623,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -12543,6 +13739,16 @@
       <c r="X124" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -12613,6 +13819,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -12697,6 +13913,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n">
@@ -12813,6 +14039,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -12901,6 +14137,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n">
@@ -12997,6 +14243,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="n">
@@ -13113,6 +14369,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n">
@@ -13201,6 +14467,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="n">
@@ -13289,6 +14565,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n">
@@ -13377,6 +14663,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -13489,6 +14785,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n">
@@ -13573,6 +14879,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -13657,6 +14973,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n">
@@ -13745,6 +15071,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -13855,6 +15191,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n">
@@ -13943,6 +15289,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -14031,6 +15387,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="8" t="n">
@@ -14119,6 +15485,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -14207,6 +15583,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="8" t="n">
@@ -14295,6 +15681,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -14411,6 +15807,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="8" t="n">
@@ -14511,6 +15917,16 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -14599,6 +16015,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="8" t="n">
@@ -14683,6 +16109,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -14795,6 +16231,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="8" t="n">
@@ -14883,6 +16329,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -14971,6 +16427,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="8" t="n">
@@ -15087,6 +16553,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -15175,6 +16651,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="8" t="n">
@@ -15287,6 +16773,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -15383,6 +16879,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="8" t="n">
@@ -15471,6 +16977,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -15587,6 +17103,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="8" t="n">
@@ -15671,6 +17197,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -15759,6 +17295,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="8" t="n">
@@ -15847,6 +17393,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="n">
@@ -15963,6 +17519,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="8" t="n">
@@ -16051,6 +17617,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="n">
@@ -16167,6 +17743,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="8" t="n">
@@ -16271,6 +17857,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="n">
@@ -16387,6 +17983,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="8" t="n">
@@ -16475,6 +18081,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="n">
@@ -16591,6 +18207,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="8" t="n">
@@ -16679,6 +18305,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="n">
@@ -16763,6 +18399,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="8" t="n">
@@ -16851,6 +18497,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="n">
@@ -16939,6 +18595,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="8" t="n">
@@ -17027,6 +18693,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="n">
@@ -17143,6 +18819,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="8" t="n">
@@ -17259,6 +18945,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="n">
@@ -17349,6 +19045,16 @@
       <c r="X174" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -17419,6 +19125,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="n">
@@ -17527,6 +19243,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="8" t="n">
@@ -17611,6 +19337,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="n">
@@ -17727,6 +19463,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="8" t="n">
@@ -17815,6 +19561,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="n">
@@ -17899,6 +19655,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="8" t="n">
@@ -17983,6 +19749,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="n">
@@ -18067,6 +19843,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="8" t="n">
@@ -18155,6 +19941,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="n">
@@ -18271,6 +20067,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="8" t="n">
@@ -18371,6 +20177,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>T-47</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="2" t="n">
@@ -18451,6 +20267,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>T-29</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="8" t="n">
@@ -18535,6 +20361,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>T-30/1</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="2" t="n">
@@ -18619,6 +20455,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>T-32</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="22" customHeight="1">
       <c r="A189" s="8" t="n">
@@ -18699,6 +20545,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="2" t="n">
@@ -18815,6 +20671,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>T-45</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="22" customHeight="1">
       <c r="A191" s="8" t="n">
@@ -18899,6 +20765,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>T-36</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="2" t="n">
@@ -19015,6 +20891,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>28.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="22" customHeight="1">
       <c r="A193" s="8" t="n">
@@ -19111,6 +20997,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>T-33</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="2" t="n">
@@ -19195,6 +21091,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>T-44</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="8" t="n">
@@ -19309,6 +21215,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="2" t="n">
@@ -19423,6 +21339,16 @@
       <c r="X196" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
         </is>
       </c>
     </row>
@@ -19489,6 +21415,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>28.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="2" t="n">
@@ -19573,6 +21509,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>T-35</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="22" customHeight="1">
       <c r="A199" s="8" t="n">
@@ -19681,6 +21627,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>T-34</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="22" customHeight="1">
       <c r="A200" s="2" t="n">
@@ -19765,6 +21721,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>T-31</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="8" t="n">
@@ -19849,6 +21815,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="2" t="n">
@@ -19933,6 +21901,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>T-30</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="22" customHeight="1">
       <c r="A203" s="8" t="n">
@@ -20017,6 +21995,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
     </row>
     <row r="204" ht="22" customHeight="1">
       <c r="A204" s="2" t="n">
@@ -20133,6 +22113,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>T-21</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="22" customHeight="1">
       <c r="A205" s="8" t="n">
@@ -20239,6 +22229,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
     </row>
     <row r="206" ht="22" customHeight="1">
       <c r="A206" s="2" t="n">
@@ -20319,6 +22311,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="8" t="n">
@@ -20431,6 +22425,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>T-30/2</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="22" customHeight="1">
       <c r="A208" s="2" t="n">
@@ -20547,6 +22551,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>T-25</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="22" customHeight="1">
       <c r="A209" s="8" t="n">
@@ -20631,6 +22645,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="22" customHeight="1">
       <c r="A210" s="2" t="n">
@@ -20751,6 +22775,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="22" customHeight="1">
       <c r="A211" s="8" t="n">
@@ -20835,6 +22869,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="22" customHeight="1">
       <c r="A212" s="2" t="n">
@@ -20951,6 +22995,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>T-09</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="22" customHeight="1">
       <c r="A213" s="8" t="n">
@@ -21035,6 +23089,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>T-37</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="22" customHeight="1">
       <c r="A214" s="2" t="n">
@@ -21151,6 +23215,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>T-40</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="22" customHeight="1">
       <c r="A215" s="8" t="n">
@@ -21235,6 +23309,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
     </row>
     <row r="216" ht="22" customHeight="1">
       <c r="A216" s="2" t="n">
@@ -21319,6 +23395,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="22" customHeight="1">
       <c r="A217" s="8" t="n">
@@ -21403,6 +23489,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>T-24</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="22" customHeight="1">
       <c r="A218" s="2" t="n">
@@ -21487,6 +23583,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>13.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="22" customHeight="1">
       <c r="A219" s="8" t="n">
@@ -21567,6 +23673,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="22" customHeight="1">
       <c r="A220" s="2" t="n">
@@ -21647,6 +23763,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="22" customHeight="1">
       <c r="A221" s="8" t="n">
@@ -21731,6 +23857,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>T-27</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="22" customHeight="1">
       <c r="A222" s="2" t="n">
@@ -21837,6 +23973,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
     </row>
     <row r="223" ht="22" customHeight="1">
       <c r="A223" s="8" t="n">
@@ -21921,6 +24059,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="22" customHeight="1">
       <c r="A224" s="2" t="n">
@@ -22005,6 +24153,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr"/>
+      <c r="AA224" t="inlineStr"/>
     </row>
     <row r="225" ht="22" customHeight="1">
       <c r="A225" s="8" t="n">
@@ -22073,6 +24223,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="22" customHeight="1">
       <c r="A226" s="2" t="n">
@@ -22189,6 +24349,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
     </row>
     <row r="227" ht="22" customHeight="1">
       <c r="A227" s="8" t="n">
@@ -22273,6 +24435,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="22" customHeight="1">
       <c r="A228" s="2" t="n">
@@ -22357,6 +24529,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="22" customHeight="1">
       <c r="A229" s="8" t="n">
@@ -22441,6 +24623,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>T-08</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="22" customHeight="1">
       <c r="A230" s="2" t="n">
@@ -22553,6 +24745,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
     </row>
     <row r="231" ht="22" customHeight="1">
       <c r="A231" s="8" t="n">
@@ -22637,6 +24831,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>16.12.2025</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="22" customHeight="1">
       <c r="A232" s="2" t="n">
@@ -22753,6 +24957,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="22" customHeight="1">
       <c r="A233" s="8" t="n">
@@ -22861,6 +25075,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="22" customHeight="1">
       <c r="A234" s="2" t="n">
@@ -22945,6 +25169,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="22" customHeight="1">
       <c r="A235" s="8" t="n">
@@ -23029,6 +25263,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="22" customHeight="1">
       <c r="A236" s="2" t="n">
@@ -23113,6 +25357,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="22" customHeight="1">
       <c r="A237" s="8" t="n">
@@ -23229,6 +25483,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
     </row>
     <row r="238" ht="22" customHeight="1">
       <c r="A238" s="2" t="n">
@@ -23337,6 +25593,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="inlineStr"/>
     </row>
     <row r="239" ht="22" customHeight="1">
       <c r="A239" s="8" t="n">
@@ -23447,6 +25705,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="inlineStr"/>
     </row>
     <row r="240" ht="22" customHeight="1">
       <c r="A240" s="2" t="n">
@@ -23531,6 +25791,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="inlineStr"/>
     </row>
     <row r="241" ht="22" customHeight="1">
       <c r="A241" s="8" t="n">
@@ -23615,6 +25877,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="inlineStr"/>
     </row>
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="2" t="n">
@@ -23695,6 +25959,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="inlineStr"/>
     </row>
     <row r="243" ht="22" customHeight="1">
       <c r="A243" s="8" t="n">
@@ -23811,6 +26077,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="inlineStr"/>
     </row>
     <row r="244" ht="22" customHeight="1">
       <c r="A244" s="2" t="n">
@@ -23895,6 +26163,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="inlineStr"/>
     </row>
     <row r="245" ht="22" customHeight="1">
       <c r="A245" s="8" t="n">
@@ -24001,6 +26271,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr"/>
+      <c r="AA245" t="inlineStr"/>
     </row>
     <row r="246" ht="22" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -24085,6 +26357,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr"/>
+      <c r="AA246" t="inlineStr"/>
     </row>
     <row r="247" ht="22" customHeight="1">
       <c r="A247" s="8" t="n">
@@ -24169,6 +26443,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z247" t="inlineStr"/>
+      <c r="AA247" t="inlineStr"/>
     </row>
     <row r="248" ht="22" customHeight="1">
       <c r="A248" s="2" t="n">
@@ -24279,6 +26555,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
     </row>
     <row r="249" ht="22" customHeight="1">
       <c r="A249" s="8" t="n">
@@ -24363,6 +26641,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr"/>
+      <c r="AA249" t="inlineStr"/>
     </row>
     <row r="250" ht="22" customHeight="1">
       <c r="A250" s="2" t="n">
@@ -24475,6 +26755,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr"/>
     </row>
     <row r="251" ht="22" customHeight="1">
       <c r="A251" s="8" t="n">
@@ -24539,6 +26821,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr"/>
     </row>
     <row r="252" ht="22" customHeight="1">
       <c r="A252" s="2" t="n">
@@ -24627,6 +26911,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
     </row>
     <row r="253" ht="22" customHeight="1">
       <c r="A253" s="8" t="n">
@@ -24715,6 +27001,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="inlineStr"/>
     </row>
     <row r="254" ht="22" customHeight="1">
       <c r="A254" s="2" t="n">
@@ -24803,6 +27091,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="inlineStr"/>
     </row>
     <row r="255" ht="22" customHeight="1">
       <c r="A255" s="8" t="n">
@@ -24887,6 +27177,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr"/>
     </row>
     <row r="256" ht="22" customHeight="1">
       <c r="A256" s="2" t="n">
@@ -24987,6 +27279,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr"/>
+      <c r="AA256" t="inlineStr"/>
     </row>
     <row r="257" ht="22" customHeight="1">
       <c r="A257" s="8" t="n">
@@ -25071,6 +27365,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="inlineStr"/>
     </row>
     <row r="258" ht="22" customHeight="1">
       <c r="A258" s="2" t="n">
@@ -25155,6 +27451,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr"/>
+      <c r="AA258" t="inlineStr"/>
     </row>
     <row r="259" ht="22" customHeight="1">
       <c r="A259" s="8" t="n">
@@ -25251,6 +27549,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr"/>
+      <c r="AA259" t="inlineStr"/>
     </row>
     <row r="260" ht="22" customHeight="1">
       <c r="A260" s="2" t="n">
@@ -25335,6 +27635,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr"/>
+      <c r="AA260" t="inlineStr"/>
     </row>
     <row r="261" ht="22" customHeight="1">
       <c r="A261" s="8" t="n">
@@ -25419,6 +27721,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
     </row>
     <row r="262" ht="22" customHeight="1">
       <c r="A262" s="2" t="n">
@@ -25507,6 +27811,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
     </row>
     <row r="263" ht="22" customHeight="1">
       <c r="A263" s="8" t="n">
@@ -25591,6 +27897,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr"/>
+      <c r="AA263" t="inlineStr"/>
     </row>
     <row r="264" ht="22" customHeight="1">
       <c r="A264" s="2" t="n">
@@ -25675,6 +27983,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr"/>
+      <c r="AA264" t="inlineStr"/>
     </row>
     <row r="265" ht="22" customHeight="1">
       <c r="A265" s="8" t="n">
@@ -25763,6 +28073,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
     </row>
     <row r="266" ht="22" customHeight="1">
       <c r="A266" s="2" t="n">
@@ -25867,6 +28179,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="inlineStr"/>
     </row>
     <row r="267" ht="22" customHeight="1">
       <c r="A267" s="8" t="n">
@@ -25975,6 +28289,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="inlineStr"/>
     </row>
     <row r="268" ht="22" customHeight="1">
       <c r="A268" s="2" t="n">
@@ -26059,6 +28375,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
     </row>
     <row r="269" ht="22" customHeight="1">
       <c r="A269" s="8" t="n">
@@ -26143,6 +28461,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="inlineStr"/>
     </row>
     <row r="270" ht="22" customHeight="1">
       <c r="A270" s="2" t="n">
@@ -26259,6 +28579,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
     </row>
     <row r="271" ht="22" customHeight="1">
       <c r="A271" s="8" t="n">
@@ -26347,6 +28669,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="inlineStr"/>
     </row>
     <row r="272" ht="22" customHeight="1">
       <c r="A272" s="2" t="n">
@@ -26431,6 +28755,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="inlineStr"/>
     </row>
     <row r="273" ht="22" customHeight="1">
       <c r="A273" s="8" t="n">
@@ -26499,6 +28825,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="inlineStr"/>
     </row>
     <row r="274" ht="22" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -26587,6 +28915,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="inlineStr"/>
     </row>
     <row r="275" ht="22" customHeight="1">
       <c r="A275" s="8" t="n">
@@ -26675,6 +29005,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="inlineStr"/>
     </row>
     <row r="276" ht="22" customHeight="1">
       <c r="A276" s="2" t="n">
@@ -26779,6 +29111,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
     </row>
     <row r="277" ht="22" customHeight="1">
       <c r="A277" s="8" t="n">
@@ -26867,6 +29201,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="inlineStr"/>
     </row>
     <row r="278" ht="22" customHeight="1">
       <c r="A278" s="2" t="n">
@@ -26951,6 +29287,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="inlineStr"/>
     </row>
     <row r="279" ht="22" customHeight="1">
       <c r="A279" s="8" t="n">
@@ -27035,6 +29373,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
     </row>
     <row r="280" ht="22" customHeight="1">
       <c r="A280" s="2" t="n">
@@ -27115,6 +29455,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
     </row>
     <row r="281" ht="22" customHeight="1">
       <c r="A281" s="8" t="n">
@@ -27199,6 +29541,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
     </row>
     <row r="282" ht="22" customHeight="1">
       <c r="A282" s="2" t="n">
@@ -27283,6 +29627,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
     </row>
     <row r="283" ht="22" customHeight="1">
       <c r="A283" s="8" t="n">
@@ -27367,6 +29713,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
     </row>
     <row r="284" ht="22" customHeight="1">
       <c r="A284" s="2" t="n">
@@ -27431,6 +29779,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
     </row>
     <row r="285" ht="22" customHeight="1">
       <c r="A285" s="8" t="n">
@@ -27547,6 +29897,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
     </row>
     <row r="286" ht="22" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -27663,6 +30015,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
     </row>
     <row r="287" ht="22" customHeight="1">
       <c r="A287" s="8" t="n">
@@ -27755,6 +30109,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr"/>
     </row>
     <row r="288" ht="22" customHeight="1">
       <c r="A288" s="2" t="n">
@@ -27867,6 +30223,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
     </row>
     <row r="289" ht="22" customHeight="1">
       <c r="A289" s="8" t="n">
@@ -27987,6 +30345,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
     </row>
     <row r="290" ht="22" customHeight="1">
       <c r="A290" s="2" t="n">
@@ -28071,6 +30431,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
     </row>
     <row r="291" ht="22" customHeight="1">
       <c r="A291" s="8" t="n">
@@ -28155,6 +30517,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
     </row>
     <row r="292" ht="22" customHeight="1">
       <c r="A292" s="2" t="n">
@@ -28243,6 +30607,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr"/>
     </row>
     <row r="293" ht="22" customHeight="1">
       <c r="A293" s="8" t="n">
@@ -28331,6 +30697,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
     </row>
     <row r="294" ht="22" customHeight="1">
       <c r="A294" s="2" t="n">
@@ -28419,6 +30787,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z294" t="inlineStr"/>
+      <c r="AA294" t="inlineStr"/>
     </row>
     <row r="295" ht="22" customHeight="1">
       <c r="A295" s="8" t="n">
@@ -28503,6 +30873,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr"/>
+      <c r="AA295" t="inlineStr"/>
     </row>
     <row r="296" ht="22" customHeight="1">
       <c r="A296" s="2" t="n">
@@ -28587,6 +30959,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr"/>
+      <c r="AA296" t="inlineStr"/>
     </row>
     <row r="297" ht="22" customHeight="1">
       <c r="A297" s="8" t="n">
@@ -28695,6 +31069,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z297" t="inlineStr"/>
+      <c r="AA297" t="inlineStr"/>
     </row>
     <row r="298" ht="22" customHeight="1">
       <c r="A298" s="2" t="n">
@@ -28747,6 +31123,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr"/>
     </row>
     <row r="299" ht="22" customHeight="1">
       <c r="A299" s="8" t="n">
@@ -28831,6 +31209,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr"/>
     </row>
     <row r="300" ht="22" customHeight="1">
       <c r="A300" s="2" t="n">
@@ -28911,6 +31291,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z300" t="inlineStr"/>
+      <c r="AA300" t="inlineStr"/>
     </row>
     <row r="301" ht="22" customHeight="1">
       <c r="A301" s="8" t="n">
@@ -28999,6 +31381,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z301" t="inlineStr"/>
+      <c r="AA301" t="inlineStr"/>
     </row>
     <row r="302" ht="22" customHeight="1">
       <c r="A302" s="2" t="n">
@@ -29099,6 +31483,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z302" t="inlineStr"/>
+      <c r="AA302" t="inlineStr"/>
     </row>
     <row r="303" ht="22" customHeight="1">
       <c r="A303" s="8" t="n">
@@ -29183,6 +31569,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr"/>
+      <c r="AA303" t="inlineStr"/>
     </row>
     <row r="304" ht="22" customHeight="1">
       <c r="A304" s="2" t="n">
@@ -29267,6 +31655,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z304" t="inlineStr"/>
+      <c r="AA304" t="inlineStr"/>
     </row>
     <row r="305" ht="22" customHeight="1">
       <c r="A305" s="8" t="n">
@@ -29351,6 +31741,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z305" t="inlineStr"/>
+      <c r="AA305" t="inlineStr"/>
     </row>
     <row r="306" ht="22" customHeight="1">
       <c r="A306" s="2" t="n">
@@ -29463,6 +31855,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr"/>
     </row>
     <row r="307" ht="22" customHeight="1">
       <c r="A307" s="8" t="n">
@@ -29527,6 +31921,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr"/>
     </row>
     <row r="308" ht="22" customHeight="1">
       <c r="A308" s="2" t="n">
@@ -29611,6 +32007,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z308" t="inlineStr"/>
+      <c r="AA308" t="inlineStr"/>
     </row>
     <row r="309" ht="22" customHeight="1">
       <c r="A309" s="8" t="n">
@@ -29721,6 +32119,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr"/>
+      <c r="AA309" t="inlineStr"/>
     </row>
     <row r="310" ht="22" customHeight="1">
       <c r="A310" s="2" t="n">
@@ -29805,6 +32205,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr"/>
+      <c r="AA310" t="inlineStr"/>
     </row>
     <row r="311" ht="22" customHeight="1">
       <c r="A311" s="8" t="n">
@@ -29917,6 +32319,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z311" t="inlineStr"/>
+      <c r="AA311" t="inlineStr"/>
     </row>
     <row r="312" ht="22" customHeight="1">
       <c r="A312" s="2" t="n">
@@ -30033,6 +32437,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z312" t="inlineStr"/>
+      <c r="AA312" t="inlineStr"/>
     </row>
     <row r="313" ht="22" customHeight="1">
       <c r="A313" s="8" t="n">
@@ -30117,6 +32523,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z313" t="inlineStr"/>
+      <c r="AA313" t="inlineStr"/>
     </row>
     <row r="314" ht="22" customHeight="1">
       <c r="A314" s="2" t="n">
@@ -30201,6 +32609,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z314" t="inlineStr"/>
+      <c r="AA314" t="inlineStr"/>
     </row>
     <row r="315" ht="22" customHeight="1">
       <c r="A315" s="8" t="n">
@@ -30285,6 +32695,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z315" t="inlineStr"/>
+      <c r="AA315" t="inlineStr"/>
     </row>
     <row r="316" ht="22" customHeight="1">
       <c r="A316" s="2" t="n">
@@ -30373,6 +32785,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z316" t="inlineStr"/>
+      <c r="AA316" t="inlineStr"/>
     </row>
     <row r="317" ht="22" customHeight="1">
       <c r="A317" s="8" t="n">
@@ -30485,6 +32899,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z317" t="inlineStr"/>
+      <c r="AA317" t="inlineStr"/>
     </row>
     <row r="318" ht="22" customHeight="1">
       <c r="A318" s="2" t="n">
@@ -30569,6 +32985,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z318" t="inlineStr"/>
+      <c r="AA318" t="inlineStr"/>
     </row>
     <row r="319" ht="22" customHeight="1">
       <c r="A319" s="8" t="n">
@@ -30677,6 +33095,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z319" t="inlineStr"/>
+      <c r="AA319" t="inlineStr"/>
     </row>
     <row r="320" ht="22" customHeight="1">
       <c r="A320" s="2" t="n">
@@ -30757,6 +33177,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z320" t="inlineStr"/>
+      <c r="AA320" t="inlineStr"/>
     </row>
     <row r="321" ht="22" customHeight="1">
       <c r="A321" s="8" t="n">
@@ -30845,6 +33267,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr"/>
+      <c r="AA321" t="inlineStr"/>
     </row>
     <row r="322" ht="22" customHeight="1">
       <c r="A322" s="2" t="n">
@@ -30929,6 +33353,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr"/>
+      <c r="AA322" t="inlineStr"/>
     </row>
     <row r="323" ht="22" customHeight="1">
       <c r="A323" s="8" t="n">
@@ -31045,6 +33471,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z323" t="inlineStr"/>
+      <c r="AA323" t="inlineStr"/>
     </row>
     <row r="324" ht="22" customHeight="1">
       <c r="A324" s="2" t="n">
@@ -31129,6 +33557,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z324" t="inlineStr"/>
+      <c r="AA324" t="inlineStr"/>
     </row>
     <row r="325" ht="22" customHeight="1">
       <c r="A325" s="8" t="n">
@@ -31209,6 +33639,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z325" t="inlineStr"/>
+      <c r="AA325" t="inlineStr"/>
     </row>
     <row r="326" ht="22" customHeight="1">
       <c r="A326" s="2" t="n">
@@ -31297,6 +33729,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z326" t="inlineStr"/>
+      <c r="AA326" t="inlineStr"/>
     </row>
     <row r="327" ht="22" customHeight="1">
       <c r="A327" s="8" t="n">
@@ -31413,6 +33847,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z327" t="inlineStr"/>
+      <c r="AA327" t="inlineStr"/>
     </row>
     <row r="328" ht="22" customHeight="1">
       <c r="A328" s="2" t="n">
@@ -31497,6 +33933,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z328" t="inlineStr"/>
+      <c r="AA328" t="inlineStr"/>
     </row>
     <row r="329" ht="22" customHeight="1">
       <c r="A329" s="8" t="n">
@@ -31605,6 +34043,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z329" t="inlineStr"/>
+      <c r="AA329" t="inlineStr"/>
     </row>
     <row r="330" ht="22" customHeight="1">
       <c r="A330" s="2" t="n">
@@ -31693,6 +34133,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z330" t="inlineStr"/>
+      <c r="AA330" t="inlineStr"/>
     </row>
     <row r="331" ht="22" customHeight="1">
       <c r="A331" s="8" t="n">
@@ -31777,6 +34219,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z331" t="inlineStr"/>
+      <c r="AA331" t="inlineStr"/>
     </row>
     <row r="332" ht="22" customHeight="1">
       <c r="A332" s="2" t="n">
@@ -31857,6 +34301,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z332" t="inlineStr"/>
+      <c r="AA332" t="inlineStr"/>
     </row>
     <row r="333" ht="22" customHeight="1">
       <c r="A333" s="8" t="n">
@@ -31957,6 +34403,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z333" t="inlineStr"/>
+      <c r="AA333" t="inlineStr"/>
     </row>
     <row r="334" ht="22" customHeight="1">
       <c r="A334" s="2" t="n">
@@ -32041,6 +34489,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z334" t="inlineStr"/>
+      <c r="AA334" t="inlineStr"/>
     </row>
     <row r="335" ht="22" customHeight="1">
       <c r="A335" s="8" t="n">
@@ -32129,6 +34579,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="inlineStr"/>
     </row>
     <row r="336" ht="22" customHeight="1">
       <c r="A336" s="2" t="n">
@@ -32213,6 +34665,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z336" t="inlineStr"/>
+      <c r="AA336" t="inlineStr"/>
     </row>
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="8" t="n">
@@ -32301,6 +34755,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="inlineStr"/>
     </row>
     <row r="338" ht="22" customHeight="1">
       <c r="A338" s="2" t="n">
@@ -32385,6 +34841,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z338" t="inlineStr"/>
+      <c r="AA338" t="inlineStr"/>
     </row>
     <row r="339" ht="22" customHeight="1">
       <c r="A339" s="8" t="n">
@@ -32505,6 +34963,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z339" t="inlineStr"/>
+      <c r="AA339" t="inlineStr"/>
     </row>
     <row r="340" ht="22" customHeight="1">
       <c r="A340" s="2" t="n">
@@ -32589,6 +35049,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z340" t="inlineStr"/>
+      <c r="AA340" t="inlineStr"/>
     </row>
     <row r="341" ht="22" customHeight="1">
       <c r="A341" s="8" t="n">
@@ -32673,6 +35135,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z341" t="inlineStr"/>
+      <c r="AA341" t="inlineStr"/>
     </row>
     <row r="342" ht="22" customHeight="1">
       <c r="A342" s="2" t="n">
@@ -32757,6 +35221,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z342" t="inlineStr"/>
+      <c r="AA342" t="inlineStr"/>
     </row>
     <row r="343" ht="22" customHeight="1">
       <c r="A343" s="8" t="n">
@@ -32841,6 +35307,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z343" t="inlineStr"/>
+      <c r="AA343" t="inlineStr"/>
     </row>
     <row r="344" ht="22" customHeight="1">
       <c r="A344" s="2" t="n">
@@ -32925,6 +35393,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z344" t="inlineStr"/>
+      <c r="AA344" t="inlineStr"/>
     </row>
     <row r="345" ht="22" customHeight="1">
       <c r="A345" s="8" t="n">
@@ -33009,6 +35479,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z345" t="inlineStr"/>
+      <c r="AA345" t="inlineStr"/>
     </row>
     <row r="346" ht="22" customHeight="1">
       <c r="A346" s="2" t="n">
@@ -33093,6 +35565,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z346" t="inlineStr"/>
+      <c r="AA346" t="inlineStr"/>
     </row>
     <row r="347" ht="22" customHeight="1">
       <c r="A347" s="8" t="n">
@@ -33177,6 +35651,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z347" t="inlineStr"/>
+      <c r="AA347" t="inlineStr"/>
     </row>
     <row r="348" ht="22" customHeight="1">
       <c r="A348" s="2" t="n">
@@ -33265,6 +35741,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z348" t="inlineStr"/>
+      <c r="AA348" t="inlineStr"/>
     </row>
     <row r="349" ht="22" customHeight="1">
       <c r="A349" s="8" t="n">
@@ -33349,6 +35827,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z349" t="inlineStr"/>
+      <c r="AA349" t="inlineStr"/>
     </row>
     <row r="350" ht="22" customHeight="1">
       <c r="A350" s="2" t="n">
@@ -33433,6 +35913,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z350" t="inlineStr"/>
+      <c r="AA350" t="inlineStr"/>
     </row>
     <row r="351" ht="22" customHeight="1">
       <c r="A351" s="8" t="n">
@@ -33533,6 +36015,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z351" t="inlineStr"/>
+      <c r="AA351" t="inlineStr"/>
     </row>
     <row r="352" ht="22" customHeight="1">
       <c r="A352" s="2" t="n">
@@ -33649,6 +36133,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z352" t="inlineStr"/>
+      <c r="AA352" t="inlineStr"/>
     </row>
     <row r="353" ht="22" customHeight="1">
       <c r="A353" s="8" t="n">
@@ -33733,6 +36219,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z353" t="inlineStr"/>
+      <c r="AA353" t="inlineStr"/>
     </row>
     <row r="354" ht="22" customHeight="1">
       <c r="A354" s="2" t="n">
@@ -33817,6 +36305,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z354" t="inlineStr"/>
+      <c r="AA354" t="inlineStr"/>
     </row>
     <row r="355" ht="22" customHeight="1">
       <c r="A355" s="8" t="n">
@@ -33929,6 +36419,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z355" t="inlineStr"/>
+      <c r="AA355" t="inlineStr"/>
     </row>
     <row r="356" ht="22" customHeight="1">
       <c r="A356" s="2" t="n">
@@ -34013,6 +36505,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z356" t="inlineStr"/>
+      <c r="AA356" t="inlineStr"/>
     </row>
     <row r="357" ht="22" customHeight="1">
       <c r="A357" s="8" t="n">
@@ -34093,6 +36587,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z357" t="inlineStr"/>
+      <c r="AA357" t="inlineStr"/>
     </row>
     <row r="358" ht="22" customHeight="1">
       <c r="A358" s="2" t="n">
@@ -34177,6 +36673,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z358" t="inlineStr"/>
+      <c r="AA358" t="inlineStr"/>
     </row>
     <row r="359" ht="22" customHeight="1">
       <c r="A359" s="8" t="n">
@@ -34261,6 +36759,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z359" t="inlineStr"/>
+      <c r="AA359" t="inlineStr"/>
     </row>
     <row r="360" ht="22" customHeight="1">
       <c r="A360" s="2" t="n">
@@ -34365,6 +36865,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z360" t="inlineStr"/>
+      <c r="AA360" t="inlineStr"/>
     </row>
     <row r="361" ht="22" customHeight="1">
       <c r="A361" s="8" t="n">
@@ -34449,6 +36951,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z361" t="inlineStr"/>
+      <c r="AA361" t="inlineStr"/>
     </row>
     <row r="362" ht="22" customHeight="1">
       <c r="A362" s="2" t="n">
@@ -34565,6 +37069,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z362" t="inlineStr"/>
+      <c r="AA362" t="inlineStr"/>
     </row>
     <row r="363" ht="22" customHeight="1">
       <c r="A363" s="8" t="n">
@@ -34649,6 +37155,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z363" t="inlineStr"/>
+      <c r="AA363" t="inlineStr"/>
     </row>
     <row r="364" ht="22" customHeight="1">
       <c r="A364" s="2" t="n">
@@ -34765,6 +37273,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z364" t="inlineStr"/>
+      <c r="AA364" t="inlineStr"/>
     </row>
     <row r="365" ht="22" customHeight="1">
       <c r="A365" s="8" t="n">
@@ -34853,6 +37363,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z365" t="inlineStr"/>
+      <c r="AA365" t="inlineStr"/>
     </row>
     <row r="366" ht="22" customHeight="1">
       <c r="A366" s="2" t="n">
@@ -34937,6 +37449,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z366" t="inlineStr"/>
+      <c r="AA366" t="inlineStr"/>
     </row>
     <row r="367" ht="22" customHeight="1">
       <c r="A367" s="8" t="n">
@@ -35021,6 +37535,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z367" t="inlineStr"/>
+      <c r="AA367" t="inlineStr"/>
     </row>
     <row r="368" ht="22" customHeight="1">
       <c r="A368" s="2" t="n">
@@ -35105,6 +37621,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z368" t="inlineStr"/>
+      <c r="AA368" t="inlineStr"/>
     </row>
     <row r="369" ht="22" customHeight="1">
       <c r="A369" s="8" t="n">
@@ -35189,6 +37707,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z369" t="inlineStr"/>
+      <c r="AA369" t="inlineStr"/>
     </row>
     <row r="370" ht="22" customHeight="1">
       <c r="A370" s="2" t="n">
@@ -35301,6 +37821,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z370" t="inlineStr"/>
+      <c r="AA370" t="inlineStr"/>
     </row>
     <row r="371" ht="22" customHeight="1">
       <c r="A371" s="8" t="n">
@@ -35393,6 +37915,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="inlineStr"/>
     </row>
     <row r="372" ht="22" customHeight="1">
       <c r="A372" s="2" t="n">
@@ -35477,6 +38001,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z372" t="inlineStr"/>
+      <c r="AA372" t="inlineStr"/>
     </row>
     <row r="373" ht="22" customHeight="1">
       <c r="A373" s="8" t="n">
@@ -35569,6 +38095,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z373" t="inlineStr"/>
+      <c r="AA373" t="inlineStr"/>
     </row>
     <row r="374" ht="22" customHeight="1">
       <c r="A374" s="2" t="n">
@@ -35653,6 +38181,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z374" t="inlineStr"/>
+      <c r="AA374" t="inlineStr"/>
     </row>
     <row r="375" ht="22" customHeight="1">
       <c r="A375" s="8" t="n">
@@ -35737,6 +38267,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="inlineStr"/>
     </row>
     <row r="376" ht="22" customHeight="1">
       <c r="A376" s="2" t="n">
@@ -35825,6 +38357,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z376" t="inlineStr"/>
+      <c r="AA376" t="inlineStr"/>
     </row>
     <row r="377" ht="22" customHeight="1">
       <c r="A377" s="8" t="n">
@@ -35909,6 +38443,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="inlineStr"/>
     </row>
     <row r="378" ht="22" customHeight="1">
       <c r="A378" s="2" t="n">
@@ -35997,6 +38533,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr"/>
     </row>
     <row r="379" ht="22" customHeight="1">
       <c r="A379" s="8" t="n">
@@ -36109,6 +38647,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z379" t="inlineStr"/>
+      <c r="AA379" t="inlineStr"/>
     </row>
     <row r="380" ht="22" customHeight="1">
       <c r="A380" s="2" t="n">
@@ -36209,6 +38749,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z380" t="inlineStr"/>
+      <c r="AA380" t="inlineStr"/>
     </row>
     <row r="381" ht="22" customHeight="1">
       <c r="A381" s="8" t="n">
@@ -36289,6 +38831,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z381" t="inlineStr"/>
+      <c r="AA381" t="inlineStr"/>
     </row>
     <row r="382" ht="22" customHeight="1">
       <c r="A382" s="2" t="n">
@@ -36373,6 +38917,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z382" t="inlineStr"/>
+      <c r="AA382" t="inlineStr"/>
     </row>
     <row r="383" ht="22" customHeight="1">
       <c r="A383" s="8" t="n">
@@ -36485,6 +39031,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z383" t="inlineStr"/>
+      <c r="AA383" t="inlineStr"/>
     </row>
     <row r="384" ht="22" customHeight="1">
       <c r="A384" s="2" t="n">
@@ -36601,6 +39149,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z384" t="inlineStr"/>
+      <c r="AA384" t="inlineStr"/>
     </row>
     <row r="385" ht="22" customHeight="1">
       <c r="A385" s="8" t="n">
@@ -36709,6 +39259,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z385" t="inlineStr"/>
+      <c r="AA385" t="inlineStr"/>
     </row>
     <row r="386" ht="22" customHeight="1">
       <c r="A386" s="2" t="n">
@@ -36785,6 +39337,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z386" t="inlineStr"/>
+      <c r="AA386" t="inlineStr"/>
     </row>
     <row r="387" ht="22" customHeight="1">
       <c r="A387" s="8" t="n">
@@ -36869,6 +39423,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z387" t="inlineStr"/>
+      <c r="AA387" t="inlineStr"/>
     </row>
     <row r="388" ht="22" customHeight="1">
       <c r="A388" s="2" t="n">
@@ -36957,6 +39513,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z388" t="inlineStr"/>
+      <c r="AA388" t="inlineStr"/>
     </row>
     <row r="389" ht="22" customHeight="1">
       <c r="A389" s="8" t="n">
@@ -37041,6 +39599,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z389" t="inlineStr"/>
+      <c r="AA389" t="inlineStr"/>
     </row>
     <row r="390" ht="22" customHeight="1">
       <c r="A390" s="2" t="n">
@@ -37161,6 +39721,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z390" t="inlineStr"/>
+      <c r="AA390" t="inlineStr"/>
     </row>
     <row r="391" ht="22" customHeight="1">
       <c r="A391" s="8" t="n">
@@ -37245,6 +39807,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z391" t="inlineStr"/>
+      <c r="AA391" t="inlineStr"/>
     </row>
     <row r="392" ht="22" customHeight="1">
       <c r="A392" s="2" t="n">
@@ -37345,6 +39909,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z392" t="inlineStr"/>
+      <c r="AA392" t="inlineStr"/>
     </row>
     <row r="393" ht="22" customHeight="1">
       <c r="A393" s="8" t="n">
@@ -37465,6 +40031,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z393" t="inlineStr"/>
+      <c r="AA393" t="inlineStr"/>
     </row>
     <row r="394" ht="22" customHeight="1">
       <c r="A394" s="2" t="n">
@@ -37549,6 +40117,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z394" t="inlineStr"/>
+      <c r="AA394" t="inlineStr"/>
     </row>
     <row r="395" ht="22" customHeight="1">
       <c r="A395" s="8" t="n">
@@ -37633,6 +40203,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z395" t="inlineStr"/>
+      <c r="AA395" t="inlineStr"/>
     </row>
     <row r="396" ht="22" customHeight="1">
       <c r="A396" s="2" t="n">
@@ -37745,6 +40317,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z396" t="inlineStr"/>
+      <c r="AA396" t="inlineStr"/>
     </row>
     <row r="397" ht="22" customHeight="1">
       <c r="A397" s="8" t="n">
@@ -37829,6 +40403,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z397" t="inlineStr"/>
+      <c r="AA397" t="inlineStr"/>
     </row>
     <row r="398" ht="22" customHeight="1">
       <c r="A398" s="2" t="n">
@@ -37917,6 +40493,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z398" t="inlineStr"/>
+      <c r="AA398" t="inlineStr"/>
     </row>
     <row r="399" ht="22" customHeight="1">
       <c r="A399" s="8" t="n">
@@ -38025,6 +40603,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z399" t="inlineStr"/>
+      <c r="AA399" t="inlineStr"/>
     </row>
     <row r="400" ht="22" customHeight="1">
       <c r="A400" s="2" t="n">
@@ -38109,6 +40689,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z400" t="inlineStr"/>
+      <c r="AA400" t="inlineStr"/>
     </row>
     <row r="401" ht="22" customHeight="1">
       <c r="A401" s="8" t="n">
@@ -38193,6 +40775,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z401" t="inlineStr"/>
+      <c r="AA401" t="inlineStr"/>
     </row>
     <row r="402" ht="22" customHeight="1">
       <c r="A402" s="2" t="n">
@@ -38277,6 +40861,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z402" t="inlineStr"/>
+      <c r="AA402" t="inlineStr"/>
     </row>
     <row r="403" ht="22" customHeight="1">
       <c r="A403" s="8" t="n">
@@ -38357,6 +40943,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z403" t="inlineStr"/>
+      <c r="AA403" t="inlineStr"/>
     </row>
     <row r="404" ht="22" customHeight="1">
       <c r="A404" s="2" t="n">
@@ -38473,6 +41061,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z404" t="inlineStr"/>
+      <c r="AA404" t="inlineStr"/>
     </row>
     <row r="405" ht="22" customHeight="1">
       <c r="A405" s="8" t="n">
@@ -38561,6 +41151,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z405" t="inlineStr"/>
+      <c r="AA405" t="inlineStr"/>
     </row>
     <row r="406" ht="22" customHeight="1">
       <c r="A406" s="2" t="n">
@@ -38645,6 +41237,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z406" t="inlineStr"/>
+      <c r="AA406" t="inlineStr"/>
     </row>
     <row r="407" ht="22" customHeight="1">
       <c r="A407" s="8" t="n">
@@ -38729,6 +41323,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z407" t="inlineStr"/>
+      <c r="AA407" t="inlineStr"/>
     </row>
     <row r="408" ht="22" customHeight="1">
       <c r="A408" s="2" t="n">
@@ -38813,6 +41409,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z408" t="inlineStr"/>
+      <c r="AA408" t="inlineStr"/>
     </row>
     <row r="409" ht="22" customHeight="1">
       <c r="A409" s="8" t="n">
@@ -38929,6 +41527,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z409" t="inlineStr"/>
+      <c r="AA409" t="inlineStr"/>
     </row>
     <row r="410" ht="22" customHeight="1">
       <c r="A410" s="2" t="n">
@@ -39013,6 +41613,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z410" t="inlineStr"/>
+      <c r="AA410" t="inlineStr"/>
     </row>
     <row r="411" ht="22" customHeight="1">
       <c r="A411" s="8" t="n">
@@ -39093,6 +41695,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z411" t="inlineStr"/>
+      <c r="AA411" t="inlineStr"/>
     </row>
     <row r="412" ht="22" customHeight="1">
       <c r="A412" s="2" t="n">
@@ -39157,6 +41761,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z412" t="inlineStr"/>
+      <c r="AA412" t="inlineStr"/>
     </row>
     <row r="413" ht="22" customHeight="1">
       <c r="A413" s="8" t="n">
@@ -39241,6 +41847,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z413" t="inlineStr"/>
+      <c r="AA413" t="inlineStr"/>
     </row>
     <row r="414" ht="22" customHeight="1">
       <c r="A414" s="2" t="n">
@@ -39325,6 +41933,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z414" t="inlineStr"/>
+      <c r="AA414" t="inlineStr"/>
     </row>
     <row r="415" ht="22" customHeight="1">
       <c r="A415" s="8" t="n">
@@ -39413,6 +42023,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z415" t="inlineStr"/>
+      <c r="AA415" t="inlineStr"/>
     </row>
     <row r="416" ht="22" customHeight="1">
       <c r="A416" s="2" t="n">
@@ -39505,6 +42117,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z416" t="inlineStr"/>
+      <c r="AA416" t="inlineStr"/>
     </row>
     <row r="417" ht="22" customHeight="1">
       <c r="A417" s="8" t="n">
@@ -39589,6 +42203,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z417" t="inlineStr"/>
+      <c r="AA417" t="inlineStr"/>
     </row>
     <row r="418" ht="22" customHeight="1">
       <c r="A418" s="2" t="n">
@@ -39685,6 +42301,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z418" t="inlineStr"/>
+      <c r="AA418" t="inlineStr"/>
     </row>
     <row r="419" ht="22" customHeight="1">
       <c r="A419" s="8" t="n">
@@ -39765,6 +42383,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z419" t="inlineStr"/>
+      <c r="AA419" t="inlineStr"/>
     </row>
     <row r="420" ht="22" customHeight="1">
       <c r="A420" s="2" t="n">
@@ -39849,6 +42469,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z420" t="inlineStr"/>
+      <c r="AA420" t="inlineStr"/>
     </row>
     <row r="421" ht="22" customHeight="1">
       <c r="A421" s="8" t="n">
@@ -39965,6 +42587,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z421" t="inlineStr"/>
+      <c r="AA421" t="inlineStr"/>
     </row>
     <row r="422" ht="22" customHeight="1">
       <c r="A422" s="2" t="n">
@@ -40049,6 +42673,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z422" t="inlineStr"/>
+      <c r="AA422" t="inlineStr"/>
     </row>
     <row r="423" ht="22" customHeight="1">
       <c r="A423" s="8" t="n">
@@ -40137,6 +42763,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z423" t="inlineStr"/>
+      <c r="AA423" t="inlineStr"/>
     </row>
     <row r="424" ht="22" customHeight="1">
       <c r="A424" s="2" t="n">
@@ -40249,6 +42877,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z424" t="inlineStr"/>
+      <c r="AA424" t="inlineStr"/>
     </row>
     <row r="425" ht="22" customHeight="1">
       <c r="A425" s="8" t="n">
@@ -40333,6 +42963,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z425" t="inlineStr"/>
+      <c r="AA425" t="inlineStr"/>
     </row>
     <row r="426" ht="22" customHeight="1">
       <c r="A426" s="2" t="n">
@@ -40437,6 +43069,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z426" t="inlineStr"/>
+      <c r="AA426" t="inlineStr"/>
     </row>
     <row r="427" ht="22" customHeight="1">
       <c r="A427" s="8" t="n">
@@ -40521,6 +43155,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z427" t="inlineStr"/>
+      <c r="AA427" t="inlineStr"/>
     </row>
     <row r="428" ht="22" customHeight="1">
       <c r="A428" s="2" t="n">
@@ -40613,6 +43249,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z428" t="inlineStr"/>
+      <c r="AA428" t="inlineStr"/>
     </row>
     <row r="429" ht="22" customHeight="1">
       <c r="A429" s="8" t="n">
@@ -40701,6 +43339,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z429" t="inlineStr"/>
+      <c r="AA429" t="inlineStr"/>
     </row>
     <row r="430" ht="22" customHeight="1">
       <c r="A430" s="2" t="n">
@@ -40811,6 +43451,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z430" t="inlineStr"/>
+      <c r="AA430" t="inlineStr"/>
     </row>
     <row r="431" ht="22" customHeight="1">
       <c r="A431" s="8" t="n">
@@ -40919,6 +43561,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z431" t="inlineStr"/>
+      <c r="AA431" t="inlineStr"/>
     </row>
     <row r="432" ht="22" customHeight="1">
       <c r="A432" s="2" t="n">
@@ -40987,6 +43631,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z432" t="inlineStr"/>
+      <c r="AA432" t="inlineStr"/>
     </row>
     <row r="433" ht="22" customHeight="1">
       <c r="A433" s="8" t="n">
@@ -41051,6 +43697,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z433" t="inlineStr"/>
+      <c r="AA433" t="inlineStr"/>
     </row>
     <row r="434" ht="22" customHeight="1">
       <c r="A434" s="2" t="n">
@@ -41135,6 +43783,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z434" t="inlineStr"/>
+      <c r="AA434" t="inlineStr"/>
     </row>
     <row r="435" ht="22" customHeight="1">
       <c r="A435" s="8" t="n">
@@ -41199,6 +43849,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z435" t="inlineStr"/>
+      <c r="AA435" t="inlineStr"/>
     </row>
     <row r="436" ht="22" customHeight="1">
       <c r="A436" s="2" t="n">
@@ -41287,6 +43939,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z436" t="inlineStr"/>
+      <c r="AA436" t="inlineStr"/>
     </row>
     <row r="437" ht="22" customHeight="1">
       <c r="A437" s="8" t="n">
@@ -41375,6 +44029,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z437" t="inlineStr"/>
+      <c r="AA437" t="inlineStr"/>
     </row>
     <row r="438" ht="22" customHeight="1">
       <c r="A438" s="2" t="n">
@@ -41491,6 +44147,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z438" t="inlineStr"/>
+      <c r="AA438" t="inlineStr"/>
     </row>
     <row r="439" ht="22" customHeight="1">
       <c r="A439" s="8" t="n">
@@ -41599,6 +44257,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z439" t="inlineStr"/>
+      <c r="AA439" t="inlineStr"/>
     </row>
     <row r="440" ht="22" customHeight="1">
       <c r="A440" s="2" t="n">
@@ -41683,6 +44343,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z440" t="inlineStr"/>
+      <c r="AA440" t="inlineStr"/>
     </row>
     <row r="441" ht="22" customHeight="1">
       <c r="A441" s="8" t="n">
@@ -41767,6 +44429,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z441" t="inlineStr"/>
+      <c r="AA441" t="inlineStr"/>
     </row>
     <row r="442" ht="22" customHeight="1">
       <c r="A442" s="2" t="n">
@@ -41851,6 +44515,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z442" t="inlineStr"/>
+      <c r="AA442" t="inlineStr"/>
     </row>
     <row r="443" ht="22" customHeight="1">
       <c r="A443" s="8" t="n">
@@ -41935,6 +44601,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z443" t="inlineStr"/>
+      <c r="AA443" t="inlineStr"/>
     </row>
     <row r="444" ht="22" customHeight="1">
       <c r="A444" s="2" t="n">
@@ -42019,6 +44687,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z444" t="inlineStr"/>
+      <c r="AA444" t="inlineStr"/>
     </row>
     <row r="445" ht="22" customHeight="1">
       <c r="A445" s="8" t="n">
@@ -42135,6 +44805,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z445" t="inlineStr"/>
+      <c r="AA445" t="inlineStr"/>
     </row>
     <row r="446" ht="22" customHeight="1">
       <c r="A446" s="2" t="n">
@@ -42191,6 +44863,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z446" t="inlineStr"/>
+      <c r="AA446" t="inlineStr"/>
     </row>
     <row r="447" ht="22" customHeight="1">
       <c r="A447" s="8" t="n">
@@ -42271,6 +44945,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z447" t="inlineStr"/>
+      <c r="AA447" t="inlineStr"/>
     </row>
     <row r="448" ht="22" customHeight="1">
       <c r="A448" s="2" t="n">
@@ -42379,6 +45055,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z448" t="inlineStr"/>
+      <c r="AA448" t="inlineStr"/>
     </row>
     <row r="449" ht="22" customHeight="1">
       <c r="A449" s="8" t="n">
@@ -42459,6 +45137,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z449" t="inlineStr"/>
+      <c r="AA449" t="inlineStr"/>
     </row>
     <row r="450" ht="22" customHeight="1">
       <c r="A450" s="2" t="n">
@@ -42543,6 +45223,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z450" t="inlineStr"/>
+      <c r="AA450" t="inlineStr"/>
     </row>
     <row r="451" ht="22" customHeight="1">
       <c r="A451" s="8" t="n">
@@ -42631,6 +45313,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z451" t="inlineStr"/>
+      <c r="AA451" t="inlineStr"/>
     </row>
     <row r="452" ht="22" customHeight="1">
       <c r="A452" s="2" t="n">
@@ -42743,6 +45427,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>T-16</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="22" customHeight="1">
       <c r="A453" s="8" t="n">
@@ -42859,6 +45553,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z453" t="inlineStr"/>
+      <c r="AA453" t="inlineStr"/>
     </row>
     <row r="454" ht="22" customHeight="1">
       <c r="A454" s="2" t="n">
@@ -42947,6 +45643,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z454" t="inlineStr"/>
+      <c r="AA454" t="inlineStr"/>
     </row>
     <row r="455" ht="22" customHeight="1">
       <c r="A455" s="8" t="n">
@@ -43051,6 +45749,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z455" t="inlineStr"/>
+      <c r="AA455" t="inlineStr"/>
     </row>
     <row r="456" ht="22" customHeight="1">
       <c r="A456" s="2" t="n">
@@ -43135,6 +45835,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z456" t="inlineStr"/>
+      <c r="AA456" t="inlineStr"/>
     </row>
     <row r="457" ht="22" customHeight="1">
       <c r="A457" s="8" t="n">
@@ -43199,6 +45901,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z457" t="inlineStr"/>
+      <c r="AA457" t="inlineStr"/>
     </row>
     <row r="458" ht="22" customHeight="1">
       <c r="A458" s="2" t="n">
@@ -43283,6 +45987,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z458" t="inlineStr"/>
+      <c r="AA458" t="inlineStr"/>
     </row>
     <row r="459" ht="22" customHeight="1">
       <c r="A459" s="8" t="n">
@@ -43367,6 +46073,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z459" t="inlineStr"/>
+      <c r="AA459" t="inlineStr"/>
     </row>
     <row r="460" ht="22" customHeight="1">
       <c r="A460" s="2" t="n">
@@ -43479,6 +46187,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z460" t="inlineStr"/>
+      <c r="AA460" t="inlineStr"/>
     </row>
     <row r="461" ht="22" customHeight="1">
       <c r="A461" s="8" t="n">
@@ -43591,6 +46301,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z461" t="inlineStr"/>
+      <c r="AA461" t="inlineStr"/>
     </row>
     <row r="462" ht="22" customHeight="1">
       <c r="A462" s="2" t="n">
@@ -43679,6 +46391,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z462" t="inlineStr"/>
+      <c r="AA462" t="inlineStr"/>
     </row>
     <row r="463" ht="22" customHeight="1">
       <c r="A463" s="8" t="n">
@@ -43763,6 +46477,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z463" t="inlineStr"/>
+      <c r="AA463" t="inlineStr"/>
     </row>
     <row r="464" ht="22" customHeight="1">
       <c r="A464" s="2" t="n">
@@ -43847,6 +46563,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z464" t="inlineStr"/>
+      <c r="AA464" t="inlineStr"/>
     </row>
     <row r="465" ht="22" customHeight="1">
       <c r="A465" s="8" t="n">
@@ -43931,6 +46649,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z465" t="inlineStr"/>
+      <c r="AA465" t="inlineStr"/>
     </row>
     <row r="466" ht="22" customHeight="1">
       <c r="A466" s="2" t="n">
@@ -44039,6 +46759,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z466" t="inlineStr"/>
+      <c r="AA466" t="inlineStr"/>
     </row>
     <row r="467" ht="22" customHeight="1">
       <c r="A467" s="8" t="n">
@@ -44123,6 +46845,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z467" t="inlineStr"/>
+      <c r="AA467" t="inlineStr"/>
     </row>
     <row r="468" ht="22" customHeight="1">
       <c r="A468" s="2" t="n">
@@ -44207,6 +46931,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z468" t="inlineStr"/>
+      <c r="AA468" t="inlineStr"/>
     </row>
     <row r="469" ht="22" customHeight="1">
       <c r="A469" s="8" t="n">
@@ -44307,6 +47033,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z469" t="inlineStr"/>
+      <c r="AA469" t="inlineStr"/>
     </row>
     <row r="470" ht="22" customHeight="1">
       <c r="A470" s="2" t="n">
@@ -44419,6 +47147,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z470" t="inlineStr"/>
+      <c r="AA470" t="inlineStr"/>
     </row>
     <row r="471" ht="22" customHeight="1">
       <c r="A471" s="8" t="n">
@@ -44535,6 +47265,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z471" t="inlineStr"/>
+      <c r="AA471" t="inlineStr"/>
     </row>
     <row r="472" ht="22" customHeight="1">
       <c r="A472" s="2" t="n">
@@ -44643,6 +47375,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z472" t="inlineStr"/>
+      <c r="AA472" t="inlineStr"/>
     </row>
     <row r="473" ht="22" customHeight="1">
       <c r="A473" s="8" t="n">
@@ -44711,6 +47445,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z473" t="inlineStr"/>
+      <c r="AA473" t="inlineStr"/>
     </row>
     <row r="474" ht="22" customHeight="1">
       <c r="A474" s="2" t="n">
@@ -44823,6 +47559,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z474" t="inlineStr"/>
+      <c r="AA474" t="inlineStr"/>
     </row>
     <row r="475" ht="22" customHeight="1">
       <c r="A475" s="8" t="n">
@@ -44907,6 +47645,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z475" t="inlineStr"/>
+      <c r="AA475" t="inlineStr"/>
     </row>
     <row r="476" ht="22" customHeight="1">
       <c r="A476" s="2" t="n">
@@ -45021,6 +47761,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z476" t="inlineStr"/>
+      <c r="AA476" t="inlineStr"/>
     </row>
     <row r="477" ht="22" customHeight="1">
       <c r="A477" s="8" t="n">
@@ -45105,6 +47847,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z477" t="inlineStr"/>
+      <c r="AA477" t="inlineStr"/>
     </row>
     <row r="478" ht="22" customHeight="1">
       <c r="A478" s="2" t="n">
@@ -45189,6 +47933,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z478" t="inlineStr"/>
+      <c r="AA478" t="inlineStr"/>
     </row>
     <row r="479" ht="22" customHeight="1">
       <c r="A479" s="8" t="n">
@@ -45273,6 +48019,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z479" t="inlineStr"/>
+      <c r="AA479" t="inlineStr"/>
     </row>
     <row r="480" ht="22" customHeight="1">
       <c r="A480" s="2" t="n">
@@ -45369,6 +48117,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z480" t="inlineStr"/>
+      <c r="AA480" t="inlineStr"/>
     </row>
     <row r="481" ht="22" customHeight="1">
       <c r="A481" s="8" t="n">
@@ -45481,6 +48231,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z481" t="inlineStr"/>
+      <c r="AA481" t="inlineStr"/>
     </row>
     <row r="482" ht="22" customHeight="1">
       <c r="A482" s="2" t="n">
@@ -45569,6 +48321,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z482" t="inlineStr"/>
+      <c r="AA482" t="inlineStr"/>
     </row>
     <row r="483" ht="22" customHeight="1">
       <c r="A483" s="8" t="n">
@@ -45653,6 +48407,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z483" t="inlineStr"/>
+      <c r="AA483" t="inlineStr"/>
     </row>
     <row r="484" ht="22" customHeight="1">
       <c r="A484" s="2" t="n">
@@ -45759,6 +48515,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z484" t="inlineStr"/>
+      <c r="AA484" t="inlineStr"/>
     </row>
     <row r="485" ht="22" customHeight="1">
       <c r="A485" s="8" t="n">
@@ -45847,6 +48605,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z485" t="inlineStr"/>
+      <c r="AA485" t="inlineStr"/>
     </row>
     <row r="486" ht="22" customHeight="1">
       <c r="A486" s="2" t="n">
@@ -45931,6 +48691,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z486" t="inlineStr"/>
+      <c r="AA486" t="inlineStr"/>
     </row>
     <row r="487" ht="22" customHeight="1">
       <c r="A487" s="8" t="n">
@@ -46051,6 +48813,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z487" t="inlineStr"/>
+      <c r="AA487" t="inlineStr"/>
     </row>
     <row r="488" ht="22" customHeight="1">
       <c r="A488" s="2" t="n">
@@ -46135,6 +48899,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z488" t="inlineStr"/>
+      <c r="AA488" t="inlineStr"/>
     </row>
     <row r="489" ht="22" customHeight="1">
       <c r="A489" s="8" t="n">
@@ -46243,6 +49009,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z489" t="inlineStr"/>
+      <c r="AA489" t="inlineStr"/>
     </row>
     <row r="490" ht="22" customHeight="1">
       <c r="A490" s="2" t="n">
@@ -46327,6 +49095,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z490" t="inlineStr"/>
+      <c r="AA490" t="inlineStr"/>
     </row>
     <row r="491" ht="22" customHeight="1">
       <c r="A491" s="8" t="n">
@@ -46411,6 +49181,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z491" t="inlineStr"/>
+      <c r="AA491" t="inlineStr"/>
     </row>
     <row r="492" ht="22" customHeight="1">
       <c r="A492" s="2" t="n">
@@ -46495,6 +49267,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z492" t="inlineStr"/>
+      <c r="AA492" t="inlineStr"/>
     </row>
     <row r="493" ht="22" customHeight="1">
       <c r="A493" s="8" t="n">
@@ -46605,6 +49379,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z493" t="inlineStr"/>
+      <c r="AA493" t="inlineStr"/>
     </row>
     <row r="494" ht="22" customHeight="1">
       <c r="A494" s="2" t="n">
@@ -46693,6 +49469,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
     </row>
     <row r="495" ht="22" customHeight="1">
       <c r="A495" s="8" t="n">
@@ -46781,6 +49559,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z495" t="inlineStr"/>
+      <c r="AA495" t="inlineStr"/>
     </row>
     <row r="496" ht="22" customHeight="1">
       <c r="A496" s="2" t="n">
@@ -46897,6 +49677,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z496" t="inlineStr"/>
+      <c r="AA496" t="inlineStr"/>
     </row>
     <row r="497" ht="22" customHeight="1">
       <c r="A497" s="8" t="n">
@@ -46981,6 +49763,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z497" t="inlineStr"/>
+      <c r="AA497" t="inlineStr"/>
     </row>
     <row r="498" ht="22" customHeight="1">
       <c r="A498" s="2" t="n">
@@ -47093,6 +49877,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z498" t="inlineStr"/>
+      <c r="AA498" t="inlineStr"/>
     </row>
     <row r="499" ht="22" customHeight="1">
       <c r="A499" s="8" t="n">
@@ -47177,6 +49963,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z499" t="inlineStr"/>
+      <c r="AA499" t="inlineStr"/>
     </row>
     <row r="500" ht="22" customHeight="1">
       <c r="A500" s="2" t="n">
@@ -47277,6 +50065,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z500" t="inlineStr"/>
+      <c r="AA500" t="inlineStr"/>
     </row>
     <row r="501" ht="22" customHeight="1">
       <c r="A501" s="8" t="n">
@@ -47361,6 +50151,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z501" t="inlineStr"/>
+      <c r="AA501" t="inlineStr"/>
     </row>
     <row r="502" ht="22" customHeight="1">
       <c r="A502" s="2" t="n">
@@ -47449,6 +50241,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z502" t="inlineStr"/>
+      <c r="AA502" t="inlineStr"/>
     </row>
     <row r="503" ht="22" customHeight="1">
       <c r="A503" s="8" t="n">
@@ -47564,6 +50358,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z503" t="inlineStr"/>
+      <c r="AA503" t="inlineStr"/>
     </row>
     <row r="504" ht="22" customHeight="1">
       <c r="A504" s="2" t="n">
@@ -47644,6 +50440,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z504" t="inlineStr"/>
+      <c r="AA504" t="inlineStr"/>
     </row>
     <row r="505" ht="22" customHeight="1">
       <c r="A505" s="8" t="n">
@@ -47742,6 +50540,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z505" t="inlineStr"/>
+      <c r="AA505" t="inlineStr"/>
     </row>
     <row r="506" ht="22" customHeight="1">
       <c r="A506" s="2" t="n">
@@ -47826,6 +50626,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z506" t="inlineStr"/>
+      <c r="AA506" t="inlineStr"/>
     </row>
     <row r="507" ht="22" customHeight="1">
       <c r="A507" s="8" t="n">
@@ -47910,6 +50712,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z507" t="inlineStr"/>
+      <c r="AA507" t="inlineStr"/>
     </row>
     <row r="508" ht="22" customHeight="1">
       <c r="A508" s="2" t="n">
@@ -48026,6 +50830,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z508" t="inlineStr"/>
+      <c r="AA508" t="inlineStr"/>
     </row>
     <row r="509" ht="22" customHeight="1">
       <c r="A509" s="8" t="n">
@@ -48106,6 +50912,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z509" t="inlineStr"/>
+      <c r="AA509" t="inlineStr"/>
     </row>
     <row r="510" ht="22" customHeight="1">
       <c r="A510" s="2" t="n">
@@ -48190,6 +50998,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z510" t="inlineStr"/>
+      <c r="AA510" t="inlineStr"/>
     </row>
     <row r="511" ht="22" customHeight="1">
       <c r="A511" s="8" t="n">
@@ -48266,6 +51076,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z511" t="inlineStr"/>
+      <c r="AA511" t="inlineStr"/>
     </row>
     <row r="512" ht="22" customHeight="1">
       <c r="A512" s="2" t="n">
@@ -48354,6 +51166,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z512" t="inlineStr"/>
+      <c r="AA512" t="inlineStr"/>
     </row>
     <row r="513" ht="22" customHeight="1">
       <c r="A513" s="8" t="n">
@@ -48438,6 +51252,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z513" t="inlineStr"/>
+      <c r="AA513" t="inlineStr"/>
     </row>
     <row r="514" ht="22" customHeight="1">
       <c r="A514" s="2" t="n">
@@ -48550,6 +51366,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z514" t="inlineStr"/>
+      <c r="AA514" t="inlineStr"/>
     </row>
     <row r="515" ht="22" customHeight="1">
       <c r="A515" s="8" t="n">
@@ -48634,6 +51452,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z515" t="inlineStr"/>
+      <c r="AA515" t="inlineStr"/>
     </row>
     <row r="516" ht="22" customHeight="1">
       <c r="A516" s="2" t="n">
@@ -48750,6 +51570,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z516" t="inlineStr"/>
+      <c r="AA516" t="inlineStr"/>
     </row>
     <row r="517" ht="22" customHeight="1">
       <c r="A517" s="8" t="n">
@@ -48834,6 +51656,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z517" t="inlineStr"/>
+      <c r="AA517" t="inlineStr"/>
     </row>
     <row r="518" ht="22" customHeight="1">
       <c r="A518" s="2" t="n">
@@ -48922,6 +51746,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z518" t="inlineStr"/>
+      <c r="AA518" t="inlineStr"/>
     </row>
     <row r="519" ht="22" customHeight="1">
       <c r="A519" s="8" t="n">
@@ -49006,6 +51832,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z519" t="inlineStr"/>
+      <c r="AA519" t="inlineStr"/>
     </row>
     <row r="520" ht="22" customHeight="1">
       <c r="A520" s="2" t="n">
@@ -49090,6 +51918,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z520" t="inlineStr"/>
+      <c r="AA520" t="inlineStr"/>
     </row>
     <row r="521" ht="22" customHeight="1">
       <c r="A521" s="8" t="n">
@@ -49174,6 +52004,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z521" t="inlineStr"/>
+      <c r="AA521" t="inlineStr"/>
     </row>
     <row r="522" ht="22" customHeight="1">
       <c r="A522" s="2" t="n">
@@ -49290,6 +52122,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z522" t="inlineStr"/>
+      <c r="AA522" t="inlineStr"/>
     </row>
     <row r="523" ht="22" customHeight="1">
       <c r="A523" s="8" t="n">
@@ -49406,6 +52240,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z523" t="inlineStr"/>
+      <c r="AA523" t="inlineStr"/>
     </row>
     <row r="524" ht="22" customHeight="1">
       <c r="A524" s="2" t="n">
@@ -49522,6 +52358,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z524" t="inlineStr"/>
+      <c r="AA524" t="inlineStr"/>
     </row>
     <row r="525" ht="22" customHeight="1">
       <c r="A525" s="8" t="n">
@@ -49642,6 +52480,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z525" t="inlineStr"/>
+      <c r="AA525" t="inlineStr"/>
     </row>
     <row r="526" ht="22" customHeight="1">
       <c r="A526" s="2" t="n">
@@ -49754,6 +52594,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z526" t="inlineStr"/>
+      <c r="AA526" t="inlineStr"/>
     </row>
     <row r="527" ht="22" customHeight="1">
       <c r="A527" s="8" t="n">
@@ -49842,6 +52684,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z527" t="inlineStr"/>
+      <c r="AA527" t="inlineStr"/>
     </row>
     <row r="528" ht="22" customHeight="1">
       <c r="A528" s="2" t="n">
@@ -49926,6 +52770,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z528" t="inlineStr"/>
+      <c r="AA528" t="inlineStr"/>
     </row>
     <row r="529" ht="22" customHeight="1">
       <c r="A529" s="8" t="n">
@@ -50006,6 +52852,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z529" t="inlineStr"/>
+      <c r="AA529" t="inlineStr"/>
     </row>
     <row r="530" ht="22" customHeight="1">
       <c r="A530" s="2" t="n">
@@ -50090,6 +52938,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z530" t="inlineStr"/>
+      <c r="AA530" t="inlineStr"/>
     </row>
     <row r="531" ht="22" customHeight="1">
       <c r="A531" s="8" t="n">
@@ -50174,6 +53024,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z531" t="inlineStr"/>
+      <c r="AA531" t="inlineStr"/>
     </row>
     <row r="532" ht="22" customHeight="1">
       <c r="A532" s="2" t="n">
@@ -50270,6 +53122,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z532" t="inlineStr"/>
+      <c r="AA532" t="inlineStr"/>
     </row>
     <row r="533" ht="22" customHeight="1">
       <c r="A533" s="8" t="n">
@@ -50358,6 +53212,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z533" t="inlineStr"/>
+      <c r="AA533" t="inlineStr"/>
     </row>
     <row r="534" ht="22" customHeight="1">
       <c r="A534" s="2" t="n">
@@ -50474,6 +53330,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z534" t="inlineStr"/>
+      <c r="AA534" t="inlineStr"/>
     </row>
     <row r="535" ht="22" customHeight="1">
       <c r="A535" s="8" t="n">
@@ -50566,6 +53424,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z535" t="inlineStr"/>
+      <c r="AA535" t="inlineStr"/>
     </row>
     <row r="536" ht="22" customHeight="1">
       <c r="A536" s="2" t="n">
@@ -50676,6 +53536,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z536" t="inlineStr"/>
+      <c r="AA536" t="inlineStr"/>
     </row>
     <row r="537" ht="22" customHeight="1">
       <c r="A537" s="8" t="n">
@@ -50792,6 +53654,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z537" t="inlineStr"/>
+      <c r="AA537" t="inlineStr"/>
     </row>
     <row r="538" ht="22" customHeight="1">
       <c r="A538" s="2" t="n">
@@ -50908,6 +53772,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z538" t="inlineStr"/>
+      <c r="AA538" t="inlineStr"/>
     </row>
     <row r="539" ht="22" customHeight="1">
       <c r="A539" s="8" t="n">
@@ -50992,6 +53858,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z539" t="inlineStr"/>
+      <c r="AA539" t="inlineStr"/>
     </row>
     <row r="540" ht="22" customHeight="1">
       <c r="A540" s="2" t="n">
@@ -51112,6 +53980,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z540" t="inlineStr"/>
+      <c r="AA540" t="inlineStr"/>
     </row>
     <row r="541" ht="22" customHeight="1">
       <c r="A541" s="8" t="n">
@@ -51196,6 +54066,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z541" t="inlineStr"/>
+      <c r="AA541" t="inlineStr"/>
     </row>
     <row r="542" ht="22" customHeight="1">
       <c r="A542" s="2" t="n">
@@ -51308,6 +54180,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>T-17</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="543" ht="22" customHeight="1">
       <c r="A543" s="8" t="n">
@@ -51392,6 +54274,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z543" t="inlineStr"/>
+      <c r="AA543" t="inlineStr"/>
     </row>
     <row r="544" ht="22" customHeight="1">
       <c r="A544" s="2" t="n">
@@ -51476,6 +54360,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z544" t="inlineStr"/>
+      <c r="AA544" t="inlineStr"/>
     </row>
     <row r="545" ht="22" customHeight="1">
       <c r="A545" s="8" t="n">
@@ -51592,6 +54478,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z545" t="inlineStr"/>
+      <c r="AA545" t="inlineStr"/>
     </row>
     <row r="546" ht="22" customHeight="1">
       <c r="A546" s="2" t="n">
@@ -51676,6 +54564,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z546" t="inlineStr"/>
+      <c r="AA546" t="inlineStr"/>
     </row>
     <row r="547" ht="22" customHeight="1">
       <c r="A547" s="8" t="n">
@@ -51756,6 +54646,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z547" t="inlineStr"/>
+      <c r="AA547" t="inlineStr"/>
     </row>
     <row r="548" ht="22" customHeight="1">
       <c r="A548" s="2" t="n">
@@ -51872,6 +54764,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z548" t="inlineStr"/>
+      <c r="AA548" t="inlineStr"/>
     </row>
     <row r="549" ht="22" customHeight="1">
       <c r="A549" s="8" t="n">
@@ -51956,6 +54850,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z549" t="inlineStr"/>
+      <c r="AA549" t="inlineStr"/>
     </row>
     <row r="550" ht="22" customHeight="1">
       <c r="A550" s="2" t="n">
@@ -52036,6 +54932,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z550" t="inlineStr"/>
+      <c r="AA550" t="inlineStr"/>
     </row>
     <row r="551" ht="22" customHeight="1">
       <c r="A551" s="8" t="n">
@@ -52124,6 +55022,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z551" t="inlineStr"/>
+      <c r="AA551" t="inlineStr"/>
     </row>
     <row r="552" ht="22" customHeight="1">
       <c r="A552" s="2" t="n">
@@ -52212,6 +55112,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z552" t="inlineStr"/>
+      <c r="AA552" t="inlineStr"/>
     </row>
     <row r="553" ht="22" customHeight="1">
       <c r="A553" s="8" t="n">
@@ -52296,6 +55198,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z553" t="inlineStr"/>
+      <c r="AA553" t="inlineStr"/>
     </row>
     <row r="554" ht="22" customHeight="1">
       <c r="A554" s="2" t="n">
@@ -52376,6 +55280,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z554" t="inlineStr"/>
+      <c r="AA554" t="inlineStr"/>
     </row>
     <row r="555" ht="22" customHeight="1">
       <c r="A555" s="8" t="n">
@@ -52460,6 +55366,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z555" t="inlineStr"/>
+      <c r="AA555" t="inlineStr"/>
     </row>
     <row r="556" ht="22" customHeight="1">
       <c r="A556" s="2" t="n">
@@ -52576,6 +55484,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z556" t="inlineStr"/>
+      <c r="AA556" t="inlineStr"/>
     </row>
     <row r="557" ht="22" customHeight="1">
       <c r="A557" s="8" t="n">
@@ -52676,6 +55586,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>T-28</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
     </row>
     <row r="558" ht="22" customHeight="1">
       <c r="A558" s="2" t="n">
@@ -52760,6 +55680,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z558" t="inlineStr"/>
+      <c r="AA558" t="inlineStr"/>
     </row>
     <row r="559" ht="22" customHeight="1">
       <c r="A559" s="8" t="n">
@@ -52876,6 +55798,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z559" t="inlineStr"/>
+      <c r="AA559" t="inlineStr"/>
     </row>
     <row r="560" ht="22" customHeight="1">
       <c r="A560" s="2" t="n">
@@ -52960,6 +55884,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z560" t="inlineStr"/>
+      <c r="AA560" t="inlineStr"/>
     </row>
     <row r="561" ht="22" customHeight="1">
       <c r="A561" s="8" t="n">
@@ -53040,6 +55966,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z561" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="22" customHeight="1">
       <c r="A562" s="2" t="n">
@@ -53152,6 +56088,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z562" t="inlineStr"/>
+      <c r="AA562" t="inlineStr"/>
     </row>
     <row r="563" ht="22" customHeight="1">
       <c r="A563" s="8" t="n">
@@ -53238,6 +56176,16 @@
       <c r="X563" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z563" t="inlineStr">
+        <is>
+          <t>T-41</t>
+        </is>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -38892,7 +38892,7 @@
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>25-17</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="C413" s="9" t="inlineStr">

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$563</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35840,7 +35840,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
@@ -54726,7 +54726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -57144,7 +57144,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Samatova Oydin</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -57154,66 +57154,82 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sulaymon qizi</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OR-SH 0346677</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -57223,13 +57239,17 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -57244,7 +57264,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -57252,79 +57272,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr"/>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr"/>
       <c r="R23" s="10" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S23" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T23" s="11" t="inlineStr">
@@ -57339,17 +57339,13 @@
       </c>
       <c r="V23" s="10" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W23" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -57364,7 +57360,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -57372,59 +57368,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
@@ -57437,15 +57453,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -57460,17 +57476,13 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -57480,72 +57492,68 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr"/>
       <c r="R25" s="10" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -57553,10 +57561,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="10" t="inlineStr"/>
+      <c r="V25" s="10" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W25" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -57576,84 +57588,92 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>To'raboyeva Sabrina</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>27.09.2008</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -57661,14 +57681,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W26" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -57688,7 +57704,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -57698,82 +57714,74 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr"/>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 3736287</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr"/>
       <c r="R27" s="10" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S27" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -57782,9 +57790,9 @@
         </is>
       </c>
       <c r="V27" s="10" t="inlineStr"/>
-      <c r="W27" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -57804,7 +57812,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'xtayeva Durdona</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -57814,7 +57822,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -57824,69 +57832,69 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
-        </is>
-      </c>
+          <t>19.06.2008</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>K 3736287</t>
+          <t>UM 03728346</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U28" s="15" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
@@ -57912,17 +57920,13 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -57932,37 +57936,37 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -57970,16 +57974,24 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O29" s="10" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
+        </is>
+      </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q29" s="10" t="inlineStr"/>
+          <t>UM 03730110</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+        </is>
+      </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
@@ -57992,15 +58004,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U29" s="15" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V29" s="10" t="inlineStr"/>
       <c r="W29" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X29" s="7" t="inlineStr">
@@ -58020,13 +58032,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -58036,62 +58052,62 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -58132,7 +58148,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -58142,7 +58158,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -58152,37 +58168,37 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -58192,22 +58208,22 @@
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03752857</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
         </is>
       </c>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
@@ -58225,7 +58241,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="10" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W31" s="13" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -58248,7 +58268,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -58258,97 +58278,85 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>K 4590366</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U32" s="15" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -58368,7 +58376,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -58378,85 +58386,93 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="10" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>K 4590366</t>
+          <t>UM 0438281</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U33" s="15" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V33" s="10" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V33" s="10" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
       <c r="W33" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -58476,7 +58492,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -58486,7 +58502,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -58496,58 +58512,62 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -58557,7 +58577,7 @@
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U34" s="7" t="inlineStr">
@@ -58565,14 +58585,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X34" s="7" t="inlineStr">
@@ -58581,124 +58597,8 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>26-02</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Xusan qizi</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>AB9239333</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>42207935680042</t>
-        </is>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>09.04.2018</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>22.07.1993</t>
-        </is>
-      </c>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>UM 03524597</t>
-        </is>
-      </c>
-      <c r="Q35" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="inlineStr">
-        <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T35" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V35" s="10" t="inlineStr"/>
-      <c r="W35" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X35" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -74064,7 +73964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -75506,76 +75406,92 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Saydaliyeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>Samatova Oydin</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Alimdjan qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Saydaliyeva Sevinch Alimdjan qizi</t>
+          <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AD3193422</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60904075590012</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>03.05.2023</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>PT 0176960</t>
+          <t>OR-SH 0346677</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Sharisabz shahar 2-sonli kasb-hunar maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Kollej</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X18" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -75590,7 +75506,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Soliyeva E'zoza</t>
+          <t>Saydaliyeva Sevinch</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
@@ -75598,62 +75514,62 @@
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Sherbobo qizi</t>
+          <t>Alimdjan qizi</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Soliyeva E'zoza Sherbobo qizi</t>
+          <t>Saydaliyeva Sevinch Alimdjan qizi</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>AD4615905</t>
+          <t>AD3193422</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>61803065680094</t>
+          <t>60904075590012</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>15.09.2023</t>
+          <t>03.05.2023</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>18.03.2006</t>
+          <t>09.04.2007</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr"/>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>UM 02151153</t>
+          <t>PT 0176960</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr"/>
       <c r="R19" s="10" t="inlineStr">
         <is>
-          <t>44-maktab</t>
+          <t>Sharisabz shahar 2-sonli kasb-hunar maktabi</t>
         </is>
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T19" s="11" t="inlineStr"/>
       <c r="U19" s="11" t="inlineStr"/>
       <c r="V19" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr"/>
@@ -75674,7 +75590,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Marjona</t>
+          <t>Soliyeva E'zoza</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -75682,42 +75598,62 @@
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ravshan qizi</t>
+          <t>Sherbobo qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Marjona Ravshan qizi</t>
+          <t>Soliyeva E'zoza Sherbobo qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>AD4615905</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60704065720162</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
+          <t>61803065680094</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>15.09.2023</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>07.04.2006</t>
+          <t>18.03.2006</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>UM 02151153</t>
+        </is>
+      </c>
       <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>44-maktab</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
       <c r="T20" s="5" t="inlineStr"/>
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr"/>
@@ -75738,7 +75674,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Suyunova Ruxshona</t>
+          <t>Suyunova Marjona</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -75746,30 +75682,30 @@
       <c r="F21" s="11" t="inlineStr"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Karimjon qizi</t>
+          <t>Ravshan qizi</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Ruxshona Karimjon qizi</t>
+          <t>Suyunova Marjona Ravshan qizi</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>61405065680104</t>
+          <t>60704065720162</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>14.05.2006</t>
+          <t>07.04.2006</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr"/>
@@ -75781,7 +75717,7 @@
       <c r="U21" s="11" t="inlineStr"/>
       <c r="V21" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr"/>
@@ -75802,7 +75738,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Shaxlo</t>
+          <t>Suyunova Ruxshona</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -75810,30 +75746,30 @@
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Tohir qizi</t>
+          <t>Karimjon qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Shaxlo Tohir qizi</t>
+          <t>Suyunova Ruxshona Karimjon qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61305065720094</t>
+          <t>61405065680104</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>13.05.2006</t>
+          <t>14.05.2006</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr"/>
@@ -75845,7 +75781,7 @@
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr"/>
@@ -75866,7 +75802,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Toshkentova Sevinchoy</t>
+          <t>Suyunova Shaxlo</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -75874,62 +75810,42 @@
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Zayniddin qizi</t>
+          <t>Tohir qizi</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Toshkentova Sevinchoy Zayniddin qizi</t>
+          <t>Suyunova Shaxlo Tohir qizi</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>AD6867124</t>
-        </is>
-      </c>
+      <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>60505075730035</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>18.04.2024</t>
-        </is>
-      </c>
+          <t>61305065720094</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>05.05.2007</t>
+          <t>13.05.2006</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UM 03301249</t>
-        </is>
-      </c>
+      <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="10" t="inlineStr"/>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>72-maktab</t>
-        </is>
-      </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
+      <c r="R23" s="10" t="inlineStr"/>
+      <c r="S23" s="11" t="inlineStr"/>
       <c r="T23" s="11" t="inlineStr"/>
       <c r="U23" s="11" t="inlineStr"/>
       <c r="V23" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W23" s="6" t="inlineStr"/>
@@ -75950,7 +75866,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Shirida</t>
+          <t>Toshkentova Sevinchoy</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -75958,50 +75874,50 @@
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Sirojiddin qizi</t>
+          <t>Zayniddin qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Shirida Sirojiddin qizi</t>
+          <t>Toshkentova Sevinchoy Zayniddin qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AD1403124</t>
+          <t>AD6867124</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61906055680059</t>
+          <t>60505075730035</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>30.05.2022</t>
+          <t>18.04.2024</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>19.06.2005</t>
+          <t>05.05.2007</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 1296145</t>
+          <t>UM 03301249</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>72-maktab</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -76034,7 +75950,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tug'izova Zahro</t>
+          <t>To'xtayeva Shirida</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -76042,42 +75958,62 @@
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Tohir qizi</t>
+          <t>Sirojiddin qizi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Tug'izova Zahro Tohir qizi</t>
+          <t>To'xtayeva Shirida Sirojiddin qizi</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>AD1403124</t>
+        </is>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>62912005590041</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr"/>
+          <t>61906055680059</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>29.12.2000</t>
+          <t>19.06.2005</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="8" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>UM 1296145</t>
+        </is>
+      </c>
       <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr"/>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>7-maktab</t>
+        </is>
+      </c>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr"/>
       <c r="V25" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr"/>
@@ -76098,7 +76034,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tursunova Sevinch</t>
+          <t>Tug'izova Zahro</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
@@ -76106,30 +76042,30 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Tohir qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Tursunova Sevinch Turg'un qizi</t>
+          <t>Tug'izova Zahro Tohir qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61905075680098</t>
+          <t>62912005590041</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>19.05.2007</t>
+          <t>29.12.2000</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr"/>
@@ -76141,7 +76077,7 @@
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr"/>
@@ -76162,7 +76098,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina</t>
+          <t>Tursunova Sevinch</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
@@ -76170,62 +76106,42 @@
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Nodir qizi</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina Nodir qizi</t>
+          <t>Tursunova Sevinch Turg'un qizi</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>AD9134105</t>
-        </is>
-      </c>
+      <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>62712075590017</t>
-        </is>
-      </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>24.10.2024</t>
-        </is>
-      </c>
+          <t>61905075680098</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>27.12.2007</t>
+          <t>19.05.2007</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr"/>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>UM 03298099</t>
-        </is>
-      </c>
+      <c r="P27" s="8" t="inlineStr"/>
       <c r="Q27" s="10" t="inlineStr"/>
-      <c r="R27" s="10" t="inlineStr">
-        <is>
-          <t>45-maktab</t>
-        </is>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
+      <c r="R27" s="10" t="inlineStr"/>
+      <c r="S27" s="11" t="inlineStr"/>
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr"/>
       <c r="V27" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W27" s="6" t="inlineStr"/>
@@ -76246,7 +76162,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona</t>
+          <t>Usmonova Jasmina</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -76254,33 +76170,33 @@
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Nodir qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona Botir qizi</t>
+          <t>Usmonova Jasmina Nodir qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AD9713077</t>
+          <t>AD9134105</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61412075590059</t>
+          <t>62712075590017</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>24.10.2024</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>14.12.2007</t>
+          <t>27.12.2007</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -76291,13 +76207,13 @@
       <c r="O28" s="4" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03295752</t>
+          <t>UM 03298099</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -76309,7 +76225,7 @@
       <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr"/>
@@ -76330,49 +76246,41 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr"/>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona Botir qizi</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9713077</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>61412075590059</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>14.12.2007</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -76383,31 +76291,27 @@
       <c r="O29" s="10" t="inlineStr"/>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>UM 03295752</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr"/>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U29" s="15" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V29" s="10" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr"/>
+      <c r="U29" s="11" t="inlineStr"/>
+      <c r="V29" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
       <c r="W29" s="6" t="inlineStr"/>
       <c r="X29" s="7" t="inlineStr">
         <is>
@@ -76426,39 +76330,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>Uzoqova Fazilat</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Jamshid qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu Jamshid qizi</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AD9506052</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61508075590121</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>21,11,2024</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr"/>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -76467,27 +76383,31 @@
       <c r="O30" s="4" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03295886</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>10-maktab</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U30" s="15" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr">
         <is>
@@ -76506,7 +76426,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna</t>
+          <t>Xamrayeva Niginabonu</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
@@ -76514,28 +76434,28 @@
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Hushvaqt qizi</t>
+          <t>Jamshid qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+          <t>Xamrayeva Niginabonu Jamshid qizi</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AE2747402</t>
+          <t>AD9506052</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>40312902560107</t>
+          <t>61508075590121</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>20,05,2025</t>
+          <t>21,11,2024</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr"/>
@@ -76547,18 +76467,18 @@
       <c r="O31" s="10" t="inlineStr"/>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>K 1234480</t>
+          <t>UM 03295886</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>Miroqi sport pedagogika kolleji</t>
+          <t>10-maktab</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T31" s="11" t="inlineStr"/>
@@ -76586,7 +76506,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda</t>
+          <t>Yoqubova Maftuna</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -76594,28 +76514,28 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Hasanovna</t>
+          <t>Hushvaqt qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda Hasanovna</t>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AB7535578</t>
+          <t>AE2747402</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>40108945590034</t>
+          <t>40312902560107</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>22,08,2017</t>
+          <t>20,05,2025</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr"/>
@@ -76627,13 +76547,13 @@
       <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>K 2404534</t>
+          <t>K 1234480</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika kolleji</t>
+          <t>Miroqi sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
@@ -76666,7 +76586,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Yuldosheva Iroda</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
@@ -76674,28 +76594,28 @@
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Hasanovna</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Yuldosheva Iroda Hasanovna</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AB7535578</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>40108945590034</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
+          <t>22,08,2017</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr"/>
@@ -76707,18 +76627,18 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>K 2404534</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>Shahrisabz pedagogika kolleji</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr"/>
@@ -76735,8 +76655,88 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>AD8888020</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>62609075590027</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$563</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31582,7 +31582,7 @@
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C333" s="9" t="inlineStr">
@@ -54726,7 +54726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -56696,7 +56696,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Quysinova Rohshona</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -56704,62 +56704,74 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Azamat qizi</t>
+          <t>To'lqin qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat qizi</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Quysinova Rohshona To'lqin qizi</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AE4905104</t>
+          <t>AE7231113</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61008085680019</t>
+          <t>60406055720067</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>10.08.2008</t>
+          <t>04.06.2005</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Yo'q</t>
+          <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>UM 03730102</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+          <t>UM 02138929</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>70-maktab</t>
+          <t>Ixtisoslashtirilgan maktabni</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -56769,7 +56781,7 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -56777,11 +56789,19 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
+        </is>
+      </c>
+      <c r="W18" s="16" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -56796,17 +56816,13 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Ro'zimurodova Larisa</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -56816,62 +56832,62 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>To'lqin qizi</t>
+          <t>Ma'matali qizi</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>AE7231113</t>
+          <t>AE5324961</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>60406055720067</t>
+          <t>61608085630072</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>04.06.2005</t>
+          <t>16.08.2008</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>Quysinova Rohshona To'lqin qizi</t>
+          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>UM 02138929</t>
+          <t>UM 03742132</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2162723/1195039/000613cf-4d65-4df9-dae0-08dc8cc4bb61?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
         </is>
       </c>
       <c r="R19" s="10" t="inlineStr">
         <is>
-          <t>Ixtisoslashtirilgan maktabni</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S19" s="11" t="inlineStr">
@@ -56881,7 +56897,7 @@
       </c>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -56891,12 +56907,12 @@
       </c>
       <c r="V19" s="10" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'QUYSINOVA ROHSHONA' | bazada: 'Quysinova Ruhshona'; imlo farqi — Shahodatnoma PDF: 'Quysinova Rohshona To'lqin qizi' | bazada: 'Quysinova Ruhshona'</t>
-        </is>
-      </c>
-      <c r="W19" s="16" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT | Shahodatnoma: TRANSLIT</t>
+          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
+        </is>
+      </c>
+      <c r="W19" s="14" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -56916,13 +56932,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>Samadova Nigora</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -56932,62 +56952,58 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ma'matali qizi</t>
+          <t>Abdisamiyevna</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Ma'matali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AE5324961</t>
+          <t>AE1836076</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61608085630072</t>
+          <t>40710895590044</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>05.03.2025</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>07.10.1989</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Ro'zimurodova Larisa Maxmatali qizi</t>
+          <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 03742132</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3801844/3535807/0b280dc6-72ff-4cdc-b46b-4de552e5425e?preview=true</t>
-        </is>
-      </c>
+          <t>O'R-SH 0658073</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -56997,7 +57013,7 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -57005,14 +57021,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — Shahodatnoma PDF: 'Ro'zimurodova Larisa Maxmatali qizi' | bazada: 'Ruzimurodova Larisa'</t>
-        </is>
-      </c>
-      <c r="W20" s="14" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: FARQ</t>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -57032,7 +57044,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Samadova Nigora</t>
+          <t>Saydalimova Ruxshona</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -57042,47 +57054,47 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Abdisamiyevna</t>
+          <t>Sharofiddin qizi</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>AE1836076</t>
+          <t>AE3352294</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>40710895590044</t>
+          <t>61807085590034</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>05.03.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>07.10.1989</t>
+          <t>18.07.2008</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -57092,18 +57104,22 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>Samadova Nigora Abdisamiyevna</t>
+          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>O'R-SH 0658073</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr"/>
+          <t>UM 03754198</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
+        </is>
+      </c>
       <c r="R21" s="10" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati shahrisabz tumanidagi 26-umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S21" s="11" t="inlineStr">
@@ -57113,7 +57129,7 @@
       </c>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -57121,10 +57137,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V21" s="10" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr">
+        <is>
+          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
+        </is>
+      </c>
       <c r="W21" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -57144,7 +57164,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona</t>
+          <t>Shonazarova Vazira</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -57152,79 +57172,59 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:00:00</t>
-        </is>
-      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Sharofiddin qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>AE3352294</t>
+          <t>AE 4233482</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61807085590034</t>
+          <t>61311085680032</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>18.07.2008</t>
+          <t>13.11.2008</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>Saydalimova Ruxshona Sharofiddin qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>UM 03754198</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4087114/3616453/43b2fbe0-3232-4e4c-a111-e6fb3ff34111?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>78-maktab</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
@@ -57239,17 +57239,13 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Familiyadagi xato tuzatildi: Saydalimova Ruxshona Sharofiddin qizi (ID-karta AE3352294, Shahodatnoma UM 03754198, shartnoma #74)</t>
-        </is>
-      </c>
-      <c r="W22" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -57264,7 +57260,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira</t>
+          <t>Shukriyeva Nariye</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -57272,59 +57268,79 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Redvanovna</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Shonazarova Vazira Botir qizi</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr"/>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>AE 4233482</t>
+          <t>AD7767171</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>61311085680032</t>
+          <t>62103085590038</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>13.11.2008</t>
+          <t>21.03.2008</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>Shukriyeva Nariye Redvanovna</t>
+        </is>
+      </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>UM 03730412</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr"/>
+          <t>UM 03751877</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
+        </is>
+      </c>
       <c r="R23" s="10" t="inlineStr">
         <is>
-          <t>78-maktab</t>
+          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S23" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T23" s="11" t="inlineStr">
@@ -57337,15 +57353,15 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V23" s="10" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="V23" s="10" t="inlineStr"/>
+      <c r="W23" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -57360,17 +57376,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Suyunova Maftuna</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -57380,72 +57392,68 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Redvanovna</t>
+          <t>Akbar qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AD7767171</t>
+          <t>AB7166586</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62103085590038</t>
+          <t>61409005680027</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>06.07.2024</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>21.03.2008</t>
+          <t>14.09.2000</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Shukriyeva Nariye Redvanovna</t>
+          <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03751877</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3846904/4159297/b808b42e-a17e-4725-b75a-46f2f33adf53?preview=true</t>
-        </is>
-      </c>
+          <t>K 5491697</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>6-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
@@ -57453,10 +57461,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
+        </is>
+      </c>
       <c r="W24" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Diplom: MOS</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -57476,84 +57488,92 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+          <t>To'raboyeva Sabrina</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Akbar qizi</t>
+          <t>Ovlaqul qizi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>AB7166586</t>
+          <t>AE3558477</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>61409005680027</t>
+          <t>62709085590070</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>14.09.2000</t>
+          <t>27.09.2008</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Maftuna Akbar qizi</t>
+          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>K 5491697</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr"/>
+          <t>UM 03754217</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
+        </is>
+      </c>
       <c r="R25" s="10" t="inlineStr">
         <is>
-          <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -57561,14 +57581,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V25" s="10" t="inlineStr">
-        <is>
-          <t>Pasport AB7166586 va kasb-hunar kolleji diplomi K 5491697 tasdiqlandi</t>
-        </is>
-      </c>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Diplom: MOS</t>
+      <c r="V25" s="10" t="inlineStr"/>
+      <c r="W25" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -57588,7 +57604,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina</t>
+          <t>Tosheva Aziza</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -57598,82 +57614,74 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Ovlaqul qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AE3558477</t>
+          <t>AD4186169</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62709085590070</t>
+          <t>40404975650046</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27.09.2008</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>04.04.1997</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>To'raboyeva Sabrina Ovlaqul qizi</t>
+          <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 03754217</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897534/3444695/3d8e5032-8748-4a66-a325-8c01aa7a6c13?preview=true</t>
-        </is>
-      </c>
+          <t>K 3736287</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
@@ -57682,9 +57690,9 @@
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: FARQ</t>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -57704,7 +57712,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tosheva Aziza</t>
+          <t>To'xtayeva Durdona</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -57714,7 +57722,7 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -57724,69 +57732,69 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Nazim qizi</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
+          <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>AD4186169</t>
+          <t>AE5199773</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>40404975650046</t>
+          <t>61906085680012</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>04.04.1997</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr"/>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>Tosheva Aziza Sherzod qizi</t>
-        </is>
-      </c>
+          <t>19.06.2008</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr"/>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>K 3736287</t>
+          <t>UM 03728346</t>
         </is>
       </c>
       <c r="Q27" s="10" t="inlineStr"/>
       <c r="R27" s="10" t="inlineStr">
         <is>
-          <t>Qarshi iqtisodiyot kolleji</t>
+          <t>11-maktab</t>
         </is>
       </c>
       <c r="S27" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U27" s="15" t="inlineStr">
+        <is>
+          <t>CHALA</t>
         </is>
       </c>
       <c r="V27" s="10" t="inlineStr"/>
@@ -57812,17 +57820,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Tursunov Sohibjon</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -57832,37 +57836,37 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Nazim qizi</t>
+          <t>Hakim o'g'li</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>To'xtayeva Durdona Nazim qizi</t>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE5199773</t>
+          <t>AE4503488</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61906085680012</t>
+          <t>51106085680031</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>26.11.2025</t>
+          <t>07.10.2025</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>19.06.2008</t>
+          <t>11.06.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -57870,16 +57874,24 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Tursunov Sohibjon Hakim o'g'li</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03728346</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr"/>
+          <t>UM 03730110</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+        </is>
+      </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>11-maktab</t>
+          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -57892,15 +57904,15 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="U28" s="15" t="inlineStr">
-        <is>
-          <t>CHALA</t>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
@@ -57920,13 +57932,17 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+          <t>Umarova Iroda</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -57936,62 +57952,62 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Hakim o'g'li</t>
+          <t>Muzaffar qizi</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AE4503488</t>
+          <t>AE5293914</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>51106085680031</t>
+          <t>60512085590078</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>11.06.2008</t>
+          <t>05.12.2008</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>Tursunov Sohibjon Hakim o'g'li</t>
+          <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>UM 03730110</t>
+          <t>UM 03754201</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3927388/3467865/1d713551-c5c0-4d4c-b68f-8dc235881e2e?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
         </is>
       </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>70-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
@@ -58032,7 +58048,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda</t>
+          <t>Uroqova Jasmina</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -58042,7 +58058,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -58052,37 +58068,37 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Muzaffar qizi</t>
+          <t>Jasur qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE5293914</t>
+          <t>AE4989343</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60512085590078</t>
+          <t>60402095590060</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>05.12.2008</t>
+          <t>04.02.2009</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -58092,22 +58108,22 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Umarova Iroda Muzaffar qizi</t>
+          <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03754201</t>
+          <t>UM 03752857</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3897519/3441555/86264aa1-a1ee-4f4a-b201-f033531a675d?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -58125,7 +58141,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
+        </is>
+      </c>
       <c r="W30" s="13" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -58148,7 +58168,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina</t>
+          <t>Usmanova Iroda</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -58158,97 +58178,85 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-12 00:00:00</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Jasur qizi</t>
+          <t>Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
+          <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AE4989343</t>
+          <t>AE7821304</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>60402095590060</t>
+          <t>41406985680067</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>04.02.2009</t>
+          <t>14.06.1998</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>Uroqova Jasmina Jasur qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr"/>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>UM 03752857</t>
-        </is>
-      </c>
-      <c r="Q31" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3464473/4174128/b63a8739-54ff-4243-919e-f065773d664a?preview=true</t>
-        </is>
-      </c>
+          <t>K 4590366</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V31" s="10" t="inlineStr">
-        <is>
-          <t>Familiyasi pasport va shahodatnoma bo'yicha 'Uroqova' deb to'g'rilandi (#148)</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U31" s="15" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V31" s="10" t="inlineStr"/>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -58268,7 +58276,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda</t>
+          <t>Xurramova Shodiya</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -58278,85 +58286,93 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Abdurazzoq qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Usmanova Iroda Abdurazzoq qizi</t>
+          <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE7821304</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>41406985680067</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>14.06.1998</t>
+          <t>27.04.2002</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>K 4590366</t>
+          <t>UM 0438281</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U32" s="15" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
       <c r="W32" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -58376,7 +58392,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Yorboboyeva Mahliyo</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -58386,7 +58402,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -58396,58 +58412,62 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
@@ -58457,7 +58477,7 @@
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -58465,14 +58485,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V33" s="10" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V33" s="10" t="inlineStr"/>
       <c r="W33" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X33" s="7" t="inlineStr">
@@ -58481,124 +58497,8 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>26-02</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Xusan qizi</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>AB9239333</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>42207935680042</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>09.04.2018</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>22.07.1993</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>UM 03524597</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="inlineStr">
-        <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U34" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
-      <c r="X34" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73964,7 +73864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -75322,76 +75222,92 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Salimova Zarina</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>Qulmatova Shabbona</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Sobirjon qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Salimova Zarina Sobirjon qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>AD8890500</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>42110975590034</t>
+          <t>61008085680019</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>07.10.2024</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>21.10.1997</t>
+          <t>10.08.2008</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O17" s="10" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>K 4174786</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr"/>
       <c r="R17" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kolleji</t>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="11" t="inlineStr"/>
-      <c r="V17" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-15</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V17" s="10" t="inlineStr"/>
       <c r="W17" s="6" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X17" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -75406,92 +75322,76 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Samatova Oydin</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
+          <t>Salimova Zarina</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Sulaymon qizi</t>
+          <t>Sobirjon qizi</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Samatova Oydin Sulaymon qizi</t>
+          <t>Salimova Zarina Sobirjon qizi</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>AD8980430</t>
+          <t>AD8890500</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42910905720012</t>
+          <t>42110975590034</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>11.10.2024</t>
+          <t>07.10.2024</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>29.10.1990</t>
+          <t>21.10.1997</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>OR-SH 0346677</t>
+          <t>K 4174786</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
+          <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kolleji</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-15</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -75506,76 +75406,92 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Saydaliyeva Sevinch</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="11" t="inlineStr"/>
+          <t>Samatova Oydin</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Alimdjan qizi</t>
+          <t>Sulaymon qizi</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Saydaliyeva Sevinch Alimdjan qizi</t>
+          <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>AD3193422</t>
+          <t>AD8980430</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>60904075590012</t>
+          <t>42910905720012</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>03.05.2023</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>09.04.2007</t>
+          <t>29.10.1990</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr"/>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>PT 0176960</t>
+          <t>OR-SH 0346677</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr"/>
       <c r="R19" s="10" t="inlineStr">
         <is>
-          <t>Sharisabz shahar 2-sonli kasb-hunar maktabi</t>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
-        </is>
-      </c>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="11" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V19" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X19" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -75590,7 +75506,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Soliyeva E'zoza</t>
+          <t>Saydaliyeva Sevinch</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -75598,62 +75514,62 @@
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Sherbobo qizi</t>
+          <t>Alimdjan qizi</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Soliyeva E'zoza Sherbobo qizi</t>
+          <t>Saydaliyeva Sevinch Alimdjan qizi</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AD4615905</t>
+          <t>AD3193422</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61803065680094</t>
+          <t>60904075590012</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>15.09.2023</t>
+          <t>03.05.2023</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>18.03.2006</t>
+          <t>09.04.2007</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>UM 02151153</t>
+          <t>PT 0176960</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>44-maktab</t>
+          <t>Sharisabz shahar 2-sonli kasb-hunar maktabi</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr"/>
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr"/>
@@ -75674,7 +75590,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Suyunova Marjona</t>
+          <t>Soliyeva E'zoza</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -75682,42 +75598,62 @@
       <c r="F21" s="11" t="inlineStr"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Ravshan qizi</t>
+          <t>Sherbobo qizi</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Marjona Ravshan qizi</t>
+          <t>Soliyeva E'zoza Sherbobo qizi</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>AD4615905</t>
+        </is>
+      </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>60704065720162</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
+          <t>61803065680094</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>15.09.2023</t>
+        </is>
+      </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>07.04.2006</t>
+          <t>18.03.2006</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UM 02151153</t>
+        </is>
+      </c>
       <c r="Q21" s="10" t="inlineStr"/>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>44-maktab</t>
+        </is>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
       <c r="T21" s="11" t="inlineStr"/>
       <c r="U21" s="11" t="inlineStr"/>
       <c r="V21" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr"/>
@@ -75738,7 +75674,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Suyunova Ruxshona</t>
+          <t>Suyunova Marjona</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -75746,30 +75682,30 @@
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Karimjon qizi</t>
+          <t>Ravshan qizi</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Suyunova Ruxshona Karimjon qizi</t>
+          <t>Suyunova Marjona Ravshan qizi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61405065680104</t>
+          <t>60704065720162</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>14.05.2006</t>
+          <t>07.04.2006</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr"/>
@@ -75781,7 +75717,7 @@
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr"/>
@@ -75802,7 +75738,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Suyunova Shaxlo</t>
+          <t>Suyunova Ruxshona</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -75810,30 +75746,30 @@
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Tohir qizi</t>
+          <t>Karimjon qizi</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Suyunova Shaxlo Tohir qizi</t>
+          <t>Suyunova Ruxshona Karimjon qizi</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>61305065720094</t>
+          <t>61405065680104</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>13.05.2006</t>
+          <t>14.05.2006</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr"/>
@@ -75845,7 +75781,7 @@
       <c r="U23" s="11" t="inlineStr"/>
       <c r="V23" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W23" s="6" t="inlineStr"/>
@@ -75866,7 +75802,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Toshkentova Sevinchoy</t>
+          <t>Suyunova Shaxlo</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -75874,62 +75810,42 @@
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Zayniddin qizi</t>
+          <t>Tohir qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Toshkentova Sevinchoy Zayniddin qizi</t>
+          <t>Suyunova Shaxlo Tohir qizi</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>AD6867124</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60505075730035</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>18.04.2024</t>
-        </is>
-      </c>
+          <t>61305065720094</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>05.05.2007</t>
+          <t>13.05.2006</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>UM 03301249</t>
-        </is>
-      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>72-maktab</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr"/>
       <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr"/>
@@ -75950,7 +75866,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>To'xtayeva Shirida</t>
+          <t>Toshkentova Sevinchoy</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -75958,50 +75874,50 @@
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Sirojiddin qizi</t>
+          <t>Zayniddin qizi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>To'xtayeva Shirida Sirojiddin qizi</t>
+          <t>Toshkentova Sevinchoy Zayniddin qizi</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>AD1403124</t>
+          <t>AD6867124</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>61906055680059</t>
+          <t>60505075730035</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>30.05.2022</t>
+          <t>18.04.2024</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>19.06.2005</t>
+          <t>05.05.2007</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr"/>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>UM 1296145</t>
+          <t>UM 03301249</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr"/>
       <c r="R25" s="10" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>72-maktab</t>
         </is>
       </c>
       <c r="S25" s="11" t="inlineStr">
@@ -76034,7 +75950,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tug'izova Zahro</t>
+          <t>To'xtayeva Shirida</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
@@ -76042,42 +75958,62 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Tohir qizi</t>
+          <t>Sirojiddin qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Tug'izova Zahro Tohir qizi</t>
+          <t>To'xtayeva Shirida Sirojiddin qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>AD1403124</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62912005590041</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
+          <t>61906055680059</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>29.12.2000</t>
+          <t>19.06.2005</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>UM 1296145</t>
+        </is>
+      </c>
       <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>7-maktab</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
       <c r="T26" s="5" t="inlineStr"/>
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr"/>
@@ -76098,7 +76034,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tursunova Sevinch</t>
+          <t>Tug'izova Zahro</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
@@ -76106,30 +76042,30 @@
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Turg'un qizi</t>
+          <t>Tohir qizi</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Tursunova Sevinch Turg'un qizi</t>
+          <t>Tug'izova Zahro Tohir qizi</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>61905075680098</t>
+          <t>62912005590041</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>19.05.2007</t>
+          <t>29.12.2000</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr"/>
@@ -76141,7 +76077,7 @@
       <c r="U27" s="11" t="inlineStr"/>
       <c r="V27" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
         </is>
       </c>
       <c r="W27" s="6" t="inlineStr"/>
@@ -76162,7 +76098,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina</t>
+          <t>Tursunova Sevinch</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -76170,62 +76106,42 @@
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Nodir qizi</t>
+          <t>Turg'un qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina Nodir qizi</t>
+          <t>Tursunova Sevinch Turg'un qizi</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>AD9134105</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>62712075590017</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>24.10.2024</t>
-        </is>
-      </c>
+          <t>61905075680098</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>27.12.2007</t>
+          <t>19.05.2007</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>UM 03298099</t>
-        </is>
-      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>45-maktab</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
       <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr"/>
@@ -76246,7 +76162,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona</t>
+          <t>Usmonova Jasmina</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
@@ -76254,33 +76170,33 @@
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Nodir qizi</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona Botir qizi</t>
+          <t>Usmonova Jasmina Nodir qizi</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AD9713077</t>
+          <t>AD9134105</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>61412075590059</t>
+          <t>62712075590017</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>24.10.2024</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>14.12.2007</t>
+          <t>27.12.2007</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -76291,13 +76207,13 @@
       <c r="O29" s="10" t="inlineStr"/>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>UM 03295752</t>
+          <t>UM 03298099</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr"/>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
@@ -76309,7 +76225,7 @@
       <c r="U29" s="11" t="inlineStr"/>
       <c r="V29" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr"/>
@@ -76330,49 +76246,41 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona Botir qizi</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9713077</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>61412075590059</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>14.12.2007</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -76383,31 +76291,27 @@
       <c r="O30" s="4" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>UM 03295752</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U30" s="15" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
       <c r="W30" s="6" t="inlineStr"/>
       <c r="X30" s="7" t="inlineStr">
         <is>
@@ -76426,39 +76330,51 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>Uzoqova Fazilat</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E31" s="11" t="inlineStr"/>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Jamshid qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu Jamshid qizi</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr"/>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AD9506052</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>61508075590121</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>21,11,2024</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr"/>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -76467,27 +76383,31 @@
       <c r="O31" s="10" t="inlineStr"/>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>UM 03295886</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>10-maktab</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr"/>
-      <c r="U31" s="11" t="inlineStr"/>
-      <c r="V31" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U31" s="15" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V31" s="10" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr">
         <is>
@@ -76506,7 +76426,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna</t>
+          <t>Xamrayeva Niginabonu</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -76514,28 +76434,28 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Hushvaqt qizi</t>
+          <t>Jamshid qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+          <t>Xamrayeva Niginabonu Jamshid qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE2747402</t>
+          <t>AD9506052</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>40312902560107</t>
+          <t>61508075590121</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>20,05,2025</t>
+          <t>21,11,2024</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr"/>
@@ -76547,18 +76467,18 @@
       <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>K 1234480</t>
+          <t>UM 03295886</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Miroqi sport pedagogika kolleji</t>
+          <t>10-maktab</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr"/>
@@ -76586,7 +76506,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda</t>
+          <t>Yoqubova Maftuna</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
@@ -76594,28 +76514,28 @@
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Hasanovna</t>
+          <t>Hushvaqt qizi</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda Hasanovna</t>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AB7535578</t>
+          <t>AE2747402</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>40108945590034</t>
+          <t>40312902560107</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>22,08,2017</t>
+          <t>20,05,2025</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr"/>
@@ -76627,13 +76547,13 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>K 2404534</t>
+          <t>K 1234480</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika kolleji</t>
+          <t>Miroqi sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
@@ -76666,7 +76586,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Yuldosheva Iroda</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
@@ -76674,28 +76594,28 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Hasanovna</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Yuldosheva Iroda Hasanovna</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AB7535578</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>40108945590034</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
+          <t>22,08,2017</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
@@ -76707,18 +76627,18 @@
       <c r="O34" s="4" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>K 2404534</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>Shahrisabz pedagogika kolleji</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr"/>
@@ -76735,8 +76655,88 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="11" t="inlineStr"/>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>AD8888020</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>62609075590027</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr"/>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr"/>
+      <c r="V35" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -24356,7 +24356,7 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>25-16</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="C253" s="9" t="inlineStr">

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44930,7 +44930,7 @@
       </c>
       <c r="B479" s="8" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C479" s="9" t="inlineStr">
@@ -73864,7 +73864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -76162,7 +76162,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina</t>
+          <t>Uktamova Sarvinoz</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
@@ -76170,33 +76170,33 @@
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Nodir qizi</t>
+          <t>Obid qizi</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina Nodir qizi</t>
+          <t>Uktamova Sarvinoz Obid qizi</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AD9134105</t>
+          <t>AB6325652</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>62712075590017</t>
+          <t>61901005590031</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>24.10.2024</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>27.12.2007</t>
+          <t>19.01.2000</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -76207,25 +76207,25 @@
       <c r="O29" s="10" t="inlineStr"/>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>UM 03298099</t>
+          <t>K 5050490</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr"/>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="11" t="inlineStr"/>
       <c r="V29" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+          <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr"/>
@@ -76246,7 +76246,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona</t>
+          <t>Usmonova Jasmina</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
@@ -76254,33 +76254,33 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Nodir qizi</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona Botir qizi</t>
+          <t>Usmonova Jasmina Nodir qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AD9713077</t>
+          <t>AD9134105</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61412075590059</t>
+          <t>62712075590017</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>24.10.2024</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>14.12.2007</t>
+          <t>27.12.2007</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -76291,13 +76291,13 @@
       <c r="O30" s="4" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 03295752</t>
+          <t>UM 03298099</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
@@ -76309,7 +76309,7 @@
       <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr"/>
@@ -76330,49 +76330,41 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr"/>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona Botir qizi</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9713077</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>61412075590059</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>14.12.2007</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -76383,31 +76375,27 @@
       <c r="O31" s="10" t="inlineStr"/>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>UM 03295752</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U31" s="15" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V31" s="10" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr"/>
+      <c r="U31" s="11" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
       <c r="W31" s="6" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr">
         <is>
@@ -76426,39 +76414,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
+          <t>Uzoqova Fazilat</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Jamshid qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu Jamshid qizi</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AD9506052</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>61508075590121</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>21,11,2024</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr"/>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -76467,27 +76467,31 @@
       <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03295886</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>10-maktab</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U32" s="15" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr">
         <is>
@@ -76506,7 +76510,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna</t>
+          <t>Xamrayeva Niginabonu</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
@@ -76514,28 +76518,28 @@
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Hushvaqt qizi</t>
+          <t>Jamshid qizi</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+          <t>Xamrayeva Niginabonu Jamshid qizi</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AE2747402</t>
+          <t>AD9506052</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>40312902560107</t>
+          <t>61508075590121</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>20,05,2025</t>
+          <t>21,11,2024</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr"/>
@@ -76547,18 +76551,18 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>K 1234480</t>
+          <t>UM 03295886</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>Miroqi sport pedagogika kolleji</t>
+          <t>10-maktab</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr"/>
@@ -76586,7 +76590,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda</t>
+          <t>Yoqubova Maftuna</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
@@ -76594,28 +76598,28 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Hasanovna</t>
+          <t>Hushvaqt qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda Hasanovna</t>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AB7535578</t>
+          <t>AE2747402</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>40108945590034</t>
+          <t>40312902560107</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>22,08,2017</t>
+          <t>20,05,2025</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
@@ -76627,13 +76631,13 @@
       <c r="O34" s="4" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>K 2404534</t>
+          <t>K 1234480</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika kolleji</t>
+          <t>Miroqi sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
@@ -76666,7 +76670,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Yuldosheva Iroda</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
@@ -76674,28 +76678,28 @@
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Hasanovna</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Yuldosheva Iroda Hasanovna</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr"/>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AB7535578</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>40108945590034</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
+          <t>22,08,2017</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr"/>
@@ -76707,18 +76711,18 @@
       <c r="O35" s="10" t="inlineStr"/>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>K 2404534</t>
         </is>
       </c>
       <c r="Q35" s="10" t="inlineStr"/>
       <c r="R35" s="10" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>Shahrisabz pedagogika kolleji</t>
         </is>
       </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T35" s="11" t="inlineStr"/>
@@ -76735,8 +76739,88 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>AD8888020</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>62609075590027</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr"/>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -2337,7 +2337,7 @@
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 26</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 268</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 74</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A269</t>
+          <t>269</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>26/27 sh/a 100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -5505,7 +5505,7 @@
       <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 28</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 76</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
@@ -6913,7 +6913,7 @@
       <c r="D67" s="10" t="inlineStr"/>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>25/26 sh/a 186</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -7253,7 +7253,7 @@
       <c r="D71" s="10" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>25/26 sh/a 6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
       <c r="D74" s="4" t="inlineStr"/>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A367</t>
+          <t>367</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
@@ -7601,7 +7601,7 @@
       <c r="D75" s="10" t="inlineStr"/>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 375</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -7693,7 +7693,7 @@
       <c r="D76" s="4" t="inlineStr"/>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 140</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
@@ -7953,7 +7953,7 @@
       <c r="D79" s="10" t="inlineStr"/>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 286</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
       <c r="D84" s="4" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A149</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       <c r="D87" s="10" t="inlineStr"/>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 103</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
       <c r="D95" s="10" t="inlineStr"/>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>26/27 sh/a 78</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -10533,7 +10533,7 @@
       <c r="D107" s="10" t="inlineStr"/>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>26/27 Sh/A79</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -10725,7 +10725,7 @@
       <c r="D109" s="10" t="inlineStr"/>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 161</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -12877,7 +12877,7 @@
       <c r="D131" s="10" t="inlineStr"/>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A105</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -12965,7 +12965,7 @@
       <c r="D132" s="4" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr"/>
@@ -13053,7 +13053,7 @@
       <c r="D133" s="10" t="inlineStr"/>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>25/26 sh/a 333</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -13333,7 +13333,7 @@
       <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 116</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
@@ -13417,7 +13417,7 @@
       <c r="D137" s="10" t="inlineStr"/>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 220</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -13699,7 +13699,7 @@
       <c r="D140" s="4" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>25/26 sh/a 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr"/>
@@ -13787,7 +13787,7 @@
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 264</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -13959,7 +13959,7 @@
       <c r="D143" s="10" t="inlineStr"/>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 107</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -14259,7 +14259,7 @@
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 142</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr"/>
@@ -14347,7 +14347,7 @@
       <c r="D147" s="10" t="inlineStr"/>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>26/27 sh/a 277</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -14547,7 +14547,7 @@
       <c r="D149" s="10" t="inlineStr"/>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A106</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -14835,7 +14835,7 @@
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A57</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr"/>
@@ -17531,7 +17531,7 @@
       <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>25/26 sh/a 385</t>
+          <t>385</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr"/>
@@ -19481,7 +19481,7 @@
       <c r="D201" s="10" t="inlineStr"/>
       <c r="E201" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A150</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F201" s="11" t="inlineStr"/>
@@ -20043,7 +20043,7 @@
       <c r="D207" s="10" t="inlineStr"/>
       <c r="E207" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 229</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F207" s="11" t="inlineStr"/>
@@ -20557,7 +20557,7 @@
       <c r="D212" s="4" t="inlineStr"/>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 266</t>
+          <t>266</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr"/>
@@ -21297,7 +21297,7 @@
       <c r="D220" s="4" t="inlineStr"/>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 506</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr"/>
@@ -21651,7 +21651,7 @@
       <c r="D224" s="4" t="inlineStr"/>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 272</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr"/>
@@ -22007,7 +22007,7 @@
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 159</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr"/>
@@ -22095,7 +22095,7 @@
       <c r="D229" s="10" t="inlineStr"/>
       <c r="E229" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 226</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F229" s="11" t="inlineStr"/>
@@ -23359,7 +23359,7 @@
       <c r="D242" s="4" t="inlineStr"/>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 177</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr"/>
@@ -23447,7 +23447,7 @@
       <c r="D243" s="10" t="inlineStr"/>
       <c r="E243" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A252</t>
+          <t>252</t>
         </is>
       </c>
       <c r="F243" s="11" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
       <c r="D247" s="10" t="inlineStr"/>
       <c r="E247" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 285</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F247" s="11" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       <c r="D248" s="4" t="inlineStr"/>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 285</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr"/>
@@ -25511,7 +25511,7 @@
       <c r="D266" s="4" t="inlineStr"/>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 372</t>
+          <t>372</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr"/>
@@ -25899,7 +25899,7 @@
       <c r="D270" s="4" t="inlineStr"/>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 286</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr"/>
@@ -26419,7 +26419,7 @@
       <c r="D276" s="4" t="inlineStr"/>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 369</t>
+          <t>369</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr"/>
@@ -27115,7 +27115,7 @@
       <c r="D284" s="4" t="inlineStr"/>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A165</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr"/>
@@ -27999,7 +27999,7 @@
       <c r="D293" s="10" t="inlineStr"/>
       <c r="E293" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A358</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F293" s="11" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       <c r="D296" s="4" t="inlineStr"/>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A114</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr"/>
@@ -28347,7 +28347,7 @@
       <c r="D297" s="10" t="inlineStr"/>
       <c r="E297" s="11" t="inlineStr">
         <is>
-          <t>25/26 Sh/A246</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F297" s="11" t="inlineStr"/>
@@ -30517,7 +30517,7 @@
       <c r="D321" s="10" t="inlineStr"/>
       <c r="E321" s="11" t="inlineStr">
         <is>
-          <t>25/26 Sh/A509</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F321" s="11" t="inlineStr"/>
@@ -31797,7 +31797,7 @@
       <c r="D335" s="10" t="inlineStr"/>
       <c r="E335" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F335" s="11" t="inlineStr"/>
@@ -32137,7 +32137,7 @@
       <c r="D339" s="10" t="inlineStr"/>
       <c r="E339" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 288</t>
+          <t>288</t>
         </is>
       </c>
       <c r="F339" s="11" t="inlineStr"/>
@@ -32345,7 +32345,7 @@
       <c r="D341" s="10" t="inlineStr"/>
       <c r="E341" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 338</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F341" s="11" t="inlineStr"/>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>25/26 SH/A 511</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F352" s="5" t="inlineStr">
@@ -33861,7 +33861,7 @@
       <c r="D358" s="4" t="inlineStr"/>
       <c r="E358" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 259</t>
+          <t>259</t>
         </is>
       </c>
       <c r="F358" s="5" t="inlineStr"/>
@@ -33945,7 +33945,7 @@
       <c r="D359" s="10" t="inlineStr"/>
       <c r="E359" s="11" t="inlineStr">
         <is>
-          <t>26/27 sh/a 235</t>
+          <t>235</t>
         </is>
       </c>
       <c r="F359" s="11" t="inlineStr"/>
@@ -35147,7 +35147,7 @@
       <c r="D372" s="4" t="inlineStr"/>
       <c r="E372" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A361</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F372" s="5" t="inlineStr"/>
@@ -35671,7 +35671,7 @@
       <c r="D378" s="4" t="inlineStr"/>
       <c r="E378" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F378" s="5" t="inlineStr"/>
@@ -36799,7 +36799,7 @@
       <c r="D390" s="4" t="inlineStr"/>
       <c r="E390" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 327</t>
+          <t>327</t>
         </is>
       </c>
       <c r="F390" s="5" t="inlineStr"/>
@@ -38039,7 +38039,7 @@
       <c r="D403" s="10" t="inlineStr"/>
       <c r="E403" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A40</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F403" s="11" t="inlineStr"/>
@@ -38859,7 +38859,7 @@
       <c r="D412" s="4" t="inlineStr"/>
       <c r="E412" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 239</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F412" s="5" t="inlineStr"/>
@@ -39171,7 +39171,7 @@
       <c r="D416" s="4" t="inlineStr"/>
       <c r="E416" s="5" t="inlineStr">
         <is>
-          <t>26/27 sh/a 147</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F416" s="5" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       <c r="D418" s="4" t="inlineStr"/>
       <c r="E418" s="5" t="inlineStr">
         <is>
-          <t>24/25 SH/A 41</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F418" s="5" t="inlineStr"/>
@@ -39539,7 +39539,7 @@
       <c r="D420" s="4" t="inlineStr"/>
       <c r="E420" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 346</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F420" s="5" t="inlineStr"/>
@@ -39823,7 +39823,7 @@
       <c r="D423" s="10" t="inlineStr"/>
       <c r="E423" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 263</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F423" s="11" t="inlineStr"/>
@@ -40383,7 +40383,7 @@
       <c r="D429" s="10" t="inlineStr"/>
       <c r="E429" s="11" t="inlineStr">
         <is>
-          <t>25/26 Sh/A365</t>
+          <t>365</t>
         </is>
       </c>
       <c r="F429" s="11" t="inlineStr"/>
@@ -40475,7 +40475,7 @@
       <c r="D430" s="4" t="inlineStr"/>
       <c r="E430" s="5" t="inlineStr">
         <is>
-          <t>26/27 Sh/A94</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F430" s="5" t="inlineStr"/>
@@ -41619,7 +41619,7 @@
       <c r="D443" s="10" t="inlineStr"/>
       <c r="E443" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A66</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F443" s="11" t="inlineStr"/>
@@ -43439,7 +43439,7 @@
       <c r="D463" s="10" t="inlineStr"/>
       <c r="E463" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A178</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F463" s="11" t="inlineStr"/>
@@ -43527,7 +43527,7 @@
       <c r="D464" s="4" t="inlineStr"/>
       <c r="E464" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A 241</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F464" s="5" t="inlineStr"/>
@@ -45429,7 +45429,7 @@
       <c r="D484" s="4" t="inlineStr"/>
       <c r="E484" s="5" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 260</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F484" s="5" t="inlineStr"/>
@@ -47209,7 +47209,7 @@
       <c r="D503" s="10" t="inlineStr"/>
       <c r="E503" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A84</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F503" s="11" t="inlineStr"/>
@@ -47954,7 +47954,7 @@
       <c r="D511" s="10" t="inlineStr"/>
       <c r="E511" s="11" t="inlineStr">
         <is>
-          <t>26/27 sh/a 180</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F511" s="11" t="inlineStr"/>
@@ -48848,7 +48848,7 @@
       <c r="D521" s="10" t="inlineStr"/>
       <c r="E521" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A123</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F521" s="11" t="inlineStr"/>
@@ -49766,7 +49766,7 @@
       <c r="D530" s="4" t="inlineStr"/>
       <c r="E530" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A153</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F530" s="5" t="inlineStr"/>
@@ -49934,7 +49934,7 @@
       <c r="D532" s="4" t="inlineStr"/>
       <c r="E532" s="5" t="inlineStr">
         <is>
-          <t>26/27 SH/A174</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F532" s="5" t="inlineStr"/>
@@ -51428,7 +51428,7 @@
       <c r="D547" s="10" t="inlineStr"/>
       <c r="E547" s="11" t="inlineStr">
         <is>
-          <t>26/27 sh/a 155</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F547" s="11" t="inlineStr"/>
@@ -51960,7 +51960,7 @@
       <c r="D553" s="10" t="inlineStr"/>
       <c r="E553" s="11" t="inlineStr">
         <is>
-          <t>26/27 SH/A 98</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F553" s="11" t="inlineStr"/>
@@ -52048,7 +52048,7 @@
       <c r="D554" s="4" t="inlineStr"/>
       <c r="E554" s="5" t="inlineStr">
         <is>
-          <t>26/37 SH/A 125</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F554" s="5" t="inlineStr"/>
@@ -52136,7 +52136,7 @@
       <c r="D555" s="10" t="inlineStr"/>
       <c r="E555" s="11" t="inlineStr">
         <is>
-          <t>25/26 SH/A 520</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F555" s="11" t="inlineStr"/>
